--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5323,31 +5323,113 @@
       <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="12" t="inlineStr">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="C58" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E58" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.0187</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L58" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="M58" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="O58" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I58" s="13" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="J58" s="13" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K58" s="13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L58" s="13" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="M58" s="13" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="N58" s="13" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="O58" s="13" t="n">
-        <v>3.27</v>
+      <c r="I59" s="13" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="J59" s="13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K59" s="13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="L59" s="13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="M59" s="13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="N59" s="13" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O59" s="13" t="n">
+        <v>2.97</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,11 +115,14 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -666,13 +669,13 @@
         <v>0.23</v>
       </c>
       <c r="I2" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="J2" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="K2" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="L2" t="n">
         <v>2.9</v>
@@ -681,10 +684,10 @@
         <v>3.03</v>
       </c>
       <c r="N2" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="O2" t="n">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -715,14 +718,10 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -799,7 +798,7 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="9" t="inlineStr">
+      <c r="W3" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -881,7 +880,7 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="9" t="inlineStr">
+      <c r="W4" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -963,7 +962,7 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="W5" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1049,7 +1048,7 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="W6" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1133,7 +1132,7 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="W7" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1221,7 +1220,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="W8" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1303,7 +1302,7 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1387,7 +1386,7 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1475,7 +1474,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="W11" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1559,7 +1558,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1639,7 +1638,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1721,7 +1720,7 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1801,7 +1800,7 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1887,7 +1886,7 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1969,7 +1968,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2053,7 +2052,7 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2131,7 +2130,7 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2213,7 +2212,7 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2299,7 +2298,7 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2383,7 +2382,7 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="11" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2463,7 +2462,7 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="11" t="inlineStr">
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2547,7 +2546,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2629,7 +2628,7 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2713,7 +2712,7 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2797,7 +2796,7 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2883,7 +2882,7 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2971,7 +2970,7 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3057,7 +3056,7 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3139,7 +3138,7 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3221,7 +3220,7 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3305,7 +3304,7 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3391,7 +3390,7 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="11" t="inlineStr">
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3471,7 +3470,7 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3549,7 +3548,7 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3637,7 +3636,7 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3723,7 +3722,7 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3805,7 +3804,7 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3891,7 +3890,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3971,7 +3970,7 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4059,7 +4058,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4141,7 +4140,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4225,7 +4224,7 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4309,7 +4308,7 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4393,7 +4392,7 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4471,7 +4470,7 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4561,7 +4560,7 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4643,7 +4642,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4725,7 +4724,7 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4813,7 +4812,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="11" t="inlineStr">
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4893,7 +4892,7 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4973,7 +4972,7 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5061,7 +5060,7 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5145,7 +5144,7 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="11" t="inlineStr">
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5229,7 +5228,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5315,7 +5314,7 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5329,25 +5328,25 @@
         </is>
       </c>
       <c r="B58" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C58" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="D58" t="n">
         <v>2.87</v>
       </c>
-      <c r="C58" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="D58" t="n">
-        <v>2.85</v>
-      </c>
       <c r="E58" t="n">
-        <v>2.88</v>
+        <v/>
       </c>
       <c r="F58" t="n">
-        <v>0.05</v>
+        <v/>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0187</v>
+        <v/>
       </c>
       <c r="H58" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="I58" t="n">
         <v>2.49</v>
@@ -5370,8 +5369,10 @@
       <c r="O58" t="n">
         <v>3.27</v>
       </c>
-      <c r="P58" s="6" t="n">
-        <v/>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5379,9 +5380,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5393,43 +5394,43 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="12" t="inlineStr">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I59" s="13" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="J59" s="13" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K59" s="13" t="n">
+      <c r="I59" s="14" t="n">
         <v>2.85</v>
       </c>
-      <c r="L59" s="13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="M59" s="13" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="N59" s="13" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="O59" s="13" t="n">
-        <v>2.97</v>
+      <c r="J59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O59" s="14" t="n">
+        <v>2.91</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,9 +120,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -5328,25 +5325,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="C58" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="D58" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>2.9</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>0.06</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>0.023</v>
       </c>
       <c r="H58" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="I58" t="n">
         <v>2.49</v>
@@ -5369,10 +5366,8 @@
       <c r="O58" t="n">
         <v>3.27</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P58" s="6" t="n">
+        <v/>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5380,9 +5375,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5401,36 +5396,36 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="13" t="inlineStr">
+      <c r="A59" s="12" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I59" s="14" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="J59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O59" s="14" t="n">
-        <v>2.91</v>
+      <c r="I59" s="13" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="J59" s="13" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K59" s="13" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="L59" s="13" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="M59" s="13" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="N59" s="13" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="O59" s="13" t="n">
+        <v>2.97</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -5334,13 +5334,13 @@
         <v>2.85</v>
       </c>
       <c r="E58" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="F58" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.023</v>
+        <v>0.0177</v>
       </c>
       <c r="H58" t="n">
         <v>0.06</v>
@@ -5410,19 +5410,19 @@
         <v>2.79</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>2.97</v>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -5328,22 +5328,22 @@
         <v>2.87</v>
       </c>
       <c r="C58" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="D58" t="n">
         <v>2.85</v>
       </c>
       <c r="E58" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="F58" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0177</v>
+        <v>0.0399</v>
       </c>
       <c r="H58" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="I58" t="n">
         <v>2.49</v>
@@ -5377,11 +5377,13 @@
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5407,25 +5409,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>2.94</v>
+        <v>3.07</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -666,25 +666,25 @@
         <v>0.23</v>
       </c>
       <c r="I2" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="J2" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="K2" t="n">
         <v>2.81</v>
       </c>
       <c r="L2" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="M2" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="N2" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="O2" t="n">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5334,13 +5334,13 @@
         <v>2.85</v>
       </c>
       <c r="E58" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="F58" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0399</v>
+        <v>0.0367</v>
       </c>
       <c r="H58" t="n">
         <v>0.1</v>
@@ -5412,7 +5412,7 @@
         <v>2.75</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="K59" s="13" t="n">
         <v>2.89</v>
@@ -5421,10 +5421,10 @@
         <v>2.92</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>3.05</v>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -5334,13 +5334,13 @@
         <v>2.85</v>
       </c>
       <c r="E58" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0367</v>
+        <v>0.0321</v>
       </c>
       <c r="H58" t="n">
         <v>0.1</v>
@@ -5412,19 +5412,19 @@
         <v>2.75</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>3.05</v>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -5334,13 +5334,13 @@
         <v>2.85</v>
       </c>
       <c r="E58" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="F58" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0321</v>
+        <v>0.0357</v>
       </c>
       <c r="H58" t="n">
         <v>0.1</v>
@@ -5412,19 +5412,19 @@
         <v>2.75</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>3.05</v>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -5334,13 +5334,13 @@
         <v>2.85</v>
       </c>
       <c r="E58" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0357</v>
+        <v>0.0389</v>
       </c>
       <c r="H58" t="n">
         <v>0.1</v>
@@ -5412,19 +5412,19 @@
         <v>2.75</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="L59" s="13" t="n">
         <v>2.92</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>3.05</v>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -5328,22 +5328,22 @@
         <v>2.87</v>
       </c>
       <c r="C58" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="D58" t="n">
         <v>2.85</v>
       </c>
       <c r="E58" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="F58" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.0459</v>
+      </c>
+      <c r="H58" t="n">
         <v>0.11</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0389</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.1</v>
       </c>
       <c r="I58" t="n">
         <v>2.49</v>
@@ -5409,25 +5409,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -5328,22 +5328,22 @@
         <v>2.87</v>
       </c>
       <c r="C58" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="D58" t="n">
         <v>2.85</v>
       </c>
       <c r="E58" t="n">
-        <v>2.96</v>
+        <v>2.89</v>
       </c>
       <c r="F58" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0459</v>
+        <v>0.0219</v>
       </c>
       <c r="H58" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="I58" t="n">
         <v>2.49</v>
@@ -5377,13 +5377,11 @@
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5409,25 +5407,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2.87</v>
+        <v>2.79</v>
       </c>
       <c r="K59" s="13" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L59" s="13" t="n">
         <v>2.9</v>
       </c>
-      <c r="L59" s="13" t="n">
-        <v>2.93</v>
-      </c>
       <c r="M59" s="13" t="n">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -666,25 +666,25 @@
         <v>0.23</v>
       </c>
       <c r="I2" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="J2" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="K2" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="L2" t="n">
         <v>2.89</v>
       </c>
       <c r="M2" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="N2" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="O2" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5340,7 +5340,7 @@
         <v>0.06</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0219</v>
+        <v>0.0212</v>
       </c>
       <c r="H58" t="n">
         <v>0.1</v>
@@ -5410,7 +5410,7 @@
         <v>2.75</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="K59" s="13" t="n">
         <v>2.84</v>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -5328,22 +5328,22 @@
         <v>2.87</v>
       </c>
       <c r="C58" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="D58" t="n">
         <v>2.85</v>
       </c>
       <c r="E58" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="F58" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0212</v>
+        <v>0.0134</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="I58" t="n">
         <v>2.49</v>
@@ -5380,8 +5380,10 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5407,25 +5409,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>3.05</v>
+        <v>3.11</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -5334,13 +5334,13 @@
         <v>2.85</v>
       </c>
       <c r="E58" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="F58" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0113</v>
       </c>
       <c r="H58" t="n">
         <v>0.13</v>
@@ -5412,7 +5412,7 @@
         <v>2.72</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="K59" s="13" t="n">
         <v>2.8</v>
@@ -5424,7 +5424,7 @@
         <v>2.93</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>3.11</v>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,8 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X59"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -666,32 +659,34 @@
         <v>0.23</v>
       </c>
       <c r="I2" t="n">
-        <v>2.58</v>
+        <v>2.71</v>
       </c>
       <c r="J2" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="K2" t="n">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="L2" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="M2" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="N2" t="n">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="O2" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
+        <v>3.1</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q2" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
@@ -5334,13 +5329,13 @@
         <v>2.85</v>
       </c>
       <c r="E58" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="F58" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0113</v>
+        <v>0.0081</v>
       </c>
       <c r="H58" t="n">
         <v>0.13</v>
@@ -5375,9 +5370,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
@@ -5400,34 +5395,6 @@
         <is>
           <t>中警訊</t>
         </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>下週預測</t>
-        </is>
-      </c>
-      <c r="I59" s="13" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="J59" s="13" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K59" s="13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L59" s="13" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="M59" s="13" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="N59" s="13" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="O59" s="13" t="n">
-        <v>3.11</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -5335,7 +5335,7 @@
         <v>0.02</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0081</v>
+        <v>0.0078</v>
       </c>
       <c r="H58" t="n">
         <v>0.13</v>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -104,17 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,134 +634,136 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0.1108</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="N2" t="n">
         <v>2.88</v>
       </c>
-      <c r="C2" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>-0.07480000000000001</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="M2" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3.05</v>
-      </c>
       <c r="O2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
+        <v>3.15</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
       <c r="V2" s="8" t="n">
         <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.64</v>
+        <v>2.97</v>
       </c>
       <c r="C3" t="n">
-        <v>3.02</v>
+        <v>3.13</v>
       </c>
       <c r="D3" t="n">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3</v>
+        <v>0.05</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.1108</v>
+        <v>0.017</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4</v>
+        <v>0.26</v>
       </c>
       <c r="I3" t="n">
-        <v>2.46</v>
+        <v>2.22</v>
       </c>
       <c r="J3" t="n">
-        <v>2.41</v>
+        <v>2.68</v>
       </c>
       <c r="K3" t="n">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="L3" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="M3" t="n">
-        <v>2.81</v>
+        <v>3.2</v>
       </c>
       <c r="N3" t="n">
-        <v>2.88</v>
+        <v>3.49</v>
       </c>
       <c r="O3" t="n">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -772,82 +774,74 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.97</v>
+        <v>3.09</v>
       </c>
       <c r="C4" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="D4" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="E4" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05</v>
+        <v>-0.11</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.017</v>
+        <v>-0.0351</v>
       </c>
       <c r="H4" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="I4" t="n">
-        <v>2.22</v>
+        <v>2.61</v>
       </c>
       <c r="J4" t="n">
-        <v>2.68</v>
+        <v>2.81</v>
       </c>
       <c r="K4" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="L4" t="n">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="M4" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="N4" t="n">
-        <v>3.49</v>
+        <v>3.33</v>
       </c>
       <c r="O4" t="n">
-        <v>3.42</v>
+        <v>3.39</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -855,16 +849,20 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -872,60 +870,64 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="M5" t="n">
         <v>3.09</v>
       </c>
-      <c r="C5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>-0.0351</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="L5" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="M5" t="n">
-        <v>3.18</v>
-      </c>
       <c r="N5" t="n">
-        <v>3.33</v>
+        <v>3.19</v>
       </c>
       <c r="O5" t="n">
-        <v>3.39</v>
+        <v>3.5</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -938,7 +940,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -954,64 +956,64 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="C6" t="n">
-        <v>3.17</v>
+        <v>2.97</v>
       </c>
       <c r="D6" t="n">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="E6" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="F6" t="n">
         <v>-0.05</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.018</v>
+        <v>-0.0184</v>
       </c>
       <c r="H6" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="J6" t="n">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="K6" t="n">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="L6" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="M6" t="n">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
       <c r="N6" t="n">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1024,15 +1026,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S6" s="7" t="inlineStr">
+      <c r="S6" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1040,7 +1040,7 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1054,50 +1054,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.91</v>
+        <v>3.15</v>
       </c>
       <c r="C7" t="n">
-        <v>2.97</v>
+        <v>3.59</v>
       </c>
       <c r="D7" t="n">
-        <v>2.77</v>
+        <v>3.13</v>
       </c>
       <c r="E7" t="n">
-        <v>2.84</v>
+        <v>3.32</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.05</v>
+        <v>0.49</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0184</v>
+        <v>0.1725</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="I7" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="J7" t="n">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
       <c r="K7" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="L7" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="M7" t="n">
-        <v>3.04</v>
+        <v>2.93</v>
       </c>
       <c r="N7" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="O7" t="n">
-        <v>3.48</v>
+        <v>3.16</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1105,83 +1105,83 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="C8" t="n">
-        <v>3.59</v>
+        <v>3.55</v>
       </c>
       <c r="D8" t="n">
-        <v>3.13</v>
+        <v>3.09</v>
       </c>
       <c r="E8" t="n">
-        <v>3.32</v>
+        <v>3.11</v>
       </c>
       <c r="F8" t="n">
-        <v>0.49</v>
+        <v>-0.22</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.1725</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="I8" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="J8" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="K8" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="L8" t="n">
-        <v>2.85</v>
+        <v>3.34</v>
       </c>
       <c r="M8" t="n">
-        <v>2.93</v>
+        <v>3.55</v>
       </c>
       <c r="N8" t="n">
-        <v>3.01</v>
+        <v>3.76</v>
       </c>
       <c r="O8" t="n">
-        <v>3.16</v>
+        <v>4.04</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1189,12 +1189,14 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S8" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
@@ -1202,70 +1204,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="C9" t="n">
-        <v>3.55</v>
+        <v>3.14</v>
       </c>
       <c r="D9" t="n">
-        <v>3.09</v>
+        <v>2.89</v>
       </c>
       <c r="E9" t="n">
-        <v>3.11</v>
+        <v>3.01</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.22</v>
+        <v>-0.1</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.0316</v>
       </c>
       <c r="H9" t="n">
-        <v>0.46</v>
+        <v>0.25</v>
       </c>
       <c r="I9" t="n">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="J9" t="n">
-        <v>2.85</v>
+        <v>2.54</v>
       </c>
       <c r="K9" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="L9" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="M9" t="n">
         <v>3.34</v>
       </c>
-      <c r="M9" t="n">
-        <v>3.55</v>
-      </c>
       <c r="N9" t="n">
-        <v>3.76</v>
+        <v>3.46</v>
       </c>
       <c r="O9" t="n">
-        <v>4.04</v>
+        <v>4.01</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1278,15 +1280,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="7" t="inlineStr">
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1294,7 +1294,7 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1308,50 +1308,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="C10" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="D10" t="n">
         <v>3.14</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.0984</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K10" t="n">
         <v>2.89</v>
       </c>
-      <c r="E10" t="n">
+      <c r="L10" t="n">
         <v>3.01</v>
       </c>
-      <c r="F10" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>-0.0316</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="L10" t="n">
-        <v>3.21</v>
-      </c>
       <c r="M10" t="n">
-        <v>3.34</v>
+        <v>3.13</v>
       </c>
       <c r="N10" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="O10" t="n">
-        <v>4.01</v>
+        <v>3.38</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1359,83 +1359,83 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.16</v>
+        <v>3.41</v>
       </c>
       <c r="C11" t="n">
-        <v>3.57</v>
+        <v>4.16</v>
       </c>
       <c r="D11" t="n">
-        <v>3.14</v>
+        <v>3.19</v>
       </c>
       <c r="E11" t="n">
-        <v>3.3</v>
+        <v>4.12</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3</v>
+        <v>0.82</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0984</v>
+        <v>0.2482</v>
       </c>
       <c r="H11" t="n">
-        <v>0.44</v>
+        <v>0.96</v>
       </c>
       <c r="I11" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="J11" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="K11" t="n">
-        <v>2.89</v>
+        <v>3.09</v>
       </c>
       <c r="L11" t="n">
-        <v>3.01</v>
+        <v>3.33</v>
       </c>
       <c r="M11" t="n">
-        <v>3.13</v>
+        <v>3.52</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>3.71</v>
       </c>
       <c r="O11" t="n">
-        <v>3.38</v>
+        <v>4.01</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1446,7 +1446,7 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="10" t="inlineStr">
+      <c r="S11" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1458,15 +1458,15 @@
       </c>
       <c r="U11" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1476,50 +1476,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.41</v>
+        <v>4.16</v>
       </c>
       <c r="C12" t="n">
-        <v>4.16</v>
+        <v>4.42</v>
       </c>
       <c r="D12" t="n">
-        <v>3.19</v>
+        <v>4.09</v>
       </c>
       <c r="E12" t="n">
-        <v>4.12</v>
+        <v>4.32</v>
       </c>
       <c r="F12" t="n">
-        <v>0.82</v>
+        <v>0.19</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.2482</v>
+        <v>0.0463</v>
       </c>
       <c r="H12" t="n">
-        <v>0.96</v>
+        <v>0.33</v>
       </c>
       <c r="I12" t="n">
-        <v>2.7</v>
+        <v>2.23</v>
       </c>
       <c r="J12" t="n">
-        <v>2.84</v>
+        <v>3.38</v>
       </c>
       <c r="K12" t="n">
-        <v>3.09</v>
+        <v>3.64</v>
       </c>
       <c r="L12" t="n">
-        <v>3.33</v>
+        <v>3.9</v>
       </c>
       <c r="M12" t="n">
-        <v>3.52</v>
+        <v>4.61</v>
       </c>
       <c r="N12" t="n">
-        <v>3.71</v>
+        <v>5.31</v>
       </c>
       <c r="O12" t="n">
-        <v>4.01</v>
+        <v>5.12</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1530,27 +1530,23 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="S12" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V12" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1560,50 +1556,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.16</v>
+        <v>4.48</v>
       </c>
       <c r="C13" t="n">
-        <v>4.42</v>
+        <v>4.69</v>
       </c>
       <c r="D13" t="n">
-        <v>4.09</v>
+        <v>4.26</v>
       </c>
       <c r="E13" t="n">
-        <v>4.32</v>
+        <v>4.57</v>
       </c>
       <c r="F13" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0463</v>
+        <v>0.0582</v>
       </c>
       <c r="H13" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="I13" t="n">
-        <v>2.23</v>
+        <v>3.75</v>
       </c>
       <c r="J13" t="n">
-        <v>3.38</v>
+        <v>4.01</v>
       </c>
       <c r="K13" t="n">
-        <v>3.64</v>
+        <v>4.15</v>
       </c>
       <c r="L13" t="n">
-        <v>3.9</v>
+        <v>4.28</v>
       </c>
       <c r="M13" t="n">
-        <v>4.61</v>
+        <v>4.48</v>
       </c>
       <c r="N13" t="n">
-        <v>5.31</v>
+        <v>4.68</v>
       </c>
       <c r="O13" t="n">
-        <v>5.12</v>
+        <v>4.75</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1614,7 +1610,7 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="10" t="inlineStr">
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1624,13 +1620,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U13" s="8" t="n">
-        <v/>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1640,50 +1638,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.48</v>
+        <v>4.53</v>
       </c>
       <c r="C14" t="n">
-        <v>4.69</v>
+        <v>4.68</v>
       </c>
       <c r="D14" t="n">
-        <v>4.26</v>
+        <v>4.24</v>
       </c>
       <c r="E14" t="n">
-        <v>4.57</v>
+        <v>4.58</v>
       </c>
       <c r="F14" t="n">
-        <v>0.25</v>
+        <v>0.01</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0582</v>
+        <v>0.0031</v>
       </c>
       <c r="H14" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="I14" t="n">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="J14" t="n">
-        <v>4.01</v>
+        <v>4.19</v>
       </c>
       <c r="K14" t="n">
-        <v>4.15</v>
+        <v>4.35</v>
       </c>
       <c r="L14" t="n">
-        <v>4.28</v>
+        <v>4.52</v>
       </c>
       <c r="M14" t="n">
-        <v>4.48</v>
+        <v>4.78</v>
       </c>
       <c r="N14" t="n">
-        <v>4.68</v>
+        <v>5.04</v>
       </c>
       <c r="O14" t="n">
-        <v>4.75</v>
+        <v>5.11</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1691,81 +1689,83 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
+      <c r="R14" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.53</v>
+        <v>4.47</v>
       </c>
       <c r="C15" t="n">
-        <v>4.68</v>
+        <v>4.87</v>
       </c>
       <c r="D15" t="n">
-        <v>4.24</v>
+        <v>4.27</v>
       </c>
       <c r="E15" t="n">
-        <v>4.58</v>
+        <v>4.85</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01</v>
+        <v>0.27</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.059</v>
       </c>
       <c r="H15" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="I15" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="J15" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="K15" t="n">
-        <v>4.35</v>
+        <v>4.36</v>
       </c>
       <c r="L15" t="n">
         <v>4.52</v>
       </c>
       <c r="M15" t="n">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="N15" t="n">
-        <v>5.04</v>
+        <v>5.08</v>
       </c>
       <c r="O15" t="n">
-        <v>5.11</v>
+        <v>5.12</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1778,13 +1778,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1792,64 +1794,60 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.47</v>
+        <v>4.87</v>
       </c>
       <c r="C16" t="n">
-        <v>4.87</v>
+        <v>5.5</v>
       </c>
       <c r="D16" t="n">
-        <v>4.27</v>
+        <v>4.76</v>
       </c>
       <c r="E16" t="n">
-        <v>4.85</v>
+        <v>5.29</v>
       </c>
       <c r="F16" t="n">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.059</v>
+        <v>0.0905</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6</v>
+        <v>0.74</v>
       </c>
       <c r="I16" t="n">
-        <v>3.8</v>
+        <v>3.66</v>
       </c>
       <c r="J16" t="n">
-        <v>4.2</v>
+        <v>4.39</v>
       </c>
       <c r="K16" t="n">
-        <v>4.36</v>
+        <v>4.55</v>
       </c>
       <c r="L16" t="n">
-        <v>4.52</v>
+        <v>4.71</v>
       </c>
       <c r="M16" t="n">
-        <v>4.8</v>
+        <v>5.15</v>
       </c>
       <c r="N16" t="n">
-        <v>5.08</v>
+        <v>5.59</v>
       </c>
       <c r="O16" t="n">
-        <v>5.12</v>
+        <v>5.47</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1857,28 +1855,28 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1888,81 +1886,83 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.87</v>
+        <v>5.1</v>
       </c>
       <c r="C17" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="D17" t="n">
-        <v>4.76</v>
+        <v>4.07</v>
       </c>
       <c r="E17" t="n">
-        <v>5.29</v>
+        <v>4.11</v>
       </c>
       <c r="F17" t="n">
-        <v>0.44</v>
+        <v>-1.18</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0905</v>
+        <v>-0.2223</v>
       </c>
       <c r="H17" t="n">
-        <v>0.74</v>
+        <v>1.14</v>
       </c>
       <c r="I17" t="n">
-        <v>3.66</v>
+        <v>4.02</v>
       </c>
       <c r="J17" t="n">
-        <v>4.39</v>
+        <v>4.63</v>
       </c>
       <c r="K17" t="n">
-        <v>4.55</v>
+        <v>4.92</v>
       </c>
       <c r="L17" t="n">
-        <v>4.71</v>
+        <v>5.21</v>
       </c>
       <c r="M17" t="n">
-        <v>5.15</v>
+        <v>5.66</v>
       </c>
       <c r="N17" t="n">
-        <v>5.59</v>
+        <v>6.11</v>
       </c>
       <c r="O17" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
+        <v>6.23</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
       </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V17" s="8" t="n">
+        <v/>
       </c>
       <c r="W17" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr"/>
@@ -1970,69 +1970,63 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.1</v>
+        <v>4.17</v>
       </c>
       <c r="C18" t="n">
-        <v>5.2</v>
+        <v>4.22</v>
       </c>
       <c r="D18" t="n">
-        <v>4.07</v>
+        <v>3.84</v>
       </c>
       <c r="E18" t="n">
-        <v>4.11</v>
+        <v>3.98</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.18</v>
+        <v>-0.13</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.2223</v>
+        <v>-0.0314</v>
       </c>
       <c r="H18" t="n">
-        <v>1.14</v>
+        <v>0.38</v>
       </c>
       <c r="I18" t="n">
-        <v>4.02</v>
+        <v>2.93</v>
       </c>
       <c r="J18" t="n">
-        <v>4.63</v>
+        <v>2.71</v>
       </c>
       <c r="K18" t="n">
-        <v>4.92</v>
+        <v>3.54</v>
       </c>
       <c r="L18" t="n">
-        <v>5.21</v>
+        <v>4.37</v>
       </c>
       <c r="M18" t="n">
-        <v>5.66</v>
+        <v>4.68</v>
       </c>
       <c r="N18" t="n">
-        <v>6.11</v>
+        <v>4.99</v>
       </c>
       <c r="O18" t="n">
-        <v>6.23</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>6.34</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2044,7 +2038,7 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2054,50 +2048,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B19" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.0959</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="L19" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="M19" t="n">
         <v>4.17</v>
       </c>
-      <c r="C19" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="D19" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="E19" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>-0.0314</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="L19" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="M19" t="n">
-        <v>4.68</v>
-      </c>
       <c r="N19" t="n">
-        <v>4.99</v>
+        <v>4.34</v>
       </c>
       <c r="O19" t="n">
-        <v>6.34</v>
+        <v>4.6</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2110,103 +2104,111 @@
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.08</v>
+        <v>4.45</v>
       </c>
       <c r="C20" t="n">
-        <v>4.59</v>
+        <v>4.72</v>
       </c>
       <c r="D20" t="n">
-        <v>3.8</v>
+        <v>3.56</v>
       </c>
       <c r="E20" t="n">
-        <v>4.37</v>
+        <v>3.62</v>
       </c>
       <c r="F20" t="n">
-        <v>0.38</v>
+        <v>-0.75</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0959</v>
+        <v>-0.1713</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8</v>
+        <v>1.16</v>
       </c>
       <c r="I20" t="n">
-        <v>3.46</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>3.58</v>
+        <v>3.66</v>
       </c>
       <c r="K20" t="n">
-        <v>3.79</v>
+        <v>3.97</v>
       </c>
       <c r="L20" t="n">
-        <v>4.01</v>
+        <v>4.28</v>
       </c>
       <c r="M20" t="n">
-        <v>4.17</v>
+        <v>4.76</v>
       </c>
       <c r="N20" t="n">
-        <v>4.34</v>
+        <v>5.25</v>
       </c>
       <c r="O20" t="n">
-        <v>4.6</v>
+        <v>5.39</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
       <c r="W20" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -2218,65 +2220,63 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4.45</v>
+        <v>3.51</v>
       </c>
       <c r="C21" t="n">
-        <v>4.72</v>
+        <v>3.63</v>
       </c>
       <c r="D21" t="n">
-        <v>3.56</v>
+        <v>3.13</v>
       </c>
       <c r="E21" t="n">
-        <v>3.62</v>
+        <v>3.17</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.75</v>
+        <v>-0.45</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.1713</v>
+        <v>-0.1241</v>
       </c>
       <c r="H21" t="n">
-        <v>1.16</v>
+        <v>0.5</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J21" t="n">
-        <v>3.66</v>
+        <v>2.2</v>
       </c>
       <c r="K21" t="n">
-        <v>3.97</v>
+        <v>3.04</v>
       </c>
       <c r="L21" t="n">
-        <v>4.28</v>
+        <v>3.88</v>
       </c>
       <c r="M21" t="n">
-        <v>4.76</v>
+        <v>4.2</v>
       </c>
       <c r="N21" t="n">
-        <v>5.25</v>
+        <v>4.51</v>
       </c>
       <c r="O21" t="n">
-        <v>5.39</v>
+        <v>5.88</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
+      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2290,64 +2290,60 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.51</v>
+        <v>3.29</v>
       </c>
       <c r="C22" t="n">
-        <v>3.63</v>
+        <v>3.5</v>
       </c>
       <c r="D22" t="n">
-        <v>3.13</v>
+        <v>3.01</v>
       </c>
       <c r="E22" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.45</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.1241</v>
+        <v>-0.0208</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="I22" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="J22" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="K22" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="L22" t="n">
-        <v>3.88</v>
+        <v>3.28</v>
       </c>
       <c r="M22" t="n">
-        <v>4.2</v>
+        <v>3.42</v>
       </c>
       <c r="N22" t="n">
-        <v>4.51</v>
+        <v>3.57</v>
       </c>
       <c r="O22" t="n">
-        <v>5.88</v>
+        <v>4.14</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2355,18 +2351,18 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2374,7 +2370,7 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2384,50 +2380,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="C23" t="n">
-        <v>3.5</v>
+        <v>5.65</v>
       </c>
       <c r="D23" t="n">
-        <v>3.01</v>
+        <v>3.38</v>
       </c>
       <c r="E23" t="n">
-        <v>3.1</v>
+        <v>5.28</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.07000000000000001</v>
+        <v>2.17</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.7</v>
       </c>
       <c r="H23" t="n">
-        <v>0.49</v>
+        <v>2.27</v>
       </c>
       <c r="I23" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="J23" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="K23" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="L23" t="n">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="M23" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>3.57</v>
+        <v>3.52</v>
       </c>
       <c r="O23" t="n">
-        <v>4.14</v>
+        <v>3.99</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2440,7 +2436,7 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
@@ -2448,15 +2444,19 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V23" s="8" t="n">
-        <v/>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
@@ -2464,50 +2464,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.5</v>
+        <v>5.79</v>
       </c>
       <c r="C24" t="n">
-        <v>5.65</v>
+        <v>7.83</v>
       </c>
       <c r="D24" t="n">
-        <v>3.38</v>
+        <v>3.73</v>
       </c>
       <c r="E24" t="n">
-        <v>5.28</v>
+        <v>4.35</v>
       </c>
       <c r="F24" t="n">
-        <v>2.17</v>
+        <v>-0.92</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.7</v>
+        <v>-0.1746</v>
       </c>
       <c r="H24" t="n">
-        <v>2.27</v>
+        <v>4.1</v>
       </c>
       <c r="I24" t="n">
-        <v>2.51</v>
+        <v>1.11</v>
       </c>
       <c r="J24" t="n">
-        <v>2.54</v>
+        <v>3.39</v>
       </c>
       <c r="K24" t="n">
-        <v>2.86</v>
+        <v>4.14</v>
       </c>
       <c r="L24" t="n">
-        <v>3.18</v>
+        <v>4.9</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>6.41</v>
       </c>
       <c r="N24" t="n">
-        <v>3.52</v>
+        <v>7.93</v>
       </c>
       <c r="O24" t="n">
-        <v>3.99</v>
+        <v>7.92</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2515,12 +2515,14 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
@@ -2528,70 +2530,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.79</v>
+        <v>3.71</v>
       </c>
       <c r="C25" t="n">
-        <v>7.83</v>
+        <v>3.74</v>
       </c>
       <c r="D25" t="n">
-        <v>3.73</v>
+        <v>3.15</v>
       </c>
       <c r="E25" t="n">
-        <v>4.35</v>
+        <v>3.42</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.92</v>
+        <v>-0.93</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.1746</v>
+        <v>-0.2141</v>
       </c>
       <c r="H25" t="n">
-        <v>4.1</v>
+        <v>0.58</v>
       </c>
       <c r="I25" t="n">
-        <v>1.11</v>
+        <v>-0.37</v>
       </c>
       <c r="J25" t="n">
-        <v>3.39</v>
+        <v>-0.46</v>
       </c>
       <c r="K25" t="n">
-        <v>4.14</v>
+        <v>2.3</v>
       </c>
       <c r="L25" t="n">
-        <v>4.9</v>
+        <v>5.07</v>
       </c>
       <c r="M25" t="n">
-        <v>6.41</v>
+        <v>6.4</v>
       </c>
       <c r="N25" t="n">
-        <v>7.93</v>
+        <v>7.74</v>
       </c>
       <c r="O25" t="n">
-        <v>7.92</v>
+        <v>11.93</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2604,15 +2606,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S25" s="7" t="inlineStr">
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2620,64 +2620,64 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>-0.0523</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="L26" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="M26" t="n">
         <v>3.71</v>
       </c>
-      <c r="C26" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="D26" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="E26" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-0.93</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>-0.2141</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I26" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="J26" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="K26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="L26" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="M26" t="n">
-        <v>6.4</v>
-      </c>
       <c r="N26" t="n">
-        <v>7.74</v>
+        <v>3.99</v>
       </c>
       <c r="O26" t="n">
-        <v>11.93</v>
+        <v>4.32</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2690,7 +2690,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S26" s="7" t="inlineStr">
+      <c r="S26" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2704,7 +2704,7 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2718,63 +2718,65 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="C27" t="n">
-        <v>3.32</v>
+        <v>3.17</v>
       </c>
       <c r="D27" t="n">
-        <v>3.06</v>
+        <v>2.92</v>
       </c>
       <c r="E27" t="n">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.18</v>
+        <v>-0.2</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0523</v>
+        <v>-0.0604</v>
       </c>
       <c r="H27" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="I27" t="n">
-        <v>2.57</v>
+        <v>2.79</v>
       </c>
       <c r="J27" t="n">
-        <v>2.83</v>
+        <v>3.01</v>
       </c>
       <c r="K27" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="L27" t="n">
-        <v>3.43</v>
+        <v>3.21</v>
       </c>
       <c r="M27" t="n">
-        <v>3.71</v>
+        <v>3.37</v>
       </c>
       <c r="N27" t="n">
-        <v>3.99</v>
+        <v>3.53</v>
       </c>
       <c r="O27" t="n">
-        <v>4.32</v>
+        <v>3.58</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2788,7 +2790,7 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2802,50 +2804,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B28" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-0.0617</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="L28" t="n">
         <v>3.05</v>
       </c>
-      <c r="C28" t="n">
+      <c r="M28" t="n">
         <v>3.17</v>
       </c>
-      <c r="D28" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="E28" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="F28" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>-0.0604</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I28" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="J28" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="K28" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="L28" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="M28" t="n">
-        <v>3.37</v>
-      </c>
       <c r="N28" t="n">
-        <v>3.53</v>
+        <v>3.3</v>
       </c>
       <c r="O28" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2860,13 +2862,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T28" s="8" t="n">
-        <v/>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2874,152 +2878,146 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3.24</v>
+        <v>2.93</v>
       </c>
       <c r="C29" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="D29" t="n">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="E29" t="n">
-        <v>2.86</v>
+        <v>3.19</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.19</v>
+        <v>0.33</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0617</v>
+        <v>0.1144</v>
       </c>
       <c r="H29" t="n">
-        <v>0.48</v>
+        <v>0.41</v>
       </c>
       <c r="I29" t="n">
-        <v>2.67</v>
+        <v>2.3</v>
       </c>
       <c r="J29" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="K29" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="L29" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="M29" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="N29" t="n">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="O29" t="n">
-        <v>3.42</v>
+        <v>3.73</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="C30" t="n">
-        <v>3.28</v>
+        <v>3.49</v>
       </c>
       <c r="D30" t="n">
-        <v>2.87</v>
+        <v>2.96</v>
       </c>
       <c r="E30" t="n">
-        <v>3.19</v>
+        <v>3.13</v>
       </c>
       <c r="F30" t="n">
-        <v>0.33</v>
+        <v>-0.06</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.1144</v>
+        <v>-0.0173</v>
       </c>
       <c r="H30" t="n">
-        <v>0.41</v>
+        <v>0.53</v>
       </c>
       <c r="I30" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="J30" t="n">
-        <v>2.3</v>
+        <v>2.83</v>
       </c>
       <c r="K30" t="n">
-        <v>2.62</v>
+        <v>2.98</v>
       </c>
       <c r="L30" t="n">
-        <v>2.94</v>
+        <v>3.13</v>
       </c>
       <c r="M30" t="n">
-        <v>3.1</v>
+        <v>3.39</v>
       </c>
       <c r="N30" t="n">
-        <v>3.26</v>
+        <v>3.66</v>
       </c>
       <c r="O30" t="n">
-        <v>3.73</v>
+        <v>3.69</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3027,12 +3025,14 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
@@ -3040,68 +3040,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="C31" t="n">
-        <v>3.49</v>
+        <v>3.27</v>
       </c>
       <c r="D31" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="E31" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0173</v>
+        <v>-0.0115</v>
       </c>
       <c r="H31" t="n">
-        <v>0.53</v>
+        <v>0.35</v>
       </c>
       <c r="I31" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="J31" t="n">
-        <v>2.83</v>
+        <v>2.55</v>
       </c>
       <c r="K31" t="n">
-        <v>2.98</v>
+        <v>2.86</v>
       </c>
       <c r="L31" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="M31" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="N31" t="n">
-        <v>3.66</v>
+        <v>3.62</v>
       </c>
       <c r="O31" t="n">
-        <v>3.69</v>
+        <v>4.03</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3109,20 +3111,16 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R31" s="6" t="n">
+        <v/>
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3130,75 +3128,77 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3.18</v>
+        <v>3.11</v>
       </c>
       <c r="C32" t="n">
-        <v>3.27</v>
+        <v>3.15</v>
       </c>
       <c r="D32" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="E32" t="n">
         <v>3.1</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0115</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="I32" t="n">
-        <v>2.43</v>
+        <v>2.58</v>
       </c>
       <c r="J32" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="K32" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="L32" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="M32" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="N32" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="O32" t="n">
         <v>3.62</v>
       </c>
-      <c r="O32" t="n">
-        <v>4.03</v>
-      </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3212,79 +3212,81 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3.11</v>
+        <v>3.06</v>
       </c>
       <c r="C33" t="n">
-        <v>3.15</v>
+        <v>3.06</v>
       </c>
       <c r="D33" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="E33" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0</v>
+        <v>-0.0953</v>
       </c>
       <c r="H33" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="I33" t="n">
         <v>2.58</v>
       </c>
       <c r="J33" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="K33" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="L33" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="M33" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="N33" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="O33" t="n">
         <v>3.44</v>
       </c>
-      <c r="O33" t="n">
-        <v>3.62</v>
-      </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3298,77 +3300,71 @@
       </c>
       <c r="W33" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3.06</v>
+        <v>2.84</v>
       </c>
       <c r="C34" t="n">
-        <v>3.06</v>
+        <v>2.89</v>
       </c>
       <c r="D34" t="n">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
       <c r="E34" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.3</v>
+        <v>-0.15</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0953</v>
+        <v>-0.0543</v>
       </c>
       <c r="H34" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="I34" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="J34" t="n">
-        <v>2.85</v>
+        <v>2.46</v>
       </c>
       <c r="K34" t="n">
-        <v>2.95</v>
+        <v>2.66</v>
       </c>
       <c r="L34" t="n">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="M34" t="n">
-        <v>3.24</v>
+        <v>2.94</v>
       </c>
       <c r="N34" t="n">
-        <v>3.43</v>
+        <v>3.02</v>
       </c>
       <c r="O34" t="n">
-        <v>3.44</v>
+        <v>3.33</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
+      <c r="S34" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3382,7 +3378,7 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3392,50 +3388,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.84</v>
+        <v>2.69</v>
       </c>
       <c r="C35" t="n">
-        <v>2.89</v>
+        <v>2.72</v>
       </c>
       <c r="D35" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="E35" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.15</v>
+        <v>0.03</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0543</v>
+        <v>0.0098</v>
       </c>
       <c r="H35" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="I35" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="J35" t="n">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="K35" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="L35" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="M35" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="N35" t="n">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="O35" t="n">
-        <v>3.33</v>
+        <v>3.15</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3443,14 +3439,12 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3462,77 +3456,87 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>2.69</v>
       </c>
       <c r="C36" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="D36" t="n">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="E36" t="n">
-        <v>2.67</v>
+        <v>2.52</v>
       </c>
       <c r="F36" t="n">
-        <v>0.03</v>
+        <v>-0.15</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0098</v>
+        <v>-0.0565</v>
       </c>
       <c r="H36" t="n">
-        <v>0.16</v>
+        <v>0.27</v>
       </c>
       <c r="I36" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="J36" t="n">
-        <v>2.33</v>
+        <v>2.53</v>
       </c>
       <c r="K36" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="L36" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="M36" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="N36" t="n">
         <v>2.85</v>
       </c>
       <c r="O36" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3540,7 +3544,7 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3554,83 +3558,81 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.69</v>
+        <v>2.51</v>
       </c>
       <c r="C37" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="D37" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="E37" t="n">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.15</v>
+        <v>0.26</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0565</v>
+        <v>0.1019</v>
       </c>
       <c r="H37" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="I37" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="J37" t="n">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="K37" t="n">
-        <v>2.59</v>
+        <v>2.39</v>
       </c>
       <c r="L37" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="M37" t="n">
         <v>2.66</v>
       </c>
-      <c r="M37" t="n">
-        <v>2.75</v>
-      </c>
       <c r="N37" t="n">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="O37" t="n">
-        <v>2.88</v>
+        <v>3.03</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -3642,50 +3644,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B38" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C38" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>-0.0083</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J38" t="n">
         <v>2.51</v>
       </c>
-      <c r="C38" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="D38" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="E38" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="G38" s="5" t="n">
-        <v>0.1019</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I38" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="J38" t="n">
-        <v>2.2</v>
-      </c>
       <c r="K38" t="n">
-        <v>2.39</v>
+        <v>2.61</v>
       </c>
       <c r="L38" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="M38" t="n">
-        <v>2.66</v>
+        <v>2.95</v>
       </c>
       <c r="N38" t="n">
-        <v>2.74</v>
+        <v>3.18</v>
       </c>
       <c r="O38" t="n">
-        <v>3.03</v>
+        <v>3.16</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3696,25 +3698,21 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3728,50 +3726,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="C39" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="D39" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="E39" t="n">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.02</v>
+        <v>0.2</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0083</v>
+        <v>0.0736</v>
       </c>
       <c r="H39" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="I39" t="n">
-        <v>2.14</v>
+        <v>2.47</v>
       </c>
       <c r="J39" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="K39" t="n">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="L39" t="n">
-        <v>2.72</v>
+        <v>2.77</v>
       </c>
       <c r="M39" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N39" t="n">
         <v>2.95</v>
       </c>
-      <c r="N39" t="n">
-        <v>3.18</v>
-      </c>
       <c r="O39" t="n">
-        <v>3.16</v>
+        <v>3.09</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3782,78 +3780,78 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="C40" t="n">
-        <v>2.98</v>
+        <v>3.14</v>
       </c>
       <c r="D40" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="E40" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2</v>
+        <v>-0.05</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0736</v>
+        <v>-0.0179</v>
       </c>
       <c r="H40" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="I40" t="n">
-        <v>2.47</v>
+        <v>2.52</v>
       </c>
       <c r="J40" t="n">
-        <v>2.54</v>
+        <v>2.78</v>
       </c>
       <c r="K40" t="n">
-        <v>2.65</v>
+        <v>2.84</v>
       </c>
       <c r="L40" t="n">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="M40" t="n">
-        <v>2.86</v>
+        <v>3.08</v>
       </c>
       <c r="N40" t="n">
-        <v>2.95</v>
+        <v>3.24</v>
       </c>
       <c r="O40" t="n">
-        <v>3.09</v>
+        <v>3.21</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3866,7 +3864,7 @@
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
@@ -3874,68 +3872,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U40" s="8" t="n">
+        <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="C41" t="n">
-        <v>3.14</v>
+        <v>3.39</v>
       </c>
       <c r="D41" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="E41" t="n">
-        <v>2.91</v>
+        <v>3.29</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.05</v>
+        <v>0.38</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.1318</v>
       </c>
       <c r="H41" t="n">
-        <v>0.25</v>
+        <v>0.53</v>
       </c>
       <c r="I41" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="J41" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K41" t="n">
         <v>2.78</v>
       </c>
-      <c r="K41" t="n">
-        <v>2.84</v>
-      </c>
       <c r="L41" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="M41" t="n">
-        <v>3.08</v>
+        <v>3.03</v>
       </c>
       <c r="N41" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="O41" t="n">
-        <v>3.21</v>
+        <v>3.39</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
@@ -3956,13 +3956,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3976,50 +3980,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.9</v>
+        <v>3.34</v>
       </c>
       <c r="C42" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="D42" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="E42" t="n">
-        <v>3.29</v>
+        <v>3.23</v>
       </c>
       <c r="F42" t="n">
-        <v>0.38</v>
+        <v>-0.06</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.1318</v>
+        <v>-0.0185</v>
       </c>
       <c r="H42" t="n">
-        <v>0.53</v>
+        <v>0.3</v>
       </c>
       <c r="I42" t="n">
-        <v>2.64</v>
+        <v>2.33</v>
       </c>
       <c r="J42" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="K42" t="n">
-        <v>2.78</v>
+        <v>3.02</v>
       </c>
       <c r="L42" t="n">
-        <v>2.96</v>
+        <v>3.21</v>
       </c>
       <c r="M42" t="n">
-        <v>3.03</v>
+        <v>3.56</v>
       </c>
       <c r="N42" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="O42" t="n">
-        <v>3.39</v>
+        <v>3.92</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4030,27 +4034,21 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4064,50 +4062,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3.34</v>
+        <v>3.18</v>
       </c>
       <c r="C43" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="D43" t="n">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="E43" t="n">
-        <v>3.23</v>
+        <v>3.12</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.06</v>
+        <v>-0.11</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0185</v>
+        <v>-0.0338</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
       <c r="I43" t="n">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="J43" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="K43" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="L43" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="M43" t="n">
-        <v>3.56</v>
+        <v>3.38</v>
       </c>
       <c r="N43" t="n">
-        <v>3.9</v>
+        <v>3.52</v>
       </c>
       <c r="O43" t="n">
-        <v>3.92</v>
+        <v>3.69</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4115,12 +4113,14 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4132,64 +4132,64 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="C44" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="D44" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="E44" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.11</v>
+        <v>0.08</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0338</v>
+        <v>0.025</v>
       </c>
       <c r="H44" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="I44" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="J44" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="K44" t="n">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="L44" t="n">
-        <v>3.24</v>
+        <v>3.13</v>
       </c>
       <c r="M44" t="n">
-        <v>3.38</v>
+        <v>3.23</v>
       </c>
       <c r="N44" t="n">
-        <v>3.52</v>
+        <v>3.33</v>
       </c>
       <c r="O44" t="n">
-        <v>3.69</v>
+        <v>3.47</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4197,83 +4197,83 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3.09</v>
+        <v>3.28</v>
       </c>
       <c r="C45" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="D45" t="n">
-        <v>3.02</v>
+        <v>3.14</v>
       </c>
       <c r="E45" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="F45" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.025</v>
+        <v>0.0103</v>
       </c>
       <c r="H45" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="I45" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="J45" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="K45" t="n">
-        <v>3.01</v>
+        <v>3.06</v>
       </c>
       <c r="L45" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="M45" t="n">
-        <v>3.23</v>
+        <v>3.34</v>
       </c>
       <c r="N45" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="O45" t="n">
-        <v>3.47</v>
+        <v>3.58</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4284,14 +4284,14 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U45" s="8" t="n">
@@ -4300,64 +4300,60 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>3.28</v>
       </c>
       <c r="C46" t="n">
-        <v>3.44</v>
+        <v>3.33</v>
       </c>
       <c r="D46" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="E46" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="F46" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0103</v>
+        <v>0.0043</v>
       </c>
       <c r="H46" t="n">
-        <v>0.31</v>
+        <v>0.18</v>
       </c>
       <c r="I46" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="J46" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="K46" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="L46" t="n">
-        <v>3.18</v>
+        <v>3.26</v>
       </c>
       <c r="M46" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="N46" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="O46" t="n">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4370,13 +4366,11 @@
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4384,77 +4378,89 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="C47" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>-0.094</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="J47" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="K47" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="L47" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="M47" t="n">
         <v>3.33</v>
       </c>
-      <c r="D47" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="E47" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>0.0043</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="I47" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="J47" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K47" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="L47" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="M47" t="n">
-        <v>3.38</v>
-      </c>
       <c r="N47" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="O47" t="n">
         <v>3.51</v>
       </c>
-      <c r="O47" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4464,7 +4470,7 @@
       </c>
       <c r="W47" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
@@ -4476,75 +4482,67 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3.21</v>
+        <v>2.93</v>
       </c>
       <c r="C48" t="n">
-        <v>3.36</v>
+        <v>2.97</v>
       </c>
       <c r="D48" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="E48" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.3</v>
+        <v>-0.03</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.094</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>0.48</v>
+        <v>0.14</v>
       </c>
       <c r="I48" t="n">
-        <v>2.97</v>
+        <v>2.39</v>
       </c>
       <c r="J48" t="n">
-        <v>3.07</v>
+        <v>2.37</v>
       </c>
       <c r="K48" t="n">
-        <v>3.16</v>
+        <v>2.7</v>
       </c>
       <c r="L48" t="n">
-        <v>3.24</v>
+        <v>3.03</v>
       </c>
       <c r="M48" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="N48" t="n">
         <v>3.33</v>
       </c>
-      <c r="N48" t="n">
-        <v>3.42</v>
-      </c>
       <c r="O48" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3.84</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4552,64 +4550,60 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="C49" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="D49" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="E49" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-0.0137</v>
       </c>
       <c r="H49" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="I49" t="n">
-        <v>2.39</v>
+        <v>2.68</v>
       </c>
       <c r="J49" t="n">
-        <v>2.37</v>
+        <v>2.77</v>
       </c>
       <c r="K49" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="L49" t="n">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="M49" t="n">
-        <v>3.18</v>
+        <v>2.98</v>
       </c>
       <c r="N49" t="n">
-        <v>3.33</v>
+        <v>3.06</v>
       </c>
       <c r="O49" t="n">
-        <v>3.84</v>
+        <v>3.11</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4617,16 +4611,20 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T49" s="8" t="n">
-        <v/>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4634,81 +4632,87 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="C50" t="n">
-        <v>2.99</v>
+        <v>2.84</v>
       </c>
       <c r="D50" t="n">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="E50" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.04</v>
+        <v>-0.12</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0432</v>
       </c>
       <c r="H50" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="I50" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="J50" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="K50" t="n">
-        <v>2.84</v>
+        <v>2.79</v>
       </c>
       <c r="L50" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="M50" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="N50" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="O50" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
+        <v>3.15</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4716,81 +4720,73 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="C51" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="D51" t="n">
         <v>2.62</v>
       </c>
       <c r="E51" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.12</v>
+        <v>-0.09</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0432</v>
+        <v>-0.0309</v>
       </c>
       <c r="H51" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="I51" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="J51" t="n">
-        <v>2.69</v>
+        <v>2.54</v>
       </c>
       <c r="K51" t="n">
-        <v>2.79</v>
+        <v>2.64</v>
       </c>
       <c r="L51" t="n">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="M51" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="N51" t="n">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="O51" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3.05</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v/>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S51" s="7" t="inlineStr">
+      <c r="S51" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4804,7 +4800,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4814,50 +4810,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="C52" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="D52" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="E52" t="n">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0309</v>
+        <v>0.0267</v>
       </c>
       <c r="H52" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="I52" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="J52" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="K52" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="L52" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="M52" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="N52" t="n">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="O52" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4865,79 +4861,83 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
       <c r="U52" s="8" t="n">
         <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="W52" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="C53" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="D53" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="E53" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="F53" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0267</v>
+        <v>0.0146</v>
       </c>
       <c r="H53" t="n">
-        <v>0.13</v>
+        <v>0.24</v>
       </c>
       <c r="I53" t="n">
-        <v>2.42</v>
+        <v>2.57</v>
       </c>
       <c r="J53" t="n">
-        <v>2.44</v>
+        <v>2.59</v>
       </c>
       <c r="K53" t="n">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="L53" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="M53" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="N53" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="O53" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4945,83 +4945,87 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T53" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="C54" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="D54" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="E54" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="F54" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0146</v>
+        <v>0.0415</v>
       </c>
       <c r="H54" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="I54" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="J54" t="n">
-        <v>2.59</v>
+        <v>2.54</v>
       </c>
       <c r="K54" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="L54" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="M54" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="N54" t="n">
-        <v>2.84</v>
+        <v>3.02</v>
       </c>
       <c r="O54" t="n">
-        <v>2.96</v>
+        <v>3.11</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5029,87 +5033,83 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="C55" t="n">
-        <v>2.94</v>
+        <v>3.03</v>
       </c>
       <c r="D55" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="E55" t="n">
-        <v>2.89</v>
+        <v>2.97</v>
       </c>
       <c r="F55" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0415</v>
+        <v>0.0301</v>
       </c>
       <c r="H55" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="I55" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="J55" t="n">
-        <v>2.54</v>
+        <v>2.67</v>
       </c>
       <c r="K55" t="n">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="L55" t="n">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="M55" t="n">
-        <v>2.89</v>
+        <v>3.01</v>
       </c>
       <c r="N55" t="n">
-        <v>3.02</v>
+        <v>3.17</v>
       </c>
       <c r="O55" t="n">
-        <v>3.11</v>
+        <v>3.19</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5120,7 +5120,7 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="10" t="inlineStr">
+      <c r="S55" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5136,7 +5136,7 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5150,69 +5150,71 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B56" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="C56" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>-0.0484</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I56" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J56" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K56" t="n">
         <v>2.88</v>
       </c>
-      <c r="C56" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="D56" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="E56" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>0.0301</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="I56" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="J56" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="K56" t="n">
-        <v>2.76</v>
-      </c>
       <c r="L56" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="M56" t="n">
-        <v>3.01</v>
+        <v>3.07</v>
       </c>
       <c r="N56" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="O56" t="n">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5220,178 +5222,92 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="C57" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="D57" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="E57" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.14</v>
+        <v>0.08</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0484</v>
+        <v>0.0286</v>
       </c>
       <c r="H57" t="n">
-        <v>0.26</v>
+        <v>0.13</v>
       </c>
       <c r="I57" t="n">
-        <v>2.64</v>
+        <v>2.49</v>
       </c>
       <c r="J57" t="n">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="K57" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="L57" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="M57" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N57" t="n">
         <v>3.07</v>
       </c>
-      <c r="N57" t="n">
-        <v>3.19</v>
-      </c>
       <c r="O57" t="n">
-        <v>3.22</v>
+        <v>3.27</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="C58" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="D58" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E58" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0078</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I58" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="J58" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K58" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L58" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="M58" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="N58" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="O58" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>中警訊</t>
         </is>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5313,6 +5313,86 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="C58" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E58" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.0288</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="L58" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="M58" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="O58" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -659,13 +659,13 @@
         <v>0.4</v>
       </c>
       <c r="I2" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="J2" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="K2" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="L2" t="n">
         <v>2.75</v>
@@ -674,10 +674,10 @@
         <v>2.81</v>
       </c>
       <c r="N2" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="O2" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5320,25 +5320,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="C58" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="D58" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="E58" t="n">
-        <v>2.83</v>
+        <v>3.04</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.08</v>
+        <v>0.13</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0288</v>
+        <v>0.0433</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="I58" t="n">
         <v>2.71</v>
@@ -5369,20 +5369,24 @@
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
       <c r="V58" s="8" t="n">
         <v/>
       </c>
@@ -5391,7 +5395,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -5323,22 +5323,22 @@
         <v>2.9</v>
       </c>
       <c r="C58" t="n">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="D58" t="n">
         <v>2.82</v>
       </c>
       <c r="E58" t="n">
-        <v>3.04</v>
+        <v>3.09</v>
       </c>
       <c r="F58" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0433</v>
+        <v>0.0594</v>
       </c>
       <c r="H58" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="I58" t="n">
         <v>2.71</v>
@@ -5384,20 +5384,22 @@
       </c>
       <c r="U58" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V58" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -5323,22 +5323,22 @@
         <v>2.9</v>
       </c>
       <c r="C58" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="D58" t="n">
         <v>2.82</v>
       </c>
       <c r="E58" t="n">
-        <v>3.09</v>
+        <v>3.16</v>
       </c>
       <c r="F58" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0594</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>0.27</v>
+        <v>0.35</v>
       </c>
       <c r="I58" t="n">
         <v>2.71</v>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>0.4</v>
       </c>
       <c r="I2" t="n">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="J2" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="K2" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="L2" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="M2" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="N2" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="O2" t="n">
-        <v>3.13</v>
+        <v>3.01</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -700,11 +700,13 @@
       </c>
       <c r="U2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -5323,22 +5325,22 @@
         <v>2.9</v>
       </c>
       <c r="C58" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="D58" t="n">
         <v>2.82</v>
       </c>
       <c r="E58" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="F58" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="I58" t="n">
         <v>2.71</v>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -5337,7 +5337,7 @@
         <v>0.26</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.09030000000000001</v>
+        <v>0.0896</v>
       </c>
       <c r="H58" t="n">
         <v>0.38</v>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -5334,10 +5334,10 @@
         <v>3.17</v>
       </c>
       <c r="F58" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0896</v>
+        <v>0.0872</v>
       </c>
       <c r="H58" t="n">
         <v>0.38</v>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -5331,13 +5331,13 @@
         <v>2.82</v>
       </c>
       <c r="E58" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="F58" t="n">
         <v>0.25</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0872</v>
+        <v>0.0852</v>
       </c>
       <c r="H58" t="n">
         <v>0.38</v>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -5325,22 +5325,22 @@
         <v>2.9</v>
       </c>
       <c r="C58" t="n">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="D58" t="n">
         <v>2.82</v>
       </c>
       <c r="E58" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="F58" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0852</v>
+        <v>0.0907</v>
       </c>
       <c r="H58" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="I58" t="n">
         <v>2.71</v>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -5325,22 +5325,22 @@
         <v>2.9</v>
       </c>
       <c r="C58" t="n">
-        <v>3.22</v>
+        <v>3.17</v>
       </c>
       <c r="D58" t="n">
         <v>2.82</v>
       </c>
       <c r="E58" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="F58" t="n">
         <v>0.26</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0907</v>
+        <v>0.0883</v>
       </c>
       <c r="H58" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="I58" t="n">
         <v>2.71</v>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -5325,22 +5325,22 @@
         <v>2.9</v>
       </c>
       <c r="C58" t="n">
-        <v>3.17</v>
+        <v>3.3</v>
       </c>
       <c r="D58" t="n">
         <v>2.82</v>
       </c>
       <c r="E58" t="n">
-        <v>3.17</v>
+        <v>3.28</v>
       </c>
       <c r="F58" t="n">
-        <v>0.26</v>
+        <v>0.37</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0883</v>
+        <v>0.1264</v>
       </c>
       <c r="H58" t="n">
-        <v>0.36</v>
+        <v>0.48</v>
       </c>
       <c r="I58" t="n">
         <v>2.71</v>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.64</v>
+        <v>2.97</v>
       </c>
       <c r="C2" t="n">
-        <v>3.02</v>
+        <v>3.13</v>
       </c>
       <c r="D2" t="n">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3</v>
+        <v>0.05</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.1108</v>
+        <v>0.017</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4</v>
+        <v>0.26</v>
       </c>
       <c r="I2" t="n">
-        <v>2.53</v>
+        <v>2.22</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="K2" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="L2" t="n">
-        <v>2.73</v>
+        <v>2.91</v>
       </c>
       <c r="M2" t="n">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="N2" t="n">
-        <v>2.82</v>
+        <v>3.49</v>
       </c>
       <c r="O2" t="n">
-        <v>3.01</v>
+        <v>3.42</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -690,82 +690,72 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.97</v>
+        <v>3.09</v>
       </c>
       <c r="C3" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="D3" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="E3" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05</v>
+        <v>-0.11</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.017</v>
+        <v>-0.0351</v>
       </c>
       <c r="H3" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="I3" t="n">
-        <v>2.22</v>
+        <v>2.61</v>
       </c>
       <c r="J3" t="n">
-        <v>2.68</v>
+        <v>2.81</v>
       </c>
       <c r="K3" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="L3" t="n">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="M3" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="N3" t="n">
-        <v>3.49</v>
+        <v>3.33</v>
       </c>
       <c r="O3" t="n">
-        <v>3.42</v>
+        <v>3.39</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -773,16 +763,20 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -795,55 +789,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="M4" t="n">
         <v>3.09</v>
       </c>
-      <c r="C4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>-0.0351</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="M4" t="n">
-        <v>3.18</v>
-      </c>
       <c r="N4" t="n">
-        <v>3.33</v>
+        <v>3.19</v>
       </c>
       <c r="O4" t="n">
-        <v>3.39</v>
+        <v>3.5</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -879,57 +877,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="C5" t="n">
-        <v>3.17</v>
+        <v>2.97</v>
       </c>
       <c r="D5" t="n">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="E5" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="F5" t="n">
         <v>-0.05</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.018</v>
+        <v>-0.0184</v>
       </c>
       <c r="H5" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="J5" t="n">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="K5" t="n">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="L5" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="M5" t="n">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
       <c r="N5" t="n">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="O5" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -947,10 +945,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -972,50 +968,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.91</v>
+        <v>3.15</v>
       </c>
       <c r="C6" t="n">
-        <v>2.97</v>
+        <v>3.59</v>
       </c>
       <c r="D6" t="n">
-        <v>2.77</v>
+        <v>3.13</v>
       </c>
       <c r="E6" t="n">
-        <v>2.84</v>
+        <v>3.32</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.05</v>
+        <v>0.49</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0184</v>
+        <v>0.1725</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="I6" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="J6" t="n">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
       <c r="K6" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="L6" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="M6" t="n">
-        <v>3.04</v>
+        <v>2.93</v>
       </c>
       <c r="N6" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="O6" t="n">
-        <v>3.48</v>
+        <v>3.16</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1023,83 +1019,83 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v/>
-      </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="C7" t="n">
-        <v>3.59</v>
+        <v>3.55</v>
       </c>
       <c r="D7" t="n">
-        <v>3.13</v>
+        <v>3.09</v>
       </c>
       <c r="E7" t="n">
-        <v>3.32</v>
+        <v>3.11</v>
       </c>
       <c r="F7" t="n">
-        <v>0.49</v>
+        <v>-0.22</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.1725</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="I7" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="J7" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="K7" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="L7" t="n">
-        <v>2.85</v>
+        <v>3.34</v>
       </c>
       <c r="M7" t="n">
-        <v>2.93</v>
+        <v>3.55</v>
       </c>
       <c r="N7" t="n">
-        <v>3.01</v>
+        <v>3.76</v>
       </c>
       <c r="O7" t="n">
-        <v>3.16</v>
+        <v>4.04</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1107,12 +1103,14 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
@@ -1120,70 +1118,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="C8" t="n">
-        <v>3.55</v>
+        <v>3.14</v>
       </c>
       <c r="D8" t="n">
-        <v>3.09</v>
+        <v>2.89</v>
       </c>
       <c r="E8" t="n">
-        <v>3.11</v>
+        <v>3.01</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.22</v>
+        <v>-0.1</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.0316</v>
       </c>
       <c r="H8" t="n">
-        <v>0.46</v>
+        <v>0.25</v>
       </c>
       <c r="I8" t="n">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="J8" t="n">
-        <v>2.85</v>
+        <v>2.54</v>
       </c>
       <c r="K8" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="L8" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="M8" t="n">
         <v>3.34</v>
       </c>
-      <c r="M8" t="n">
-        <v>3.55</v>
-      </c>
       <c r="N8" t="n">
-        <v>3.76</v>
+        <v>3.46</v>
       </c>
       <c r="O8" t="n">
-        <v>4.04</v>
+        <v>4.01</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1201,10 +1199,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1226,50 +1222,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="C9" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="D9" t="n">
         <v>3.14</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0.0984</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K9" t="n">
         <v>2.89</v>
       </c>
-      <c r="E9" t="n">
+      <c r="L9" t="n">
         <v>3.01</v>
       </c>
-      <c r="F9" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>-0.0316</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="L9" t="n">
-        <v>3.21</v>
-      </c>
       <c r="M9" t="n">
-        <v>3.34</v>
+        <v>3.13</v>
       </c>
       <c r="N9" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
-        <v>4.01</v>
+        <v>3.38</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1277,83 +1273,83 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V9" s="8" t="n">
-        <v/>
+      <c r="V9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.16</v>
+        <v>3.41</v>
       </c>
       <c r="C10" t="n">
-        <v>3.57</v>
+        <v>4.16</v>
       </c>
       <c r="D10" t="n">
-        <v>3.14</v>
+        <v>3.19</v>
       </c>
       <c r="E10" t="n">
-        <v>3.3</v>
+        <v>4.12</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3</v>
+        <v>0.82</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0984</v>
+        <v>0.2482</v>
       </c>
       <c r="H10" t="n">
-        <v>0.44</v>
+        <v>0.96</v>
       </c>
       <c r="I10" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="J10" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="K10" t="n">
-        <v>2.89</v>
+        <v>3.09</v>
       </c>
       <c r="L10" t="n">
-        <v>3.01</v>
+        <v>3.33</v>
       </c>
       <c r="M10" t="n">
-        <v>3.13</v>
+        <v>3.52</v>
       </c>
       <c r="N10" t="n">
-        <v>3.25</v>
+        <v>3.71</v>
       </c>
       <c r="O10" t="n">
-        <v>3.38</v>
+        <v>4.01</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1376,12 +1372,12 @@
       </c>
       <c r="U10" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W10" s="9" t="inlineStr">
@@ -1394,50 +1390,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.41</v>
+        <v>4.16</v>
       </c>
       <c r="C11" t="n">
-        <v>4.16</v>
+        <v>4.42</v>
       </c>
       <c r="D11" t="n">
-        <v>3.19</v>
+        <v>4.09</v>
       </c>
       <c r="E11" t="n">
-        <v>4.12</v>
+        <v>4.32</v>
       </c>
       <c r="F11" t="n">
-        <v>0.82</v>
+        <v>0.19</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.2482</v>
+        <v>0.0463</v>
       </c>
       <c r="H11" t="n">
-        <v>0.96</v>
+        <v>0.33</v>
       </c>
       <c r="I11" t="n">
-        <v>2.7</v>
+        <v>2.23</v>
       </c>
       <c r="J11" t="n">
-        <v>2.84</v>
+        <v>3.38</v>
       </c>
       <c r="K11" t="n">
-        <v>3.09</v>
+        <v>3.64</v>
       </c>
       <c r="L11" t="n">
-        <v>3.33</v>
+        <v>3.9</v>
       </c>
       <c r="M11" t="n">
-        <v>3.52</v>
+        <v>4.61</v>
       </c>
       <c r="N11" t="n">
-        <v>3.71</v>
+        <v>5.31</v>
       </c>
       <c r="O11" t="n">
-        <v>4.01</v>
+        <v>5.12</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1455,18 +1451,14 @@
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v/>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
@@ -1478,50 +1470,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.16</v>
+        <v>4.48</v>
       </c>
       <c r="C12" t="n">
-        <v>4.42</v>
+        <v>4.69</v>
       </c>
       <c r="D12" t="n">
-        <v>4.09</v>
+        <v>4.26</v>
       </c>
       <c r="E12" t="n">
-        <v>4.32</v>
+        <v>4.57</v>
       </c>
       <c r="F12" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0463</v>
+        <v>0.0582</v>
       </c>
       <c r="H12" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="I12" t="n">
-        <v>2.23</v>
+        <v>3.75</v>
       </c>
       <c r="J12" t="n">
-        <v>3.38</v>
+        <v>4.01</v>
       </c>
       <c r="K12" t="n">
-        <v>3.64</v>
+        <v>4.15</v>
       </c>
       <c r="L12" t="n">
-        <v>3.9</v>
+        <v>4.28</v>
       </c>
       <c r="M12" t="n">
-        <v>4.61</v>
+        <v>4.48</v>
       </c>
       <c r="N12" t="n">
-        <v>5.31</v>
+        <v>4.68</v>
       </c>
       <c r="O12" t="n">
-        <v>5.12</v>
+        <v>4.75</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1542,8 +1534,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U12" s="8" t="n">
-        <v/>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
@@ -1558,50 +1552,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.48</v>
+        <v>4.53</v>
       </c>
       <c r="C13" t="n">
-        <v>4.69</v>
+        <v>4.68</v>
       </c>
       <c r="D13" t="n">
-        <v>4.26</v>
+        <v>4.24</v>
       </c>
       <c r="E13" t="n">
-        <v>4.57</v>
+        <v>4.58</v>
       </c>
       <c r="F13" t="n">
-        <v>0.25</v>
+        <v>0.01</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0582</v>
+        <v>0.0031</v>
       </c>
       <c r="H13" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="I13" t="n">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="J13" t="n">
-        <v>4.01</v>
+        <v>4.19</v>
       </c>
       <c r="K13" t="n">
-        <v>4.15</v>
+        <v>4.35</v>
       </c>
       <c r="L13" t="n">
-        <v>4.28</v>
+        <v>4.52</v>
       </c>
       <c r="M13" t="n">
-        <v>4.48</v>
+        <v>4.78</v>
       </c>
       <c r="N13" t="n">
-        <v>4.68</v>
+        <v>5.04</v>
       </c>
       <c r="O13" t="n">
-        <v>4.75</v>
+        <v>5.11</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1609,23 +1603,21 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1635,55 +1627,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.53</v>
+        <v>4.47</v>
       </c>
       <c r="C14" t="n">
-        <v>4.68</v>
+        <v>4.87</v>
       </c>
       <c r="D14" t="n">
-        <v>4.24</v>
+        <v>4.27</v>
       </c>
       <c r="E14" t="n">
-        <v>4.58</v>
+        <v>4.85</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01</v>
+        <v>0.27</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.059</v>
       </c>
       <c r="H14" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="I14" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="J14" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="K14" t="n">
-        <v>4.35</v>
+        <v>4.36</v>
       </c>
       <c r="L14" t="n">
         <v>4.52</v>
       </c>
       <c r="M14" t="n">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="N14" t="n">
-        <v>5.04</v>
+        <v>5.08</v>
       </c>
       <c r="O14" t="n">
-        <v>5.11</v>
+        <v>5.12</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1698,11 +1694,13 @@
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1715,59 +1713,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.47</v>
+        <v>4.87</v>
       </c>
       <c r="C15" t="n">
-        <v>4.87</v>
+        <v>5.5</v>
       </c>
       <c r="D15" t="n">
-        <v>4.27</v>
+        <v>4.76</v>
       </c>
       <c r="E15" t="n">
-        <v>4.85</v>
+        <v>5.29</v>
       </c>
       <c r="F15" t="n">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.059</v>
+        <v>0.0905</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6</v>
+        <v>0.74</v>
       </c>
       <c r="I15" t="n">
-        <v>3.8</v>
+        <v>3.66</v>
       </c>
       <c r="J15" t="n">
-        <v>4.2</v>
+        <v>4.39</v>
       </c>
       <c r="K15" t="n">
-        <v>4.36</v>
+        <v>4.55</v>
       </c>
       <c r="L15" t="n">
-        <v>4.52</v>
+        <v>4.71</v>
       </c>
       <c r="M15" t="n">
-        <v>4.8</v>
+        <v>5.15</v>
       </c>
       <c r="N15" t="n">
-        <v>5.08</v>
+        <v>5.59</v>
       </c>
       <c r="O15" t="n">
-        <v>5.12</v>
+        <v>5.47</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1775,26 +1769,26 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v/>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
@@ -1806,81 +1800,83 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.87</v>
+        <v>5.1</v>
       </c>
       <c r="C16" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="D16" t="n">
-        <v>4.76</v>
+        <v>4.07</v>
       </c>
       <c r="E16" t="n">
-        <v>5.29</v>
+        <v>4.11</v>
       </c>
       <c r="F16" t="n">
-        <v>0.44</v>
+        <v>-1.18</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0905</v>
+        <v>-0.2223</v>
       </c>
       <c r="H16" t="n">
-        <v>0.74</v>
+        <v>1.14</v>
       </c>
       <c r="I16" t="n">
-        <v>3.66</v>
+        <v>4.02</v>
       </c>
       <c r="J16" t="n">
-        <v>4.39</v>
+        <v>4.63</v>
       </c>
       <c r="K16" t="n">
-        <v>4.55</v>
+        <v>4.92</v>
       </c>
       <c r="L16" t="n">
-        <v>4.71</v>
+        <v>5.21</v>
       </c>
       <c r="M16" t="n">
-        <v>5.15</v>
+        <v>5.66</v>
       </c>
       <c r="N16" t="n">
-        <v>5.59</v>
+        <v>6.11</v>
       </c>
       <c r="O16" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
+        <v>6.23</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
       <c r="U16" s="8" t="n">
         <v/>
       </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W16" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="V16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W16" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
@@ -1888,69 +1884,63 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.1</v>
+        <v>4.17</v>
       </c>
       <c r="C17" t="n">
-        <v>5.2</v>
+        <v>4.22</v>
       </c>
       <c r="D17" t="n">
-        <v>4.07</v>
+        <v>3.84</v>
       </c>
       <c r="E17" t="n">
-        <v>4.11</v>
+        <v>3.98</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.18</v>
+        <v>-0.13</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.2223</v>
+        <v>-0.0314</v>
       </c>
       <c r="H17" t="n">
-        <v>1.14</v>
+        <v>0.38</v>
       </c>
       <c r="I17" t="n">
-        <v>4.02</v>
+        <v>2.93</v>
       </c>
       <c r="J17" t="n">
-        <v>4.63</v>
+        <v>2.71</v>
       </c>
       <c r="K17" t="n">
-        <v>4.92</v>
+        <v>3.54</v>
       </c>
       <c r="L17" t="n">
-        <v>5.21</v>
+        <v>4.37</v>
       </c>
       <c r="M17" t="n">
-        <v>5.66</v>
+        <v>4.68</v>
       </c>
       <c r="N17" t="n">
-        <v>6.11</v>
+        <v>4.99</v>
       </c>
       <c r="O17" t="n">
-        <v>6.23</v>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>6.34</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1972,50 +1962,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.0959</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="L18" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="M18" t="n">
         <v>4.17</v>
       </c>
-      <c r="C18" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="D18" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="E18" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>-0.0314</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="L18" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="M18" t="n">
-        <v>4.68</v>
-      </c>
       <c r="N18" t="n">
-        <v>4.99</v>
+        <v>4.34</v>
       </c>
       <c r="O18" t="n">
-        <v>6.34</v>
+        <v>4.6</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2026,105 +2016,113 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="W18" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.08</v>
+        <v>4.45</v>
       </c>
       <c r="C19" t="n">
-        <v>4.59</v>
+        <v>4.72</v>
       </c>
       <c r="D19" t="n">
-        <v>3.8</v>
+        <v>3.56</v>
       </c>
       <c r="E19" t="n">
-        <v>4.37</v>
+        <v>3.62</v>
       </c>
       <c r="F19" t="n">
-        <v>0.38</v>
+        <v>-0.75</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0959</v>
+        <v>-0.1713</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8</v>
+        <v>1.16</v>
       </c>
       <c r="I19" t="n">
-        <v>3.46</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>3.58</v>
+        <v>3.66</v>
       </c>
       <c r="K19" t="n">
-        <v>3.79</v>
+        <v>3.97</v>
       </c>
       <c r="L19" t="n">
-        <v>4.01</v>
+        <v>4.28</v>
       </c>
       <c r="M19" t="n">
-        <v>4.17</v>
+        <v>4.76</v>
       </c>
       <c r="N19" t="n">
-        <v>4.34</v>
+        <v>5.25</v>
       </c>
       <c r="O19" t="n">
-        <v>4.6</v>
+        <v>5.39</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W19" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -2136,64 +2134,62 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.45</v>
+        <v>3.51</v>
       </c>
       <c r="C20" t="n">
-        <v>4.72</v>
+        <v>3.63</v>
       </c>
       <c r="D20" t="n">
-        <v>3.56</v>
+        <v>3.13</v>
       </c>
       <c r="E20" t="n">
-        <v>3.62</v>
+        <v>3.17</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.75</v>
+        <v>-0.45</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.1713</v>
+        <v>-0.1241</v>
       </c>
       <c r="H20" t="n">
-        <v>1.16</v>
+        <v>0.5</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
-        <v>3.66</v>
+        <v>2.2</v>
       </c>
       <c r="K20" t="n">
-        <v>3.97</v>
+        <v>3.04</v>
       </c>
       <c r="L20" t="n">
-        <v>4.28</v>
+        <v>3.88</v>
       </c>
       <c r="M20" t="n">
-        <v>4.76</v>
+        <v>4.2</v>
       </c>
       <c r="N20" t="n">
-        <v>5.25</v>
+        <v>4.51</v>
       </c>
       <c r="O20" t="n">
-        <v>5.39</v>
+        <v>5.88</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -2213,59 +2209,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.51</v>
+        <v>3.29</v>
       </c>
       <c r="C21" t="n">
-        <v>3.63</v>
+        <v>3.5</v>
       </c>
       <c r="D21" t="n">
-        <v>3.13</v>
+        <v>3.01</v>
       </c>
       <c r="E21" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.45</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.1241</v>
+        <v>-0.0208</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="I21" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="J21" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="K21" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="L21" t="n">
-        <v>3.88</v>
+        <v>3.28</v>
       </c>
       <c r="M21" t="n">
-        <v>4.2</v>
+        <v>3.42</v>
       </c>
       <c r="N21" t="n">
-        <v>4.51</v>
+        <v>3.57</v>
       </c>
       <c r="O21" t="n">
-        <v>5.88</v>
+        <v>4.14</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2273,18 +2265,18 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R21" s="6" t="n">
+        <v/>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2302,50 +2294,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="C22" t="n">
-        <v>3.5</v>
+        <v>5.65</v>
       </c>
       <c r="D22" t="n">
-        <v>3.01</v>
+        <v>3.38</v>
       </c>
       <c r="E22" t="n">
-        <v>3.1</v>
+        <v>5.28</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.07000000000000001</v>
+        <v>2.17</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.7</v>
       </c>
       <c r="H22" t="n">
-        <v>0.49</v>
+        <v>2.27</v>
       </c>
       <c r="I22" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="J22" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="K22" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="L22" t="n">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="M22" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>3.57</v>
+        <v>3.52</v>
       </c>
       <c r="O22" t="n">
-        <v>4.14</v>
+        <v>3.99</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2356,9 +2348,9 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
@@ -2366,15 +2358,19 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W22" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W22" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X22" t="inlineStr"/>
@@ -2382,50 +2378,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.5</v>
+        <v>5.79</v>
       </c>
       <c r="C23" t="n">
-        <v>5.65</v>
+        <v>7.83</v>
       </c>
       <c r="D23" t="n">
-        <v>3.38</v>
+        <v>3.73</v>
       </c>
       <c r="E23" t="n">
-        <v>5.28</v>
+        <v>4.35</v>
       </c>
       <c r="F23" t="n">
-        <v>2.17</v>
+        <v>-0.92</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.7</v>
+        <v>-0.1746</v>
       </c>
       <c r="H23" t="n">
-        <v>2.27</v>
+        <v>4.1</v>
       </c>
       <c r="I23" t="n">
-        <v>2.51</v>
+        <v>1.11</v>
       </c>
       <c r="J23" t="n">
-        <v>2.54</v>
+        <v>3.39</v>
       </c>
       <c r="K23" t="n">
-        <v>2.86</v>
+        <v>4.14</v>
       </c>
       <c r="L23" t="n">
-        <v>3.18</v>
+        <v>4.9</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>6.41</v>
       </c>
       <c r="N23" t="n">
-        <v>3.52</v>
+        <v>7.93</v>
       </c>
       <c r="O23" t="n">
-        <v>3.99</v>
+        <v>7.92</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2433,12 +2429,14 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
@@ -2446,70 +2444,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5.79</v>
+        <v>3.71</v>
       </c>
       <c r="C24" t="n">
-        <v>7.83</v>
+        <v>3.74</v>
       </c>
       <c r="D24" t="n">
-        <v>3.73</v>
+        <v>3.15</v>
       </c>
       <c r="E24" t="n">
-        <v>4.35</v>
+        <v>3.42</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.92</v>
+        <v>-0.93</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.1746</v>
+        <v>-0.2141</v>
       </c>
       <c r="H24" t="n">
-        <v>4.1</v>
+        <v>0.58</v>
       </c>
       <c r="I24" t="n">
-        <v>1.11</v>
+        <v>-0.37</v>
       </c>
       <c r="J24" t="n">
-        <v>3.39</v>
+        <v>-0.46</v>
       </c>
       <c r="K24" t="n">
-        <v>4.14</v>
+        <v>2.3</v>
       </c>
       <c r="L24" t="n">
-        <v>4.9</v>
+        <v>5.07</v>
       </c>
       <c r="M24" t="n">
-        <v>6.41</v>
+        <v>6.4</v>
       </c>
       <c r="N24" t="n">
-        <v>7.93</v>
+        <v>7.74</v>
       </c>
       <c r="O24" t="n">
-        <v>7.92</v>
+        <v>11.93</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2527,10 +2525,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T24" s="8" t="n">
+        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2545,57 +2541,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>-0.0523</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="L25" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="M25" t="n">
         <v>3.71</v>
       </c>
-      <c r="C25" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="D25" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="E25" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-0.93</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>-0.2141</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I25" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="J25" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="L25" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="M25" t="n">
-        <v>6.4</v>
-      </c>
       <c r="N25" t="n">
-        <v>7.74</v>
+        <v>3.99</v>
       </c>
       <c r="O25" t="n">
-        <v>11.93</v>
+        <v>4.32</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2636,60 +2632,62 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="C26" t="n">
-        <v>3.32</v>
+        <v>3.17</v>
       </c>
       <c r="D26" t="n">
-        <v>3.06</v>
+        <v>2.92</v>
       </c>
       <c r="E26" t="n">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.18</v>
+        <v>-0.2</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0523</v>
+        <v>-0.0604</v>
       </c>
       <c r="H26" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="I26" t="n">
-        <v>2.57</v>
+        <v>2.79</v>
       </c>
       <c r="J26" t="n">
-        <v>2.83</v>
+        <v>3.01</v>
       </c>
       <c r="K26" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="L26" t="n">
-        <v>3.43</v>
+        <v>3.21</v>
       </c>
       <c r="M26" t="n">
-        <v>3.71</v>
+        <v>3.37</v>
       </c>
       <c r="N26" t="n">
-        <v>3.99</v>
+        <v>3.53</v>
       </c>
       <c r="O26" t="n">
-        <v>4.32</v>
+        <v>3.58</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
@@ -2720,50 +2718,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B27" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>-0.0617</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="L27" t="n">
         <v>3.05</v>
       </c>
-      <c r="C27" t="n">
+      <c r="M27" t="n">
         <v>3.17</v>
       </c>
-      <c r="D27" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="E27" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="F27" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>-0.0604</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I27" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="J27" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="L27" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="M27" t="n">
-        <v>3.37</v>
-      </c>
       <c r="N27" t="n">
-        <v>3.53</v>
+        <v>3.3</v>
       </c>
       <c r="O27" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2783,8 +2781,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T27" s="8" t="n">
-        <v/>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2799,84 +2799,82 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.24</v>
+        <v>2.93</v>
       </c>
       <c r="C28" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="D28" t="n">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="E28" t="n">
-        <v>2.86</v>
+        <v>3.19</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.19</v>
+        <v>0.33</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0617</v>
+        <v>0.1144</v>
       </c>
       <c r="H28" t="n">
-        <v>0.48</v>
+        <v>0.41</v>
       </c>
       <c r="I28" t="n">
-        <v>2.67</v>
+        <v>2.3</v>
       </c>
       <c r="J28" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="K28" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="L28" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="M28" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="O28" t="n">
-        <v>3.42</v>
+        <v>3.73</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
@@ -2885,59 +2883,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="C29" t="n">
-        <v>3.28</v>
+        <v>3.49</v>
       </c>
       <c r="D29" t="n">
-        <v>2.87</v>
+        <v>2.96</v>
       </c>
       <c r="E29" t="n">
-        <v>3.19</v>
+        <v>3.13</v>
       </c>
       <c r="F29" t="n">
-        <v>0.33</v>
+        <v>-0.06</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.1144</v>
+        <v>-0.0173</v>
       </c>
       <c r="H29" t="n">
-        <v>0.41</v>
+        <v>0.53</v>
       </c>
       <c r="I29" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="J29" t="n">
-        <v>2.3</v>
+        <v>2.83</v>
       </c>
       <c r="K29" t="n">
-        <v>2.62</v>
+        <v>2.98</v>
       </c>
       <c r="L29" t="n">
-        <v>2.94</v>
+        <v>3.13</v>
       </c>
       <c r="M29" t="n">
-        <v>3.1</v>
+        <v>3.39</v>
       </c>
       <c r="N29" t="n">
-        <v>3.26</v>
+        <v>3.66</v>
       </c>
       <c r="O29" t="n">
-        <v>3.73</v>
+        <v>3.69</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2945,12 +2939,14 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
@@ -2958,10 +2954,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2971,55 +2965,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="C30" t="n">
-        <v>3.49</v>
+        <v>3.27</v>
       </c>
       <c r="D30" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="E30" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0173</v>
+        <v>-0.0115</v>
       </c>
       <c r="H30" t="n">
-        <v>0.53</v>
+        <v>0.35</v>
       </c>
       <c r="I30" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="J30" t="n">
-        <v>2.83</v>
+        <v>2.55</v>
       </c>
       <c r="K30" t="n">
-        <v>2.98</v>
+        <v>2.86</v>
       </c>
       <c r="L30" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="M30" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>3.66</v>
+        <v>3.62</v>
       </c>
       <c r="O30" t="n">
-        <v>3.69</v>
+        <v>4.03</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3027,20 +3025,16 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3055,66 +3049,68 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3.18</v>
+        <v>3.11</v>
       </c>
       <c r="C31" t="n">
-        <v>3.27</v>
+        <v>3.15</v>
       </c>
       <c r="D31" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="E31" t="n">
         <v>3.1</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0115</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="I31" t="n">
-        <v>2.43</v>
+        <v>2.58</v>
       </c>
       <c r="J31" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="K31" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="L31" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="N31" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="O31" t="n">
         <v>3.62</v>
       </c>
-      <c r="O31" t="n">
-        <v>4.03</v>
-      </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
@@ -3137,63 +3133,65 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3.11</v>
+        <v>3.06</v>
       </c>
       <c r="C32" t="n">
-        <v>3.15</v>
+        <v>3.06</v>
       </c>
       <c r="D32" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="E32" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0</v>
+        <v>-0.0953</v>
       </c>
       <c r="H32" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="I32" t="n">
         <v>2.58</v>
       </c>
       <c r="J32" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="K32" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="L32" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="M32" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="N32" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="O32" t="n">
         <v>3.44</v>
       </c>
-      <c r="O32" t="n">
-        <v>3.62</v>
-      </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
@@ -3202,7 +3200,7 @@
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3214,76 +3212,70 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W32" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3.06</v>
+        <v>2.84</v>
       </c>
       <c r="C33" t="n">
-        <v>3.06</v>
+        <v>2.89</v>
       </c>
       <c r="D33" t="n">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
       <c r="E33" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3</v>
+        <v>-0.15</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0953</v>
+        <v>-0.0543</v>
       </c>
       <c r="H33" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="I33" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="J33" t="n">
-        <v>2.85</v>
+        <v>2.46</v>
       </c>
       <c r="K33" t="n">
-        <v>2.95</v>
+        <v>2.66</v>
       </c>
       <c r="L33" t="n">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="M33" t="n">
-        <v>3.24</v>
+        <v>2.94</v>
       </c>
       <c r="N33" t="n">
-        <v>3.43</v>
+        <v>3.02</v>
       </c>
       <c r="O33" t="n">
-        <v>3.44</v>
+        <v>3.33</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S33" s="10" t="inlineStr">
@@ -3310,50 +3302,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.84</v>
+        <v>2.69</v>
       </c>
       <c r="C34" t="n">
-        <v>2.89</v>
+        <v>2.72</v>
       </c>
       <c r="D34" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="E34" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.15</v>
+        <v>0.03</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0543</v>
+        <v>0.0098</v>
       </c>
       <c r="H34" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="I34" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="J34" t="n">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="K34" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="L34" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="M34" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="N34" t="n">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="O34" t="n">
-        <v>3.33</v>
+        <v>3.15</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3361,14 +3353,12 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R34" s="6" t="n">
+        <v/>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3385,72 +3375,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>2.69</v>
       </c>
       <c r="C35" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="D35" t="n">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="E35" t="n">
-        <v>2.67</v>
+        <v>2.52</v>
       </c>
       <c r="F35" t="n">
-        <v>0.03</v>
+        <v>-0.15</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0098</v>
+        <v>-0.0565</v>
       </c>
       <c r="H35" t="n">
-        <v>0.16</v>
+        <v>0.27</v>
       </c>
       <c r="I35" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
-        <v>2.33</v>
+        <v>2.53</v>
       </c>
       <c r="K35" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="L35" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="M35" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="N35" t="n">
         <v>2.85</v>
       </c>
       <c r="O35" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3472,83 +3472,81 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.69</v>
+        <v>2.51</v>
       </c>
       <c r="C36" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="D36" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="E36" t="n">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.15</v>
+        <v>0.26</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0565</v>
+        <v>0.1019</v>
       </c>
       <c r="H36" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="J36" t="n">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="K36" t="n">
-        <v>2.59</v>
+        <v>2.39</v>
       </c>
       <c r="L36" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="M36" t="n">
         <v>2.66</v>
       </c>
-      <c r="M36" t="n">
-        <v>2.75</v>
-      </c>
       <c r="N36" t="n">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="O36" t="n">
-        <v>2.88</v>
+        <v>3.03</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W36" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -3560,50 +3558,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B37" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C37" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>-0.0083</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J37" t="n">
         <v>2.51</v>
       </c>
-      <c r="C37" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="D37" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="E37" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="G37" s="5" t="n">
-        <v>0.1019</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I37" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="J37" t="n">
-        <v>2.2</v>
-      </c>
       <c r="K37" t="n">
-        <v>2.39</v>
+        <v>2.61</v>
       </c>
       <c r="L37" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="M37" t="n">
-        <v>2.66</v>
+        <v>2.95</v>
       </c>
       <c r="N37" t="n">
-        <v>2.74</v>
+        <v>3.18</v>
       </c>
       <c r="O37" t="n">
-        <v>3.03</v>
+        <v>3.16</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3616,18 +3614,14 @@
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3646,50 +3640,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="C38" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="D38" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="E38" t="n">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.02</v>
+        <v>0.2</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0083</v>
+        <v>0.0736</v>
       </c>
       <c r="H38" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="I38" t="n">
-        <v>2.14</v>
+        <v>2.47</v>
       </c>
       <c r="J38" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="K38" t="n">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="L38" t="n">
-        <v>2.72</v>
+        <v>2.77</v>
       </c>
       <c r="M38" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N38" t="n">
         <v>2.95</v>
       </c>
-      <c r="N38" t="n">
-        <v>3.18</v>
-      </c>
       <c r="O38" t="n">
-        <v>3.16</v>
+        <v>3.09</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3702,14 +3696,18 @@
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3719,59 +3717,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="C39" t="n">
-        <v>2.98</v>
+        <v>3.14</v>
       </c>
       <c r="D39" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="E39" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2</v>
+        <v>-0.05</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0736</v>
+        <v>-0.0179</v>
       </c>
       <c r="H39" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="I39" t="n">
-        <v>2.47</v>
+        <v>2.52</v>
       </c>
       <c r="J39" t="n">
-        <v>2.54</v>
+        <v>2.78</v>
       </c>
       <c r="K39" t="n">
-        <v>2.65</v>
+        <v>2.84</v>
       </c>
       <c r="L39" t="n">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="M39" t="n">
-        <v>2.86</v>
+        <v>3.08</v>
       </c>
       <c r="N39" t="n">
-        <v>2.95</v>
+        <v>3.24</v>
       </c>
       <c r="O39" t="n">
-        <v>3.09</v>
+        <v>3.21</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3782,9 +3776,9 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
@@ -3792,10 +3786,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U39" s="8" t="n">
+        <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3805,55 +3797,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="C40" t="n">
-        <v>3.14</v>
+        <v>3.39</v>
       </c>
       <c r="D40" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="E40" t="n">
-        <v>2.91</v>
+        <v>3.29</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.05</v>
+        <v>0.38</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.1318</v>
       </c>
       <c r="H40" t="n">
-        <v>0.25</v>
+        <v>0.53</v>
       </c>
       <c r="I40" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="J40" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K40" t="n">
         <v>2.78</v>
       </c>
-      <c r="K40" t="n">
-        <v>2.84</v>
-      </c>
       <c r="L40" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="M40" t="n">
-        <v>3.08</v>
+        <v>3.03</v>
       </c>
       <c r="N40" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="O40" t="n">
-        <v>3.21</v>
+        <v>3.39</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3864,9 +3860,9 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
@@ -3874,11 +3870,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V40" s="8" t="n">
-        <v/>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W40" s="9" t="inlineStr">
         <is>
@@ -3894,50 +3894,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.9</v>
+        <v>3.34</v>
       </c>
       <c r="C41" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="D41" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.29</v>
+        <v>3.23</v>
       </c>
       <c r="F41" t="n">
-        <v>0.38</v>
+        <v>-0.06</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.1318</v>
+        <v>-0.0185</v>
       </c>
       <c r="H41" t="n">
-        <v>0.53</v>
+        <v>0.3</v>
       </c>
       <c r="I41" t="n">
-        <v>2.64</v>
+        <v>2.33</v>
       </c>
       <c r="J41" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="K41" t="n">
-        <v>2.78</v>
+        <v>3.02</v>
       </c>
       <c r="L41" t="n">
-        <v>2.96</v>
+        <v>3.21</v>
       </c>
       <c r="M41" t="n">
-        <v>3.03</v>
+        <v>3.56</v>
       </c>
       <c r="N41" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="O41" t="n">
-        <v>3.39</v>
+        <v>3.92</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3950,23 +3950,17 @@
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v/>
       </c>
       <c r="W41" s="9" t="inlineStr">
         <is>
@@ -3982,50 +3976,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3.34</v>
+        <v>3.18</v>
       </c>
       <c r="C42" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="D42" t="n">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="E42" t="n">
-        <v>3.23</v>
+        <v>3.12</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.06</v>
+        <v>-0.11</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0185</v>
+        <v>-0.0338</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
       <c r="I42" t="n">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="J42" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="K42" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="L42" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="M42" t="n">
-        <v>3.56</v>
+        <v>3.38</v>
       </c>
       <c r="N42" t="n">
-        <v>3.9</v>
+        <v>3.52</v>
       </c>
       <c r="O42" t="n">
-        <v>3.92</v>
+        <v>3.69</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4033,12 +4027,14 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4057,57 +4053,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="C43" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="D43" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="E43" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.11</v>
+        <v>0.08</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0338</v>
+        <v>0.025</v>
       </c>
       <c r="H43" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="I43" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="J43" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="K43" t="n">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="L43" t="n">
-        <v>3.24</v>
+        <v>3.13</v>
       </c>
       <c r="M43" t="n">
-        <v>3.38</v>
+        <v>3.23</v>
       </c>
       <c r="N43" t="n">
-        <v>3.52</v>
+        <v>3.33</v>
       </c>
       <c r="O43" t="n">
-        <v>3.69</v>
+        <v>3.47</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4115,19 +4111,19 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
       <c r="U43" s="8" t="n">
         <v/>
       </c>
@@ -4141,57 +4137,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3.09</v>
+        <v>3.28</v>
       </c>
       <c r="C44" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="D44" t="n">
-        <v>3.02</v>
+        <v>3.14</v>
       </c>
       <c r="E44" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="F44" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.025</v>
+        <v>0.0103</v>
       </c>
       <c r="H44" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="I44" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="J44" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="K44" t="n">
-        <v>3.01</v>
+        <v>3.06</v>
       </c>
       <c r="L44" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="M44" t="n">
-        <v>3.23</v>
+        <v>3.34</v>
       </c>
       <c r="N44" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="O44" t="n">
-        <v>3.47</v>
+        <v>3.58</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4204,12 +4200,12 @@
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U44" s="8" t="n">
@@ -4223,59 +4219,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>3.28</v>
       </c>
       <c r="C45" t="n">
-        <v>3.44</v>
+        <v>3.33</v>
       </c>
       <c r="D45" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="E45" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="F45" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0103</v>
+        <v>0.0043</v>
       </c>
       <c r="H45" t="n">
-        <v>0.31</v>
+        <v>0.18</v>
       </c>
       <c r="I45" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="J45" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="K45" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="L45" t="n">
-        <v>3.18</v>
+        <v>3.26</v>
       </c>
       <c r="M45" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="N45" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="O45" t="n">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4286,15 +4278,13 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4307,72 +4297,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="C46" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>-0.094</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I46" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="K46" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="L46" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="M46" t="n">
         <v>3.33</v>
       </c>
-      <c r="D46" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="E46" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>0.0043</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="I46" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="J46" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K46" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="L46" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="M46" t="n">
-        <v>3.38</v>
-      </c>
       <c r="N46" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="O46" t="n">
         <v>3.51</v>
       </c>
-      <c r="O46" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4380,9 +4382,9 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W46" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
@@ -4394,75 +4396,67 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3.21</v>
+        <v>2.93</v>
       </c>
       <c r="C47" t="n">
-        <v>3.36</v>
+        <v>2.97</v>
       </c>
       <c r="D47" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="E47" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.3</v>
+        <v>-0.03</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.094</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>0.48</v>
+        <v>0.14</v>
       </c>
       <c r="I47" t="n">
-        <v>2.97</v>
+        <v>2.39</v>
       </c>
       <c r="J47" t="n">
-        <v>3.07</v>
+        <v>2.37</v>
       </c>
       <c r="K47" t="n">
-        <v>3.16</v>
+        <v>2.7</v>
       </c>
       <c r="L47" t="n">
-        <v>3.24</v>
+        <v>3.03</v>
       </c>
       <c r="M47" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="N47" t="n">
         <v>3.33</v>
       </c>
-      <c r="N47" t="n">
-        <v>3.42</v>
-      </c>
       <c r="O47" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3.84</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4475,59 +4469,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="C48" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="D48" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="E48" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-0.0137</v>
       </c>
       <c r="H48" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="I48" t="n">
-        <v>2.39</v>
+        <v>2.68</v>
       </c>
       <c r="J48" t="n">
-        <v>2.37</v>
+        <v>2.77</v>
       </c>
       <c r="K48" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="L48" t="n">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="M48" t="n">
-        <v>3.18</v>
+        <v>2.98</v>
       </c>
       <c r="N48" t="n">
-        <v>3.33</v>
+        <v>3.06</v>
       </c>
       <c r="O48" t="n">
-        <v>3.84</v>
+        <v>3.11</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4535,16 +4525,20 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T48" s="8" t="n">
-        <v/>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4557,76 +4551,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="C49" t="n">
-        <v>2.99</v>
+        <v>2.84</v>
       </c>
       <c r="D49" t="n">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="E49" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.04</v>
+        <v>-0.12</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0432</v>
       </c>
       <c r="H49" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="I49" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="J49" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="K49" t="n">
-        <v>2.84</v>
+        <v>2.79</v>
       </c>
       <c r="L49" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="M49" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="N49" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="O49" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
+        <v>3.15</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4639,69 +4639,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="C50" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="D50" t="n">
         <v>2.62</v>
       </c>
       <c r="E50" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.12</v>
+        <v>-0.09</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0432</v>
+        <v>-0.0309</v>
       </c>
       <c r="H50" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="I50" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="J50" t="n">
-        <v>2.69</v>
+        <v>2.54</v>
       </c>
       <c r="K50" t="n">
-        <v>2.79</v>
+        <v>2.64</v>
       </c>
       <c r="L50" t="n">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="M50" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="N50" t="n">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="O50" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3.05</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v/>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
@@ -4732,50 +4724,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="C51" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="D51" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="E51" t="n">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0309</v>
+        <v>0.0267</v>
       </c>
       <c r="H51" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="I51" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="J51" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="K51" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="L51" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="M51" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="N51" t="n">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="O51" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4783,19 +4775,19 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
       <c r="U51" s="8" t="n">
         <v/>
       </c>
@@ -4807,55 +4799,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="C52" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="D52" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="E52" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="F52" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0267</v>
+        <v>0.0146</v>
       </c>
       <c r="H52" t="n">
-        <v>0.13</v>
+        <v>0.24</v>
       </c>
       <c r="I52" t="n">
-        <v>2.42</v>
+        <v>2.57</v>
       </c>
       <c r="J52" t="n">
-        <v>2.44</v>
+        <v>2.59</v>
       </c>
       <c r="K52" t="n">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="L52" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="M52" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="N52" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="O52" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4863,21 +4859,25 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
@@ -4889,57 +4889,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="C53" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="D53" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="E53" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="F53" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0146</v>
+        <v>0.0415</v>
       </c>
       <c r="H53" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="I53" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="J53" t="n">
-        <v>2.59</v>
+        <v>2.54</v>
       </c>
       <c r="K53" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="L53" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="M53" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="N53" t="n">
-        <v>2.84</v>
+        <v>3.02</v>
       </c>
       <c r="O53" t="n">
-        <v>2.96</v>
+        <v>3.11</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4947,25 +4947,21 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R53" s="6" t="n">
+        <v/>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T53" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -4977,57 +4973,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="C54" t="n">
-        <v>2.94</v>
+        <v>3.03</v>
       </c>
       <c r="D54" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="E54" t="n">
-        <v>2.89</v>
+        <v>2.97</v>
       </c>
       <c r="F54" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0415</v>
+        <v>0.0301</v>
       </c>
       <c r="H54" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="I54" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="J54" t="n">
-        <v>2.54</v>
+        <v>2.67</v>
       </c>
       <c r="K54" t="n">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="L54" t="n">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="M54" t="n">
-        <v>2.89</v>
+        <v>3.01</v>
       </c>
       <c r="N54" t="n">
-        <v>3.02</v>
+        <v>3.17</v>
       </c>
       <c r="O54" t="n">
-        <v>3.11</v>
+        <v>3.19</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5068,70 +5064,72 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B55" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="C55" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E55" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>-0.0484</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I55" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K55" t="n">
         <v>2.88</v>
       </c>
-      <c r="C55" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="D55" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="E55" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>0.0301</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="I55" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="J55" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="K55" t="n">
-        <v>2.76</v>
-      </c>
       <c r="L55" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="M55" t="n">
-        <v>3.01</v>
+        <v>3.07</v>
       </c>
       <c r="N55" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="O55" t="n">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
+      <c r="Q55" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
       <c r="U55" s="8" t="n">
         <v/>
       </c>
@@ -5143,81 +5141,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="C56" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="D56" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="E56" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.14</v>
+        <v>0.08</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0484</v>
+        <v>0.0286</v>
       </c>
       <c r="H56" t="n">
-        <v>0.26</v>
+        <v>0.13</v>
       </c>
       <c r="I56" t="n">
-        <v>2.64</v>
+        <v>2.49</v>
       </c>
       <c r="J56" t="n">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="K56" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="L56" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="M56" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N56" t="n">
         <v>3.07</v>
       </c>
-      <c r="N56" t="n">
-        <v>3.19</v>
-      </c>
       <c r="O56" t="n">
-        <v>3.22</v>
+        <v>3.27</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
       <c r="U56" s="8" t="n">
         <v/>
       </c>
@@ -5229,55 +5221,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="C57" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="E57" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.1075</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I57" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="J57" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="L57" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="M57" t="n">
         <v>2.98</v>
       </c>
-      <c r="D57" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E57" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>0.0286</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I57" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="J57" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K57" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L57" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="M57" t="n">
-        <v>2.96</v>
-      </c>
       <c r="N57" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="O57" t="n">
-        <v>3.27</v>
+        <v>3.11</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5285,8 +5281,10 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
@@ -5295,111 +5293,25 @@
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V57" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W57" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W57" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="C58" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D58" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="E58" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.1264</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="I58" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="J58" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K58" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="L58" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="M58" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="N58" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="O58" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
         <is>
           <t>弱警訊</t>
         </is>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5243,13 +5243,13 @@
         <v>2.82</v>
       </c>
       <c r="E57" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="F57" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.1075</v>
+        <v>0.0975</v>
       </c>
       <c r="H57" t="n">
         <v>0.5</v>
@@ -5314,6 +5314,88 @@
       <c r="X57" t="inlineStr">
         <is>
           <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="C58" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="E58" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.0153</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="L58" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="M58" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="O58" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>0.26</v>
       </c>
       <c r="I2" t="n">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="J2" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="K2" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="L2" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="M2" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="N2" t="n">
-        <v>3.49</v>
+        <v>3.45</v>
       </c>
       <c r="O2" t="n">
-        <v>3.42</v>
+        <v>3.39</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5324,25 +5324,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="C58" t="n">
-        <v>3.16</v>
+        <v>3.11</v>
       </c>
       <c r="D58" t="n">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="E58" t="n">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.05</v>
+        <v>-0.18</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0153</v>
+        <v>-0.0566</v>
       </c>
       <c r="H58" t="n">
-        <v>0.01</v>
+        <v>0.14</v>
       </c>
       <c r="I58" t="n">
         <v>2.32</v>
@@ -5371,12 +5371,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>0.26</v>
       </c>
       <c r="I2" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="J2" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="K2" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="L2" t="n">
         <v>2.92</v>
       </c>
       <c r="M2" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="N2" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="O2" t="n">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -690,11 +690,13 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -5327,22 +5329,22 @@
         <v>3.08</v>
       </c>
       <c r="C58" t="n">
-        <v>3.11</v>
+        <v>3.16</v>
       </c>
       <c r="D58" t="n">
         <v>2.97</v>
       </c>
       <c r="E58" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0566</v>
+        <v>-0.0585</v>
       </c>
       <c r="H58" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="I58" t="n">
         <v>2.32</v>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>0.26</v>
       </c>
       <c r="I2" t="n">
-        <v>2.33</v>
+        <v>2.68</v>
       </c>
       <c r="J2" t="n">
-        <v>2.72</v>
+        <v>2.85</v>
       </c>
       <c r="K2" t="n">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="L2" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="M2" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="O2" t="n">
-        <v>3.37</v>
+        <v>3.2</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,8 +685,10 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -5332,19 +5334,19 @@
         <v>3.16</v>
       </c>
       <c r="D58" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="E58" t="n">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.19</v>
+        <v>-0.25</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0585</v>
+        <v>-0.0767</v>
       </c>
       <c r="H58" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="I58" t="n">
         <v>2.32</v>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.97</v>
+        <v>3.09</v>
       </c>
       <c r="C2" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="D2" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="E2" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05</v>
+        <v>-0.11</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.017</v>
+        <v>-0.0351</v>
       </c>
       <c r="H2" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="I2" t="n">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="J2" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="K2" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="L2" t="n">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="M2" t="n">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="N2" t="n">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
       <c r="O2" t="n">
-        <v>3.2</v>
+        <v>3.39</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -687,19 +687,19 @@
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="U2" s="8" t="n">
         <v/>
       </c>
@@ -711,55 +711,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="M3" t="n">
         <v>3.09</v>
       </c>
-      <c r="C3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>-0.0351</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="L3" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="M3" t="n">
-        <v>3.18</v>
-      </c>
       <c r="N3" t="n">
-        <v>3.33</v>
+        <v>3.19</v>
       </c>
       <c r="O3" t="n">
-        <v>3.39</v>
+        <v>3.5</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -772,7 +776,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -795,57 +799,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="C4" t="n">
-        <v>3.17</v>
+        <v>2.97</v>
       </c>
       <c r="D4" t="n">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="E4" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="F4" t="n">
         <v>-0.05</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.018</v>
+        <v>-0.0184</v>
       </c>
       <c r="H4" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="J4" t="n">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="K4" t="n">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="L4" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="M4" t="n">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
       <c r="N4" t="n">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="O4" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -858,15 +862,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -888,50 +890,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.91</v>
+        <v>3.15</v>
       </c>
       <c r="C5" t="n">
-        <v>2.97</v>
+        <v>3.59</v>
       </c>
       <c r="D5" t="n">
-        <v>2.77</v>
+        <v>3.13</v>
       </c>
       <c r="E5" t="n">
-        <v>2.84</v>
+        <v>3.32</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.05</v>
+        <v>0.49</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0184</v>
+        <v>0.1725</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="I5" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="J5" t="n">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
       <c r="K5" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="L5" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="M5" t="n">
-        <v>3.04</v>
+        <v>2.93</v>
       </c>
       <c r="N5" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="O5" t="n">
-        <v>3.48</v>
+        <v>3.16</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -939,83 +941,83 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
-      </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="C6" t="n">
-        <v>3.59</v>
+        <v>3.55</v>
       </c>
       <c r="D6" t="n">
-        <v>3.13</v>
+        <v>3.09</v>
       </c>
       <c r="E6" t="n">
-        <v>3.32</v>
+        <v>3.11</v>
       </c>
       <c r="F6" t="n">
-        <v>0.49</v>
+        <v>-0.22</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.1725</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="I6" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="J6" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="K6" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="L6" t="n">
-        <v>2.85</v>
+        <v>3.34</v>
       </c>
       <c r="M6" t="n">
-        <v>2.93</v>
+        <v>3.55</v>
       </c>
       <c r="N6" t="n">
-        <v>3.01</v>
+        <v>3.76</v>
       </c>
       <c r="O6" t="n">
-        <v>3.16</v>
+        <v>4.04</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1023,12 +1025,14 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
@@ -1036,70 +1040,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="C7" t="n">
-        <v>3.55</v>
+        <v>3.14</v>
       </c>
       <c r="D7" t="n">
-        <v>3.09</v>
+        <v>2.89</v>
       </c>
       <c r="E7" t="n">
-        <v>3.11</v>
+        <v>3.01</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.22</v>
+        <v>-0.1</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.0316</v>
       </c>
       <c r="H7" t="n">
-        <v>0.46</v>
+        <v>0.25</v>
       </c>
       <c r="I7" t="n">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="J7" t="n">
-        <v>2.85</v>
+        <v>2.54</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="L7" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="M7" t="n">
         <v>3.34</v>
       </c>
-      <c r="M7" t="n">
-        <v>3.55</v>
-      </c>
       <c r="N7" t="n">
-        <v>3.76</v>
+        <v>3.46</v>
       </c>
       <c r="O7" t="n">
-        <v>4.04</v>
+        <v>4.01</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1112,15 +1116,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
+      <c r="S7" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1142,50 +1144,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="C8" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="D8" t="n">
         <v>3.14</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.0984</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K8" t="n">
         <v>2.89</v>
       </c>
-      <c r="E8" t="n">
+      <c r="L8" t="n">
         <v>3.01</v>
       </c>
-      <c r="F8" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>-0.0316</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3.21</v>
-      </c>
       <c r="M8" t="n">
-        <v>3.34</v>
+        <v>3.13</v>
       </c>
       <c r="N8" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="O8" t="n">
-        <v>4.01</v>
+        <v>3.38</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1193,83 +1195,83 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v/>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.16</v>
+        <v>3.41</v>
       </c>
       <c r="C9" t="n">
-        <v>3.57</v>
+        <v>4.16</v>
       </c>
       <c r="D9" t="n">
-        <v>3.14</v>
+        <v>3.19</v>
       </c>
       <c r="E9" t="n">
-        <v>3.3</v>
+        <v>4.12</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3</v>
+        <v>0.82</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0984</v>
+        <v>0.2482</v>
       </c>
       <c r="H9" t="n">
-        <v>0.44</v>
+        <v>0.96</v>
       </c>
       <c r="I9" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="J9" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="K9" t="n">
-        <v>2.89</v>
+        <v>3.09</v>
       </c>
       <c r="L9" t="n">
-        <v>3.01</v>
+        <v>3.33</v>
       </c>
       <c r="M9" t="n">
-        <v>3.13</v>
+        <v>3.52</v>
       </c>
       <c r="N9" t="n">
-        <v>3.25</v>
+        <v>3.71</v>
       </c>
       <c r="O9" t="n">
-        <v>3.38</v>
+        <v>4.01</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1280,7 +1282,7 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="7" t="inlineStr">
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1292,12 +1294,12 @@
       </c>
       <c r="U9" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V9" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="V9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W9" s="9" t="inlineStr">
@@ -1310,50 +1312,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.41</v>
+        <v>4.16</v>
       </c>
       <c r="C10" t="n">
-        <v>4.16</v>
+        <v>4.42</v>
       </c>
       <c r="D10" t="n">
-        <v>3.19</v>
+        <v>4.09</v>
       </c>
       <c r="E10" t="n">
-        <v>4.12</v>
+        <v>4.32</v>
       </c>
       <c r="F10" t="n">
-        <v>0.82</v>
+        <v>0.19</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.2482</v>
+        <v>0.0463</v>
       </c>
       <c r="H10" t="n">
-        <v>0.96</v>
+        <v>0.33</v>
       </c>
       <c r="I10" t="n">
-        <v>2.7</v>
+        <v>2.23</v>
       </c>
       <c r="J10" t="n">
-        <v>2.84</v>
+        <v>3.38</v>
       </c>
       <c r="K10" t="n">
-        <v>3.09</v>
+        <v>3.64</v>
       </c>
       <c r="L10" t="n">
-        <v>3.33</v>
+        <v>3.9</v>
       </c>
       <c r="M10" t="n">
-        <v>3.52</v>
+        <v>4.61</v>
       </c>
       <c r="N10" t="n">
-        <v>3.71</v>
+        <v>5.31</v>
       </c>
       <c r="O10" t="n">
-        <v>4.01</v>
+        <v>5.12</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1364,25 +1366,21 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="7" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v/>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
@@ -1394,50 +1392,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.16</v>
+        <v>4.48</v>
       </c>
       <c r="C11" t="n">
-        <v>4.42</v>
+        <v>4.69</v>
       </c>
       <c r="D11" t="n">
-        <v>4.09</v>
+        <v>4.26</v>
       </c>
       <c r="E11" t="n">
-        <v>4.32</v>
+        <v>4.57</v>
       </c>
       <c r="F11" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0463</v>
+        <v>0.0582</v>
       </c>
       <c r="H11" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="I11" t="n">
-        <v>2.23</v>
+        <v>3.75</v>
       </c>
       <c r="J11" t="n">
-        <v>3.38</v>
+        <v>4.01</v>
       </c>
       <c r="K11" t="n">
-        <v>3.64</v>
+        <v>4.15</v>
       </c>
       <c r="L11" t="n">
-        <v>3.9</v>
+        <v>4.28</v>
       </c>
       <c r="M11" t="n">
-        <v>4.61</v>
+        <v>4.48</v>
       </c>
       <c r="N11" t="n">
-        <v>5.31</v>
+        <v>4.68</v>
       </c>
       <c r="O11" t="n">
-        <v>5.12</v>
+        <v>4.75</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1448,7 +1446,7 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="7" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1458,8 +1456,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U11" s="8" t="n">
-        <v/>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1474,50 +1474,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.48</v>
+        <v>4.53</v>
       </c>
       <c r="C12" t="n">
-        <v>4.69</v>
+        <v>4.68</v>
       </c>
       <c r="D12" t="n">
-        <v>4.26</v>
+        <v>4.24</v>
       </c>
       <c r="E12" t="n">
-        <v>4.57</v>
+        <v>4.58</v>
       </c>
       <c r="F12" t="n">
-        <v>0.25</v>
+        <v>0.01</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0582</v>
+        <v>0.0031</v>
       </c>
       <c r="H12" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="I12" t="n">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="J12" t="n">
-        <v>4.01</v>
+        <v>4.19</v>
       </c>
       <c r="K12" t="n">
-        <v>4.15</v>
+        <v>4.35</v>
       </c>
       <c r="L12" t="n">
-        <v>4.28</v>
+        <v>4.52</v>
       </c>
       <c r="M12" t="n">
-        <v>4.48</v>
+        <v>4.78</v>
       </c>
       <c r="N12" t="n">
-        <v>4.68</v>
+        <v>5.04</v>
       </c>
       <c r="O12" t="n">
-        <v>4.75</v>
+        <v>5.11</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1525,24 +1525,22 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
+      <c r="R12" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
@@ -1551,55 +1549,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.53</v>
+        <v>4.47</v>
       </c>
       <c r="C13" t="n">
-        <v>4.68</v>
+        <v>4.87</v>
       </c>
       <c r="D13" t="n">
-        <v>4.24</v>
+        <v>4.27</v>
       </c>
       <c r="E13" t="n">
-        <v>4.58</v>
+        <v>4.85</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01</v>
+        <v>0.27</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.059</v>
       </c>
       <c r="H13" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="I13" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="J13" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="K13" t="n">
-        <v>4.35</v>
+        <v>4.36</v>
       </c>
       <c r="L13" t="n">
         <v>4.52</v>
       </c>
       <c r="M13" t="n">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="N13" t="n">
-        <v>5.04</v>
+        <v>5.08</v>
       </c>
       <c r="O13" t="n">
-        <v>5.11</v>
+        <v>5.12</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1612,13 +1614,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1631,59 +1635,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.47</v>
+        <v>4.87</v>
       </c>
       <c r="C14" t="n">
-        <v>4.87</v>
+        <v>5.5</v>
       </c>
       <c r="D14" t="n">
-        <v>4.27</v>
+        <v>4.76</v>
       </c>
       <c r="E14" t="n">
-        <v>4.85</v>
+        <v>5.29</v>
       </c>
       <c r="F14" t="n">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.059</v>
+        <v>0.0905</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6</v>
+        <v>0.74</v>
       </c>
       <c r="I14" t="n">
-        <v>3.8</v>
+        <v>3.66</v>
       </c>
       <c r="J14" t="n">
-        <v>4.2</v>
+        <v>4.39</v>
       </c>
       <c r="K14" t="n">
-        <v>4.36</v>
+        <v>4.55</v>
       </c>
       <c r="L14" t="n">
-        <v>4.52</v>
+        <v>4.71</v>
       </c>
       <c r="M14" t="n">
-        <v>4.8</v>
+        <v>5.15</v>
       </c>
       <c r="N14" t="n">
-        <v>5.08</v>
+        <v>5.59</v>
       </c>
       <c r="O14" t="n">
-        <v>5.12</v>
+        <v>5.47</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1691,26 +1691,26 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v/>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
@@ -1722,81 +1722,83 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.87</v>
+        <v>5.1</v>
       </c>
       <c r="C15" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="D15" t="n">
-        <v>4.76</v>
+        <v>4.07</v>
       </c>
       <c r="E15" t="n">
-        <v>5.29</v>
+        <v>4.11</v>
       </c>
       <c r="F15" t="n">
-        <v>0.44</v>
+        <v>-1.18</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0905</v>
+        <v>-0.2223</v>
       </c>
       <c r="H15" t="n">
-        <v>0.74</v>
+        <v>1.14</v>
       </c>
       <c r="I15" t="n">
-        <v>3.66</v>
+        <v>4.02</v>
       </c>
       <c r="J15" t="n">
-        <v>4.39</v>
+        <v>4.63</v>
       </c>
       <c r="K15" t="n">
-        <v>4.55</v>
+        <v>4.92</v>
       </c>
       <c r="L15" t="n">
-        <v>4.71</v>
+        <v>5.21</v>
       </c>
       <c r="M15" t="n">
-        <v>5.15</v>
+        <v>5.66</v>
       </c>
       <c r="N15" t="n">
-        <v>5.59</v>
+        <v>6.11</v>
       </c>
       <c r="O15" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+        <v>6.23</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
       </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W15" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="V15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W15" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
@@ -1804,69 +1806,63 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.1</v>
+        <v>4.17</v>
       </c>
       <c r="C16" t="n">
-        <v>5.2</v>
+        <v>4.22</v>
       </c>
       <c r="D16" t="n">
-        <v>4.07</v>
+        <v>3.84</v>
       </c>
       <c r="E16" t="n">
-        <v>4.11</v>
+        <v>3.98</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.18</v>
+        <v>-0.13</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.2223</v>
+        <v>-0.0314</v>
       </c>
       <c r="H16" t="n">
-        <v>1.14</v>
+        <v>0.38</v>
       </c>
       <c r="I16" t="n">
-        <v>4.02</v>
+        <v>2.93</v>
       </c>
       <c r="J16" t="n">
-        <v>4.63</v>
+        <v>2.71</v>
       </c>
       <c r="K16" t="n">
-        <v>4.92</v>
+        <v>3.54</v>
       </c>
       <c r="L16" t="n">
-        <v>5.21</v>
+        <v>4.37</v>
       </c>
       <c r="M16" t="n">
-        <v>5.66</v>
+        <v>4.68</v>
       </c>
       <c r="N16" t="n">
-        <v>6.11</v>
+        <v>4.99</v>
       </c>
       <c r="O16" t="n">
-        <v>6.23</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>6.34</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1888,50 +1884,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B17" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.0959</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="M17" t="n">
         <v>4.17</v>
       </c>
-      <c r="C17" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="D17" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="E17" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>-0.0314</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="L17" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="M17" t="n">
-        <v>4.68</v>
-      </c>
       <c r="N17" t="n">
-        <v>4.99</v>
+        <v>4.34</v>
       </c>
       <c r="O17" t="n">
-        <v>6.34</v>
+        <v>4.6</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1944,103 +1940,111 @@
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="W17" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.08</v>
+        <v>4.45</v>
       </c>
       <c r="C18" t="n">
-        <v>4.59</v>
+        <v>4.72</v>
       </c>
       <c r="D18" t="n">
-        <v>3.8</v>
+        <v>3.56</v>
       </c>
       <c r="E18" t="n">
-        <v>4.37</v>
+        <v>3.62</v>
       </c>
       <c r="F18" t="n">
-        <v>0.38</v>
+        <v>-0.75</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0959</v>
+        <v>-0.1713</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8</v>
+        <v>1.16</v>
       </c>
       <c r="I18" t="n">
-        <v>3.46</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>3.58</v>
+        <v>3.66</v>
       </c>
       <c r="K18" t="n">
-        <v>3.79</v>
+        <v>3.97</v>
       </c>
       <c r="L18" t="n">
-        <v>4.01</v>
+        <v>4.28</v>
       </c>
       <c r="M18" t="n">
-        <v>4.17</v>
+        <v>4.76</v>
       </c>
       <c r="N18" t="n">
-        <v>4.34</v>
+        <v>5.25</v>
       </c>
       <c r="O18" t="n">
-        <v>4.6</v>
+        <v>5.39</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W18" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -2052,65 +2056,63 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.45</v>
+        <v>3.51</v>
       </c>
       <c r="C19" t="n">
-        <v>4.72</v>
+        <v>3.63</v>
       </c>
       <c r="D19" t="n">
-        <v>3.56</v>
+        <v>3.13</v>
       </c>
       <c r="E19" t="n">
-        <v>3.62</v>
+        <v>3.17</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.75</v>
+        <v>-0.45</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.1713</v>
+        <v>-0.1241</v>
       </c>
       <c r="H19" t="n">
-        <v>1.16</v>
+        <v>0.5</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
-        <v>3.66</v>
+        <v>2.2</v>
       </c>
       <c r="K19" t="n">
-        <v>3.97</v>
+        <v>3.04</v>
       </c>
       <c r="L19" t="n">
-        <v>4.28</v>
+        <v>3.88</v>
       </c>
       <c r="M19" t="n">
-        <v>4.76</v>
+        <v>4.2</v>
       </c>
       <c r="N19" t="n">
-        <v>5.25</v>
+        <v>4.51</v>
       </c>
       <c r="O19" t="n">
-        <v>5.39</v>
+        <v>5.88</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
+      <c r="S19" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2129,59 +2131,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.51</v>
+        <v>3.29</v>
       </c>
       <c r="C20" t="n">
-        <v>3.63</v>
+        <v>3.5</v>
       </c>
       <c r="D20" t="n">
-        <v>3.13</v>
+        <v>3.01</v>
       </c>
       <c r="E20" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.45</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.1241</v>
+        <v>-0.0208</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="J20" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="K20" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="L20" t="n">
-        <v>3.88</v>
+        <v>3.28</v>
       </c>
       <c r="M20" t="n">
-        <v>4.2</v>
+        <v>3.42</v>
       </c>
       <c r="N20" t="n">
-        <v>4.51</v>
+        <v>3.57</v>
       </c>
       <c r="O20" t="n">
-        <v>5.88</v>
+        <v>4.14</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2189,18 +2187,18 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2218,50 +2216,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="C21" t="n">
-        <v>3.5</v>
+        <v>5.65</v>
       </c>
       <c r="D21" t="n">
-        <v>3.01</v>
+        <v>3.38</v>
       </c>
       <c r="E21" t="n">
-        <v>3.1</v>
+        <v>5.28</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.07000000000000001</v>
+        <v>2.17</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.7</v>
       </c>
       <c r="H21" t="n">
-        <v>0.49</v>
+        <v>2.27</v>
       </c>
       <c r="I21" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="J21" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="K21" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="L21" t="n">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="M21" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>3.57</v>
+        <v>3.52</v>
       </c>
       <c r="O21" t="n">
-        <v>4.14</v>
+        <v>3.99</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2274,7 +2272,7 @@
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
@@ -2282,15 +2280,19 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W21" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W21" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr"/>
@@ -2298,50 +2300,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.5</v>
+        <v>5.79</v>
       </c>
       <c r="C22" t="n">
-        <v>5.65</v>
+        <v>7.83</v>
       </c>
       <c r="D22" t="n">
-        <v>3.38</v>
+        <v>3.73</v>
       </c>
       <c r="E22" t="n">
-        <v>5.28</v>
+        <v>4.35</v>
       </c>
       <c r="F22" t="n">
-        <v>2.17</v>
+        <v>-0.92</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.7</v>
+        <v>-0.1746</v>
       </c>
       <c r="H22" t="n">
-        <v>2.27</v>
+        <v>4.1</v>
       </c>
       <c r="I22" t="n">
-        <v>2.51</v>
+        <v>1.11</v>
       </c>
       <c r="J22" t="n">
-        <v>2.54</v>
+        <v>3.39</v>
       </c>
       <c r="K22" t="n">
-        <v>2.86</v>
+        <v>4.14</v>
       </c>
       <c r="L22" t="n">
-        <v>3.18</v>
+        <v>4.9</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>6.41</v>
       </c>
       <c r="N22" t="n">
-        <v>3.52</v>
+        <v>7.93</v>
       </c>
       <c r="O22" t="n">
-        <v>3.99</v>
+        <v>7.92</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2349,12 +2351,14 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
@@ -2362,70 +2366,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5.79</v>
+        <v>3.71</v>
       </c>
       <c r="C23" t="n">
-        <v>7.83</v>
+        <v>3.74</v>
       </c>
       <c r="D23" t="n">
-        <v>3.73</v>
+        <v>3.15</v>
       </c>
       <c r="E23" t="n">
-        <v>4.35</v>
+        <v>3.42</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.92</v>
+        <v>-0.93</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.1746</v>
+        <v>-0.2141</v>
       </c>
       <c r="H23" t="n">
-        <v>4.1</v>
+        <v>0.58</v>
       </c>
       <c r="I23" t="n">
-        <v>1.11</v>
+        <v>-0.37</v>
       </c>
       <c r="J23" t="n">
-        <v>3.39</v>
+        <v>-0.46</v>
       </c>
       <c r="K23" t="n">
-        <v>4.14</v>
+        <v>2.3</v>
       </c>
       <c r="L23" t="n">
-        <v>4.9</v>
+        <v>5.07</v>
       </c>
       <c r="M23" t="n">
-        <v>6.41</v>
+        <v>6.4</v>
       </c>
       <c r="N23" t="n">
-        <v>7.93</v>
+        <v>7.74</v>
       </c>
       <c r="O23" t="n">
-        <v>7.92</v>
+        <v>11.93</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2438,15 +2442,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S23" s="10" t="inlineStr">
+      <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T23" s="8" t="n">
+        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2461,57 +2463,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>-0.0523</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="L24" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="M24" t="n">
         <v>3.71</v>
       </c>
-      <c r="C24" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="D24" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="E24" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-0.93</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>-0.2141</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I24" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="J24" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="L24" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="M24" t="n">
-        <v>6.4</v>
-      </c>
       <c r="N24" t="n">
-        <v>7.74</v>
+        <v>3.99</v>
       </c>
       <c r="O24" t="n">
-        <v>11.93</v>
+        <v>4.32</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2524,7 +2526,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S24" s="10" t="inlineStr">
+      <c r="S24" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2552,63 +2554,65 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="C25" t="n">
-        <v>3.32</v>
+        <v>3.17</v>
       </c>
       <c r="D25" t="n">
-        <v>3.06</v>
+        <v>2.92</v>
       </c>
       <c r="E25" t="n">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.18</v>
+        <v>-0.2</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0523</v>
+        <v>-0.0604</v>
       </c>
       <c r="H25" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="I25" t="n">
-        <v>2.57</v>
+        <v>2.79</v>
       </c>
       <c r="J25" t="n">
-        <v>2.83</v>
+        <v>3.01</v>
       </c>
       <c r="K25" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="L25" t="n">
-        <v>3.43</v>
+        <v>3.21</v>
       </c>
       <c r="M25" t="n">
-        <v>3.71</v>
+        <v>3.37</v>
       </c>
       <c r="N25" t="n">
-        <v>3.99</v>
+        <v>3.53</v>
       </c>
       <c r="O25" t="n">
-        <v>4.32</v>
+        <v>3.58</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2636,50 +2640,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B26" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>-0.0617</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="L26" t="n">
         <v>3.05</v>
       </c>
-      <c r="C26" t="n">
+      <c r="M26" t="n">
         <v>3.17</v>
       </c>
-      <c r="D26" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="E26" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>-0.0604</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="L26" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="M26" t="n">
-        <v>3.37</v>
-      </c>
       <c r="N26" t="n">
-        <v>3.53</v>
+        <v>3.3</v>
       </c>
       <c r="O26" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2694,13 +2698,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="S26" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T26" s="8" t="n">
-        <v/>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2715,84 +2721,82 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.24</v>
+        <v>2.93</v>
       </c>
       <c r="C27" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="D27" t="n">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="E27" t="n">
-        <v>2.86</v>
+        <v>3.19</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.19</v>
+        <v>0.33</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0617</v>
+        <v>0.1144</v>
       </c>
       <c r="H27" t="n">
-        <v>0.48</v>
+        <v>0.41</v>
       </c>
       <c r="I27" t="n">
-        <v>2.67</v>
+        <v>2.3</v>
       </c>
       <c r="J27" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="K27" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="L27" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="M27" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="N27" t="n">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="O27" t="n">
-        <v>3.42</v>
+        <v>3.73</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
@@ -2801,59 +2805,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="C28" t="n">
-        <v>3.28</v>
+        <v>3.49</v>
       </c>
       <c r="D28" t="n">
-        <v>2.87</v>
+        <v>2.96</v>
       </c>
       <c r="E28" t="n">
-        <v>3.19</v>
+        <v>3.13</v>
       </c>
       <c r="F28" t="n">
-        <v>0.33</v>
+        <v>-0.06</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.1144</v>
+        <v>-0.0173</v>
       </c>
       <c r="H28" t="n">
-        <v>0.41</v>
+        <v>0.53</v>
       </c>
       <c r="I28" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="J28" t="n">
-        <v>2.3</v>
+        <v>2.83</v>
       </c>
       <c r="K28" t="n">
-        <v>2.62</v>
+        <v>2.98</v>
       </c>
       <c r="L28" t="n">
-        <v>2.94</v>
+        <v>3.13</v>
       </c>
       <c r="M28" t="n">
-        <v>3.1</v>
+        <v>3.39</v>
       </c>
       <c r="N28" t="n">
-        <v>3.26</v>
+        <v>3.66</v>
       </c>
       <c r="O28" t="n">
-        <v>3.73</v>
+        <v>3.69</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2861,12 +2861,14 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
@@ -2874,10 +2876,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2887,55 +2887,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="C29" t="n">
-        <v>3.49</v>
+        <v>3.27</v>
       </c>
       <c r="D29" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="E29" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0173</v>
+        <v>-0.0115</v>
       </c>
       <c r="H29" t="n">
-        <v>0.53</v>
+        <v>0.35</v>
       </c>
       <c r="I29" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="J29" t="n">
-        <v>2.83</v>
+        <v>2.55</v>
       </c>
       <c r="K29" t="n">
-        <v>2.98</v>
+        <v>2.86</v>
       </c>
       <c r="L29" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="M29" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>3.66</v>
+        <v>3.62</v>
       </c>
       <c r="O29" t="n">
-        <v>3.69</v>
+        <v>4.03</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2943,20 +2947,16 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R29" s="6" t="n">
+        <v/>
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2971,68 +2971,70 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.18</v>
+        <v>3.11</v>
       </c>
       <c r="C30" t="n">
-        <v>3.27</v>
+        <v>3.15</v>
       </c>
       <c r="D30" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="E30" t="n">
         <v>3.1</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0115</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="I30" t="n">
-        <v>2.43</v>
+        <v>2.58</v>
       </c>
       <c r="J30" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="K30" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="L30" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="N30" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="O30" t="n">
         <v>3.62</v>
       </c>
-      <c r="O30" t="n">
-        <v>4.03</v>
-      </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3053,72 +3055,74 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3.11</v>
+        <v>3.06</v>
       </c>
       <c r="C31" t="n">
-        <v>3.15</v>
+        <v>3.06</v>
       </c>
       <c r="D31" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="E31" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0</v>
+        <v>-0.0953</v>
       </c>
       <c r="H31" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="I31" t="n">
         <v>2.58</v>
       </c>
       <c r="J31" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="K31" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="L31" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="M31" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="N31" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="O31" t="n">
         <v>3.44</v>
       </c>
-      <c r="O31" t="n">
-        <v>3.62</v>
-      </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3130,79 +3134,73 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W31" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3.06</v>
+        <v>2.84</v>
       </c>
       <c r="C32" t="n">
-        <v>3.06</v>
+        <v>2.89</v>
       </c>
       <c r="D32" t="n">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
       <c r="E32" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.3</v>
+        <v>-0.15</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0953</v>
+        <v>-0.0543</v>
       </c>
       <c r="H32" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="I32" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="J32" t="n">
-        <v>2.85</v>
+        <v>2.46</v>
       </c>
       <c r="K32" t="n">
-        <v>2.95</v>
+        <v>2.66</v>
       </c>
       <c r="L32" t="n">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="M32" t="n">
-        <v>3.24</v>
+        <v>2.94</v>
       </c>
       <c r="N32" t="n">
-        <v>3.43</v>
+        <v>3.02</v>
       </c>
       <c r="O32" t="n">
-        <v>3.44</v>
+        <v>3.33</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3226,50 +3224,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.84</v>
+        <v>2.69</v>
       </c>
       <c r="C33" t="n">
-        <v>2.89</v>
+        <v>2.72</v>
       </c>
       <c r="D33" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="E33" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.15</v>
+        <v>0.03</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0543</v>
+        <v>0.0098</v>
       </c>
       <c r="H33" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="I33" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="J33" t="n">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="K33" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="L33" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="M33" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="N33" t="n">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="O33" t="n">
-        <v>3.33</v>
+        <v>3.15</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3277,14 +3275,12 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3301,72 +3297,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>2.69</v>
       </c>
       <c r="C34" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="D34" t="n">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="E34" t="n">
-        <v>2.67</v>
+        <v>2.52</v>
       </c>
       <c r="F34" t="n">
-        <v>0.03</v>
+        <v>-0.15</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0098</v>
+        <v>-0.0565</v>
       </c>
       <c r="H34" t="n">
-        <v>0.16</v>
+        <v>0.27</v>
       </c>
       <c r="I34" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
-        <v>2.33</v>
+        <v>2.53</v>
       </c>
       <c r="K34" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="L34" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="M34" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="N34" t="n">
         <v>2.85</v>
       </c>
       <c r="O34" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3388,83 +3394,81 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.69</v>
+        <v>2.51</v>
       </c>
       <c r="C35" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="D35" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="E35" t="n">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.15</v>
+        <v>0.26</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0565</v>
+        <v>0.1019</v>
       </c>
       <c r="H35" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="J35" t="n">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="K35" t="n">
-        <v>2.59</v>
+        <v>2.39</v>
       </c>
       <c r="L35" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="M35" t="n">
         <v>2.66</v>
       </c>
-      <c r="M35" t="n">
-        <v>2.75</v>
-      </c>
       <c r="N35" t="n">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="O35" t="n">
-        <v>2.88</v>
+        <v>3.03</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W35" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
@@ -3476,50 +3480,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B36" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>-0.0083</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J36" t="n">
         <v>2.51</v>
       </c>
-      <c r="C36" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="D36" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="E36" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>0.1019</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I36" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="J36" t="n">
-        <v>2.2</v>
-      </c>
       <c r="K36" t="n">
-        <v>2.39</v>
+        <v>2.61</v>
       </c>
       <c r="L36" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="M36" t="n">
-        <v>2.66</v>
+        <v>2.95</v>
       </c>
       <c r="N36" t="n">
-        <v>2.74</v>
+        <v>3.18</v>
       </c>
       <c r="O36" t="n">
-        <v>3.03</v>
+        <v>3.16</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3530,20 +3534,16 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3562,50 +3562,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="C37" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="D37" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="E37" t="n">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.02</v>
+        <v>0.2</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0083</v>
+        <v>0.0736</v>
       </c>
       <c r="H37" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="I37" t="n">
-        <v>2.14</v>
+        <v>2.47</v>
       </c>
       <c r="J37" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="K37" t="n">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="L37" t="n">
-        <v>2.72</v>
+        <v>2.77</v>
       </c>
       <c r="M37" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N37" t="n">
         <v>2.95</v>
       </c>
-      <c r="N37" t="n">
-        <v>3.18</v>
-      </c>
       <c r="O37" t="n">
-        <v>3.16</v>
+        <v>3.09</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3616,16 +3616,20 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3635,59 +3639,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="C38" t="n">
-        <v>2.98</v>
+        <v>3.14</v>
       </c>
       <c r="D38" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="E38" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="F38" t="n">
-        <v>0.2</v>
+        <v>-0.05</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0736</v>
+        <v>-0.0179</v>
       </c>
       <c r="H38" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="I38" t="n">
-        <v>2.47</v>
+        <v>2.52</v>
       </c>
       <c r="J38" t="n">
-        <v>2.54</v>
+        <v>2.78</v>
       </c>
       <c r="K38" t="n">
-        <v>2.65</v>
+        <v>2.84</v>
       </c>
       <c r="L38" t="n">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="M38" t="n">
-        <v>2.86</v>
+        <v>3.08</v>
       </c>
       <c r="N38" t="n">
-        <v>2.95</v>
+        <v>3.24</v>
       </c>
       <c r="O38" t="n">
-        <v>3.09</v>
+        <v>3.21</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
@@ -3708,10 +3708,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U38" s="8" t="n">
+        <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3721,55 +3719,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="C39" t="n">
-        <v>3.14</v>
+        <v>3.39</v>
       </c>
       <c r="D39" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="E39" t="n">
-        <v>2.91</v>
+        <v>3.29</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.05</v>
+        <v>0.38</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.1318</v>
       </c>
       <c r="H39" t="n">
-        <v>0.25</v>
+        <v>0.53</v>
       </c>
       <c r="I39" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="J39" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K39" t="n">
         <v>2.78</v>
       </c>
-      <c r="K39" t="n">
-        <v>2.84</v>
-      </c>
       <c r="L39" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="M39" t="n">
-        <v>3.08</v>
+        <v>3.03</v>
       </c>
       <c r="N39" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="O39" t="n">
-        <v>3.21</v>
+        <v>3.39</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3782,7 +3784,7 @@
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
@@ -3790,11 +3792,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v/>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W39" s="9" t="inlineStr">
         <is>
@@ -3810,50 +3816,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.9</v>
+        <v>3.34</v>
       </c>
       <c r="C40" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="D40" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="E40" t="n">
-        <v>3.29</v>
+        <v>3.23</v>
       </c>
       <c r="F40" t="n">
-        <v>0.38</v>
+        <v>-0.06</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.1318</v>
+        <v>-0.0185</v>
       </c>
       <c r="H40" t="n">
-        <v>0.53</v>
+        <v>0.3</v>
       </c>
       <c r="I40" t="n">
-        <v>2.64</v>
+        <v>2.33</v>
       </c>
       <c r="J40" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="K40" t="n">
-        <v>2.78</v>
+        <v>3.02</v>
       </c>
       <c r="L40" t="n">
-        <v>2.96</v>
+        <v>3.21</v>
       </c>
       <c r="M40" t="n">
-        <v>3.03</v>
+        <v>3.56</v>
       </c>
       <c r="N40" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="O40" t="n">
-        <v>3.39</v>
+        <v>3.92</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3864,25 +3870,19 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V40" s="8" t="n">
+        <v/>
       </c>
       <c r="W40" s="9" t="inlineStr">
         <is>
@@ -3898,50 +3898,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3.34</v>
+        <v>3.18</v>
       </c>
       <c r="C41" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="D41" t="n">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="E41" t="n">
-        <v>3.23</v>
+        <v>3.12</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.06</v>
+        <v>-0.11</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0185</v>
+        <v>-0.0338</v>
       </c>
       <c r="H41" t="n">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
       <c r="I41" t="n">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="J41" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="K41" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="L41" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="M41" t="n">
-        <v>3.56</v>
+        <v>3.38</v>
       </c>
       <c r="N41" t="n">
-        <v>3.9</v>
+        <v>3.52</v>
       </c>
       <c r="O41" t="n">
-        <v>3.92</v>
+        <v>3.69</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3949,12 +3949,14 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3973,57 +3975,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="C42" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="D42" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="E42" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.11</v>
+        <v>0.08</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0338</v>
+        <v>0.025</v>
       </c>
       <c r="H42" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="I42" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="J42" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="K42" t="n">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="L42" t="n">
-        <v>3.24</v>
+        <v>3.13</v>
       </c>
       <c r="M42" t="n">
-        <v>3.38</v>
+        <v>3.23</v>
       </c>
       <c r="N42" t="n">
-        <v>3.52</v>
+        <v>3.33</v>
       </c>
       <c r="O42" t="n">
-        <v>3.69</v>
+        <v>3.47</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4031,19 +4033,19 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
@@ -4057,57 +4059,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3.09</v>
+        <v>3.28</v>
       </c>
       <c r="C43" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="D43" t="n">
-        <v>3.02</v>
+        <v>3.14</v>
       </c>
       <c r="E43" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="F43" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.025</v>
+        <v>0.0103</v>
       </c>
       <c r="H43" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="I43" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="J43" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="K43" t="n">
-        <v>3.01</v>
+        <v>3.06</v>
       </c>
       <c r="L43" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="M43" t="n">
-        <v>3.23</v>
+        <v>3.34</v>
       </c>
       <c r="N43" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="O43" t="n">
-        <v>3.47</v>
+        <v>3.58</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4118,14 +4120,14 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U43" s="8" t="n">
@@ -4139,59 +4141,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>3.28</v>
       </c>
       <c r="C44" t="n">
-        <v>3.44</v>
+        <v>3.33</v>
       </c>
       <c r="D44" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="E44" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="F44" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0103</v>
+        <v>0.0043</v>
       </c>
       <c r="H44" t="n">
-        <v>0.31</v>
+        <v>0.18</v>
       </c>
       <c r="I44" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="J44" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="K44" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="L44" t="n">
-        <v>3.18</v>
+        <v>3.26</v>
       </c>
       <c r="M44" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="N44" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="O44" t="n">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4204,13 +4202,11 @@
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4223,72 +4219,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="C45" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>-0.094</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="J45" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="K45" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="L45" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="M45" t="n">
         <v>3.33</v>
       </c>
-      <c r="D45" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="E45" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>0.0043</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="I45" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K45" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="L45" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="M45" t="n">
-        <v>3.38</v>
-      </c>
       <c r="N45" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="O45" t="n">
         <v>3.51</v>
       </c>
-      <c r="O45" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4296,9 +4304,9 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W45" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
@@ -4310,75 +4318,67 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3.21</v>
+        <v>2.93</v>
       </c>
       <c r="C46" t="n">
-        <v>3.36</v>
+        <v>2.97</v>
       </c>
       <c r="D46" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="E46" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.3</v>
+        <v>-0.03</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.094</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="H46" t="n">
-        <v>0.48</v>
+        <v>0.14</v>
       </c>
       <c r="I46" t="n">
-        <v>2.97</v>
+        <v>2.39</v>
       </c>
       <c r="J46" t="n">
-        <v>3.07</v>
+        <v>2.37</v>
       </c>
       <c r="K46" t="n">
-        <v>3.16</v>
+        <v>2.7</v>
       </c>
       <c r="L46" t="n">
-        <v>3.24</v>
+        <v>3.03</v>
       </c>
       <c r="M46" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="N46" t="n">
         <v>3.33</v>
       </c>
-      <c r="N46" t="n">
-        <v>3.42</v>
-      </c>
       <c r="O46" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3.84</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4391,59 +4391,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="C47" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="D47" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="E47" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-0.0137</v>
       </c>
       <c r="H47" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="I47" t="n">
-        <v>2.39</v>
+        <v>2.68</v>
       </c>
       <c r="J47" t="n">
-        <v>2.37</v>
+        <v>2.77</v>
       </c>
       <c r="K47" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="L47" t="n">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="M47" t="n">
-        <v>3.18</v>
+        <v>2.98</v>
       </c>
       <c r="N47" t="n">
-        <v>3.33</v>
+        <v>3.06</v>
       </c>
       <c r="O47" t="n">
-        <v>3.84</v>
+        <v>3.11</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4451,16 +4447,20 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T47" s="8" t="n">
-        <v/>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4473,76 +4473,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="C48" t="n">
-        <v>2.99</v>
+        <v>2.84</v>
       </c>
       <c r="D48" t="n">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="E48" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.04</v>
+        <v>-0.12</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0432</v>
       </c>
       <c r="H48" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="I48" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="J48" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="K48" t="n">
-        <v>2.84</v>
+        <v>2.79</v>
       </c>
       <c r="L48" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="M48" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="N48" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="O48" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
+        <v>3.15</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4555,76 +4561,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="C49" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="D49" t="n">
         <v>2.62</v>
       </c>
       <c r="E49" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.12</v>
+        <v>-0.09</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0432</v>
+        <v>-0.0309</v>
       </c>
       <c r="H49" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="I49" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="J49" t="n">
-        <v>2.69</v>
+        <v>2.54</v>
       </c>
       <c r="K49" t="n">
-        <v>2.79</v>
+        <v>2.64</v>
       </c>
       <c r="L49" t="n">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="M49" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="N49" t="n">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="O49" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3.05</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="10" t="inlineStr">
+      <c r="S49" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4648,50 +4646,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="C50" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="D50" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="E50" t="n">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0309</v>
+        <v>0.0267</v>
       </c>
       <c r="H50" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="I50" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="J50" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="K50" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="L50" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="M50" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="N50" t="n">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="O50" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4699,19 +4697,19 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
       <c r="U50" s="8" t="n">
         <v/>
       </c>
@@ -4723,55 +4721,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="C51" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="D51" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="E51" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="F51" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0267</v>
+        <v>0.0146</v>
       </c>
       <c r="H51" t="n">
-        <v>0.13</v>
+        <v>0.24</v>
       </c>
       <c r="I51" t="n">
-        <v>2.42</v>
+        <v>2.57</v>
       </c>
       <c r="J51" t="n">
-        <v>2.44</v>
+        <v>2.59</v>
       </c>
       <c r="K51" t="n">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="L51" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="M51" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="N51" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="O51" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4779,21 +4781,25 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4805,57 +4811,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="C52" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="D52" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="E52" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="F52" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0146</v>
+        <v>0.0415</v>
       </c>
       <c r="H52" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="I52" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="J52" t="n">
-        <v>2.59</v>
+        <v>2.54</v>
       </c>
       <c r="K52" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="L52" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="M52" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="N52" t="n">
-        <v>2.84</v>
+        <v>3.02</v>
       </c>
       <c r="O52" t="n">
-        <v>2.96</v>
+        <v>3.11</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4863,25 +4869,21 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
@@ -4893,57 +4895,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="C53" t="n">
-        <v>2.94</v>
+        <v>3.03</v>
       </c>
       <c r="D53" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="E53" t="n">
-        <v>2.89</v>
+        <v>2.97</v>
       </c>
       <c r="F53" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0415</v>
+        <v>0.0301</v>
       </c>
       <c r="H53" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="I53" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="J53" t="n">
-        <v>2.54</v>
+        <v>2.67</v>
       </c>
       <c r="K53" t="n">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="L53" t="n">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="M53" t="n">
-        <v>2.89</v>
+        <v>3.01</v>
       </c>
       <c r="N53" t="n">
-        <v>3.02</v>
+        <v>3.17</v>
       </c>
       <c r="O53" t="n">
-        <v>3.11</v>
+        <v>3.19</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4954,7 +4956,7 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="7" t="inlineStr">
+      <c r="S53" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4984,69 +4986,71 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B54" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="C54" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>-0.0484</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I54" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K54" t="n">
         <v>2.88</v>
       </c>
-      <c r="C54" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="D54" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="E54" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>0.0301</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="I54" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="J54" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="K54" t="n">
-        <v>2.76</v>
-      </c>
       <c r="L54" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="M54" t="n">
-        <v>3.01</v>
+        <v>3.07</v>
       </c>
       <c r="N54" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="O54" t="n">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5059,81 +5063,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="C55" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="D55" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="E55" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.14</v>
+        <v>0.08</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0484</v>
+        <v>0.0286</v>
       </c>
       <c r="H55" t="n">
-        <v>0.26</v>
+        <v>0.13</v>
       </c>
       <c r="I55" t="n">
-        <v>2.64</v>
+        <v>2.49</v>
       </c>
       <c r="J55" t="n">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="K55" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="L55" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="M55" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N55" t="n">
         <v>3.07</v>
       </c>
-      <c r="N55" t="n">
-        <v>3.19</v>
-      </c>
       <c r="O55" t="n">
-        <v>3.22</v>
+        <v>3.27</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
       <c r="U55" s="8" t="n">
         <v/>
       </c>
@@ -5145,55 +5143,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="C56" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="E56" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.0975</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I56" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="J56" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K56" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="L56" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="M56" t="n">
         <v>2.98</v>
       </c>
-      <c r="D56" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E56" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>0.0286</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I56" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="J56" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K56" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L56" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="M56" t="n">
-        <v>2.96</v>
-      </c>
       <c r="N56" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="O56" t="n">
-        <v>3.27</v>
+        <v>3.11</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5201,83 +5203,89 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V56" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W56" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W56" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="C57" t="n">
-        <v>3.32</v>
+        <v>3.16</v>
       </c>
       <c r="D57" t="n">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="E57" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="F57" t="n">
-        <v>0.28</v>
+        <v>-0.16</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0975</v>
+        <v>-0.0504</v>
       </c>
       <c r="H57" t="n">
-        <v>0.5</v>
+        <v>0.24</v>
       </c>
       <c r="I57" t="n">
-        <v>2.71</v>
+        <v>2.32</v>
       </c>
       <c r="J57" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="K57" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="L57" t="n">
-        <v>2.91</v>
+        <v>3.13</v>
       </c>
       <c r="M57" t="n">
-        <v>2.98</v>
+        <v>3.45</v>
       </c>
       <c r="N57" t="n">
-        <v>3.04</v>
+        <v>3.76</v>
       </c>
       <c r="O57" t="n">
-        <v>3.11</v>
+        <v>3.82</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5287,28 +5295,22 @@
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
       </c>
       <c r="W57" s="9" t="inlineStr">
         <is>
@@ -5316,90 +5318,6 @@
         </is>
       </c>
       <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="C58" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="D58" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="E58" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0767</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I58" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="J58" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="K58" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="L58" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="M58" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N58" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="O58" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
         <is>
           <t>中警訊</t>
         </is>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5323,6 +5323,88 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="C58" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="E58" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L58" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="M58" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="O58" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>0.3</v>
       </c>
       <c r="I2" t="n">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="J2" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="K2" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="L2" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="N2" t="n">
-        <v>3.33</v>
+        <v>3.22</v>
       </c>
       <c r="O2" t="n">
-        <v>3.39</v>
+        <v>3.3</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -713,7 +713,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -5330,25 +5330,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="C58" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="D58" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="F58" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.0343</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="I58" t="n">
         <v>2.67</v>
@@ -5382,11 +5382,13 @@
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -659,35 +659,39 @@
         <v>0.3</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="J2" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="K2" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="L2" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="M2" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>3.22</v>
+        <v>3.14</v>
       </c>
       <c r="O2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+        <v>3.24</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
@@ -700,8 +704,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -5333,22 +5339,22 @@
         <v>3.02</v>
       </c>
       <c r="C58" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="D58" t="n">
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.14</v>
+        <v>3.26</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1</v>
+        <v>0.23</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0343</v>
+        <v>0.0745</v>
       </c>
       <c r="H58" t="n">
-        <v>0.14</v>
+        <v>0.3</v>
       </c>
       <c r="I58" t="n">
         <v>2.67</v>
@@ -5387,12 +5393,14 @@
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
       <c r="V58" s="8" t="n">
         <v/>
       </c>
@@ -5401,11 +5409,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -5351,7 +5351,7 @@
         <v>0.23</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0745</v>
+        <v>0.0755</v>
       </c>
       <c r="H58" t="n">
         <v>0.3</v>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -5339,22 +5339,22 @@
         <v>3.02</v>
       </c>
       <c r="C58" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="D58" t="n">
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.26</v>
+        <v>3.13</v>
       </c>
       <c r="F58" t="n">
-        <v>0.23</v>
+        <v>0.1</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0755</v>
+        <v>0.032</v>
       </c>
       <c r="H58" t="n">
-        <v>0.3</v>
+        <v>0.26</v>
       </c>
       <c r="I58" t="n">
         <v>2.67</v>
@@ -5393,13 +5393,11 @@
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
       </c>
       <c r="V58" s="8" t="n">
         <v/>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,80 +634,74 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="M2" t="n">
         <v>3.09</v>
       </c>
-      <c r="C2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>-0.0351</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="L2" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3.1</v>
-      </c>
       <c r="N2" t="n">
-        <v>3.14</v>
+        <v>3.19</v>
       </c>
       <c r="O2" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
+        <v>3.5</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U2" s="8" t="n">
+        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -719,57 +713,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="C3" t="n">
-        <v>3.17</v>
+        <v>2.97</v>
       </c>
       <c r="D3" t="n">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="E3" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="F3" t="n">
         <v>-0.05</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.018</v>
+        <v>-0.0184</v>
       </c>
       <c r="H3" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="J3" t="n">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="K3" t="n">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="L3" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="M3" t="n">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
       <c r="N3" t="n">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="O3" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -787,10 +781,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -812,50 +804,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.91</v>
+        <v>3.15</v>
       </c>
       <c r="C4" t="n">
-        <v>2.97</v>
+        <v>3.59</v>
       </c>
       <c r="D4" t="n">
-        <v>2.77</v>
+        <v>3.13</v>
       </c>
       <c r="E4" t="n">
-        <v>2.84</v>
+        <v>3.32</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.05</v>
+        <v>0.49</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0184</v>
+        <v>0.1725</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="I4" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="J4" t="n">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
       <c r="K4" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="L4" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="M4" t="n">
-        <v>3.04</v>
+        <v>2.93</v>
       </c>
       <c r="N4" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="O4" t="n">
-        <v>3.48</v>
+        <v>3.16</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -863,83 +855,83 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
-      </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="C5" t="n">
-        <v>3.59</v>
+        <v>3.55</v>
       </c>
       <c r="D5" t="n">
-        <v>3.13</v>
+        <v>3.09</v>
       </c>
       <c r="E5" t="n">
-        <v>3.32</v>
+        <v>3.11</v>
       </c>
       <c r="F5" t="n">
-        <v>0.49</v>
+        <v>-0.22</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.1725</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="I5" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="J5" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="K5" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="L5" t="n">
-        <v>2.85</v>
+        <v>3.34</v>
       </c>
       <c r="M5" t="n">
-        <v>2.93</v>
+        <v>3.55</v>
       </c>
       <c r="N5" t="n">
-        <v>3.01</v>
+        <v>3.76</v>
       </c>
       <c r="O5" t="n">
-        <v>3.16</v>
+        <v>4.04</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -947,12 +939,14 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
@@ -960,70 +954,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="C6" t="n">
-        <v>3.55</v>
+        <v>3.14</v>
       </c>
       <c r="D6" t="n">
-        <v>3.09</v>
+        <v>2.89</v>
       </c>
       <c r="E6" t="n">
-        <v>3.11</v>
+        <v>3.01</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.22</v>
+        <v>-0.1</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.0316</v>
       </c>
       <c r="H6" t="n">
-        <v>0.46</v>
+        <v>0.25</v>
       </c>
       <c r="I6" t="n">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="J6" t="n">
-        <v>2.85</v>
+        <v>2.54</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="L6" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="M6" t="n">
         <v>3.34</v>
       </c>
-      <c r="M6" t="n">
-        <v>3.55</v>
-      </c>
       <c r="N6" t="n">
-        <v>3.76</v>
+        <v>3.46</v>
       </c>
       <c r="O6" t="n">
-        <v>4.04</v>
+        <v>4.01</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1041,10 +1035,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1066,50 +1058,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="C7" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="D7" t="n">
         <v>3.14</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.0984</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K7" t="n">
         <v>2.89</v>
       </c>
-      <c r="E7" t="n">
+      <c r="L7" t="n">
         <v>3.01</v>
       </c>
-      <c r="F7" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>-0.0316</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3.21</v>
-      </c>
       <c r="M7" t="n">
-        <v>3.34</v>
+        <v>3.13</v>
       </c>
       <c r="N7" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="O7" t="n">
-        <v>4.01</v>
+        <v>3.38</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1117,83 +1109,83 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v/>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.16</v>
+        <v>3.41</v>
       </c>
       <c r="C8" t="n">
-        <v>3.57</v>
+        <v>4.16</v>
       </c>
       <c r="D8" t="n">
-        <v>3.14</v>
+        <v>3.19</v>
       </c>
       <c r="E8" t="n">
-        <v>3.3</v>
+        <v>4.12</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3</v>
+        <v>0.82</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0984</v>
+        <v>0.2482</v>
       </c>
       <c r="H8" t="n">
-        <v>0.44</v>
+        <v>0.96</v>
       </c>
       <c r="I8" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="J8" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="K8" t="n">
-        <v>2.89</v>
+        <v>3.09</v>
       </c>
       <c r="L8" t="n">
-        <v>3.01</v>
+        <v>3.33</v>
       </c>
       <c r="M8" t="n">
-        <v>3.13</v>
+        <v>3.52</v>
       </c>
       <c r="N8" t="n">
-        <v>3.25</v>
+        <v>3.71</v>
       </c>
       <c r="O8" t="n">
-        <v>3.38</v>
+        <v>4.01</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1216,12 +1208,12 @@
       </c>
       <c r="U8" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W8" s="9" t="inlineStr">
@@ -1234,50 +1226,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.41</v>
+        <v>4.16</v>
       </c>
       <c r="C9" t="n">
-        <v>4.16</v>
+        <v>4.42</v>
       </c>
       <c r="D9" t="n">
-        <v>3.19</v>
+        <v>4.09</v>
       </c>
       <c r="E9" t="n">
-        <v>4.12</v>
+        <v>4.32</v>
       </c>
       <c r="F9" t="n">
-        <v>0.82</v>
+        <v>0.19</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.2482</v>
+        <v>0.0463</v>
       </c>
       <c r="H9" t="n">
-        <v>0.96</v>
+        <v>0.33</v>
       </c>
       <c r="I9" t="n">
-        <v>2.7</v>
+        <v>2.23</v>
       </c>
       <c r="J9" t="n">
-        <v>2.84</v>
+        <v>3.38</v>
       </c>
       <c r="K9" t="n">
-        <v>3.09</v>
+        <v>3.64</v>
       </c>
       <c r="L9" t="n">
-        <v>3.33</v>
+        <v>3.9</v>
       </c>
       <c r="M9" t="n">
-        <v>3.52</v>
+        <v>4.61</v>
       </c>
       <c r="N9" t="n">
-        <v>3.71</v>
+        <v>5.31</v>
       </c>
       <c r="O9" t="n">
-        <v>4.01</v>
+        <v>5.12</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1295,18 +1287,14 @@
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V9" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v/>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
@@ -1318,50 +1306,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.16</v>
+        <v>4.48</v>
       </c>
       <c r="C10" t="n">
-        <v>4.42</v>
+        <v>4.69</v>
       </c>
       <c r="D10" t="n">
-        <v>4.09</v>
+        <v>4.26</v>
       </c>
       <c r="E10" t="n">
-        <v>4.32</v>
+        <v>4.57</v>
       </c>
       <c r="F10" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0463</v>
+        <v>0.0582</v>
       </c>
       <c r="H10" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="I10" t="n">
-        <v>2.23</v>
+        <v>3.75</v>
       </c>
       <c r="J10" t="n">
-        <v>3.38</v>
+        <v>4.01</v>
       </c>
       <c r="K10" t="n">
-        <v>3.64</v>
+        <v>4.15</v>
       </c>
       <c r="L10" t="n">
-        <v>3.9</v>
+        <v>4.28</v>
       </c>
       <c r="M10" t="n">
-        <v>4.61</v>
+        <v>4.48</v>
       </c>
       <c r="N10" t="n">
-        <v>5.31</v>
+        <v>4.68</v>
       </c>
       <c r="O10" t="n">
-        <v>5.12</v>
+        <v>4.75</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1382,8 +1370,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U10" s="8" t="n">
-        <v/>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1398,50 +1388,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.48</v>
+        <v>4.53</v>
       </c>
       <c r="C11" t="n">
-        <v>4.69</v>
+        <v>4.68</v>
       </c>
       <c r="D11" t="n">
-        <v>4.26</v>
+        <v>4.24</v>
       </c>
       <c r="E11" t="n">
-        <v>4.57</v>
+        <v>4.58</v>
       </c>
       <c r="F11" t="n">
-        <v>0.25</v>
+        <v>0.01</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0582</v>
+        <v>0.0031</v>
       </c>
       <c r="H11" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="I11" t="n">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="J11" t="n">
-        <v>4.01</v>
+        <v>4.19</v>
       </c>
       <c r="K11" t="n">
-        <v>4.15</v>
+        <v>4.35</v>
       </c>
       <c r="L11" t="n">
-        <v>4.28</v>
+        <v>4.52</v>
       </c>
       <c r="M11" t="n">
-        <v>4.48</v>
+        <v>4.78</v>
       </c>
       <c r="N11" t="n">
-        <v>4.68</v>
+        <v>5.04</v>
       </c>
       <c r="O11" t="n">
-        <v>4.75</v>
+        <v>5.11</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1449,23 +1439,21 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1475,55 +1463,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.53</v>
+        <v>4.47</v>
       </c>
       <c r="C12" t="n">
-        <v>4.68</v>
+        <v>4.87</v>
       </c>
       <c r="D12" t="n">
-        <v>4.24</v>
+        <v>4.27</v>
       </c>
       <c r="E12" t="n">
-        <v>4.58</v>
+        <v>4.85</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01</v>
+        <v>0.27</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.059</v>
       </c>
       <c r="H12" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="I12" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="J12" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="K12" t="n">
-        <v>4.35</v>
+        <v>4.36</v>
       </c>
       <c r="L12" t="n">
         <v>4.52</v>
       </c>
       <c r="M12" t="n">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="N12" t="n">
-        <v>5.04</v>
+        <v>5.08</v>
       </c>
       <c r="O12" t="n">
-        <v>5.11</v>
+        <v>5.12</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1538,11 +1530,13 @@
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1555,59 +1549,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.47</v>
+        <v>4.87</v>
       </c>
       <c r="C13" t="n">
-        <v>4.87</v>
+        <v>5.5</v>
       </c>
       <c r="D13" t="n">
-        <v>4.27</v>
+        <v>4.76</v>
       </c>
       <c r="E13" t="n">
-        <v>4.85</v>
+        <v>5.29</v>
       </c>
       <c r="F13" t="n">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.059</v>
+        <v>0.0905</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6</v>
+        <v>0.74</v>
       </c>
       <c r="I13" t="n">
-        <v>3.8</v>
+        <v>3.66</v>
       </c>
       <c r="J13" t="n">
-        <v>4.2</v>
+        <v>4.39</v>
       </c>
       <c r="K13" t="n">
-        <v>4.36</v>
+        <v>4.55</v>
       </c>
       <c r="L13" t="n">
-        <v>4.52</v>
+        <v>4.71</v>
       </c>
       <c r="M13" t="n">
-        <v>4.8</v>
+        <v>5.15</v>
       </c>
       <c r="N13" t="n">
-        <v>5.08</v>
+        <v>5.59</v>
       </c>
       <c r="O13" t="n">
-        <v>5.12</v>
+        <v>5.47</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1615,26 +1605,26 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v/>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
@@ -1646,81 +1636,83 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.87</v>
+        <v>5.1</v>
       </c>
       <c r="C14" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="D14" t="n">
-        <v>4.76</v>
+        <v>4.07</v>
       </c>
       <c r="E14" t="n">
-        <v>5.29</v>
+        <v>4.11</v>
       </c>
       <c r="F14" t="n">
-        <v>0.44</v>
+        <v>-1.18</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0905</v>
+        <v>-0.2223</v>
       </c>
       <c r="H14" t="n">
-        <v>0.74</v>
+        <v>1.14</v>
       </c>
       <c r="I14" t="n">
-        <v>3.66</v>
+        <v>4.02</v>
       </c>
       <c r="J14" t="n">
-        <v>4.39</v>
+        <v>4.63</v>
       </c>
       <c r="K14" t="n">
-        <v>4.55</v>
+        <v>4.92</v>
       </c>
       <c r="L14" t="n">
-        <v>4.71</v>
+        <v>5.21</v>
       </c>
       <c r="M14" t="n">
-        <v>5.15</v>
+        <v>5.66</v>
       </c>
       <c r="N14" t="n">
-        <v>5.59</v>
+        <v>6.11</v>
       </c>
       <c r="O14" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
+        <v>6.23</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W14" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="V14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W14" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
@@ -1728,69 +1720,63 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.1</v>
+        <v>4.17</v>
       </c>
       <c r="C15" t="n">
-        <v>5.2</v>
+        <v>4.22</v>
       </c>
       <c r="D15" t="n">
-        <v>4.07</v>
+        <v>3.84</v>
       </c>
       <c r="E15" t="n">
-        <v>4.11</v>
+        <v>3.98</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.18</v>
+        <v>-0.13</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.2223</v>
+        <v>-0.0314</v>
       </c>
       <c r="H15" t="n">
-        <v>1.14</v>
+        <v>0.38</v>
       </c>
       <c r="I15" t="n">
-        <v>4.02</v>
+        <v>2.93</v>
       </c>
       <c r="J15" t="n">
-        <v>4.63</v>
+        <v>2.71</v>
       </c>
       <c r="K15" t="n">
-        <v>4.92</v>
+        <v>3.54</v>
       </c>
       <c r="L15" t="n">
-        <v>5.21</v>
+        <v>4.37</v>
       </c>
       <c r="M15" t="n">
-        <v>5.66</v>
+        <v>4.68</v>
       </c>
       <c r="N15" t="n">
-        <v>6.11</v>
+        <v>4.99</v>
       </c>
       <c r="O15" t="n">
-        <v>6.23</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>6.34</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1812,50 +1798,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B16" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.0959</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="L16" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="M16" t="n">
         <v>4.17</v>
       </c>
-      <c r="C16" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="D16" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="E16" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>-0.0314</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="L16" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="M16" t="n">
-        <v>4.68</v>
-      </c>
       <c r="N16" t="n">
-        <v>4.99</v>
+        <v>4.34</v>
       </c>
       <c r="O16" t="n">
-        <v>6.34</v>
+        <v>4.6</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1866,105 +1852,113 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="W16" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.08</v>
+        <v>4.45</v>
       </c>
       <c r="C17" t="n">
-        <v>4.59</v>
+        <v>4.72</v>
       </c>
       <c r="D17" t="n">
-        <v>3.8</v>
+        <v>3.56</v>
       </c>
       <c r="E17" t="n">
-        <v>4.37</v>
+        <v>3.62</v>
       </c>
       <c r="F17" t="n">
-        <v>0.38</v>
+        <v>-0.75</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0959</v>
+        <v>-0.1713</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8</v>
+        <v>1.16</v>
       </c>
       <c r="I17" t="n">
-        <v>3.46</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>3.58</v>
+        <v>3.66</v>
       </c>
       <c r="K17" t="n">
-        <v>3.79</v>
+        <v>3.97</v>
       </c>
       <c r="L17" t="n">
-        <v>4.01</v>
+        <v>4.28</v>
       </c>
       <c r="M17" t="n">
-        <v>4.17</v>
+        <v>4.76</v>
       </c>
       <c r="N17" t="n">
-        <v>4.34</v>
+        <v>5.25</v>
       </c>
       <c r="O17" t="n">
-        <v>4.6</v>
+        <v>5.39</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W17" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -1976,64 +1970,62 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.45</v>
+        <v>3.51</v>
       </c>
       <c r="C18" t="n">
-        <v>4.72</v>
+        <v>3.63</v>
       </c>
       <c r="D18" t="n">
-        <v>3.56</v>
+        <v>3.13</v>
       </c>
       <c r="E18" t="n">
-        <v>3.62</v>
+        <v>3.17</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.75</v>
+        <v>-0.45</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.1713</v>
+        <v>-0.1241</v>
       </c>
       <c r="H18" t="n">
-        <v>1.16</v>
+        <v>0.5</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
-        <v>3.66</v>
+        <v>2.2</v>
       </c>
       <c r="K18" t="n">
-        <v>3.97</v>
+        <v>3.04</v>
       </c>
       <c r="L18" t="n">
-        <v>4.28</v>
+        <v>3.88</v>
       </c>
       <c r="M18" t="n">
-        <v>4.76</v>
+        <v>4.2</v>
       </c>
       <c r="N18" t="n">
-        <v>5.25</v>
+        <v>4.51</v>
       </c>
       <c r="O18" t="n">
-        <v>5.39</v>
+        <v>5.88</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -2053,59 +2045,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.51</v>
+        <v>3.29</v>
       </c>
       <c r="C19" t="n">
-        <v>3.63</v>
+        <v>3.5</v>
       </c>
       <c r="D19" t="n">
-        <v>3.13</v>
+        <v>3.01</v>
       </c>
       <c r="E19" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.45</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.1241</v>
+        <v>-0.0208</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="I19" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="J19" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="K19" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="L19" t="n">
-        <v>3.88</v>
+        <v>3.28</v>
       </c>
       <c r="M19" t="n">
-        <v>4.2</v>
+        <v>3.42</v>
       </c>
       <c r="N19" t="n">
-        <v>4.51</v>
+        <v>3.57</v>
       </c>
       <c r="O19" t="n">
-        <v>5.88</v>
+        <v>4.14</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2113,18 +2101,18 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R19" s="6" t="n">
+        <v/>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2142,50 +2130,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="C20" t="n">
-        <v>3.5</v>
+        <v>5.65</v>
       </c>
       <c r="D20" t="n">
-        <v>3.01</v>
+        <v>3.38</v>
       </c>
       <c r="E20" t="n">
-        <v>3.1</v>
+        <v>5.28</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.07000000000000001</v>
+        <v>2.17</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.7</v>
       </c>
       <c r="H20" t="n">
-        <v>0.49</v>
+        <v>2.27</v>
       </c>
       <c r="I20" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="J20" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="K20" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="L20" t="n">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="M20" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>3.57</v>
+        <v>3.52</v>
       </c>
       <c r="O20" t="n">
-        <v>4.14</v>
+        <v>3.99</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2196,9 +2184,9 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
@@ -2206,15 +2194,19 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W20" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W20" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
@@ -2222,50 +2214,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.5</v>
+        <v>5.79</v>
       </c>
       <c r="C21" t="n">
-        <v>5.65</v>
+        <v>7.83</v>
       </c>
       <c r="D21" t="n">
-        <v>3.38</v>
+        <v>3.73</v>
       </c>
       <c r="E21" t="n">
-        <v>5.28</v>
+        <v>4.35</v>
       </c>
       <c r="F21" t="n">
-        <v>2.17</v>
+        <v>-0.92</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.7</v>
+        <v>-0.1746</v>
       </c>
       <c r="H21" t="n">
-        <v>2.27</v>
+        <v>4.1</v>
       </c>
       <c r="I21" t="n">
-        <v>2.51</v>
+        <v>1.11</v>
       </c>
       <c r="J21" t="n">
-        <v>2.54</v>
+        <v>3.39</v>
       </c>
       <c r="K21" t="n">
-        <v>2.86</v>
+        <v>4.14</v>
       </c>
       <c r="L21" t="n">
-        <v>3.18</v>
+        <v>4.9</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>6.41</v>
       </c>
       <c r="N21" t="n">
-        <v>3.52</v>
+        <v>7.93</v>
       </c>
       <c r="O21" t="n">
-        <v>3.99</v>
+        <v>7.92</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2273,12 +2265,14 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
@@ -2286,70 +2280,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5.79</v>
+        <v>3.71</v>
       </c>
       <c r="C22" t="n">
-        <v>7.83</v>
+        <v>3.74</v>
       </c>
       <c r="D22" t="n">
-        <v>3.73</v>
+        <v>3.15</v>
       </c>
       <c r="E22" t="n">
-        <v>4.35</v>
+        <v>3.42</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.92</v>
+        <v>-0.93</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.1746</v>
+        <v>-0.2141</v>
       </c>
       <c r="H22" t="n">
-        <v>4.1</v>
+        <v>0.58</v>
       </c>
       <c r="I22" t="n">
-        <v>1.11</v>
+        <v>-0.37</v>
       </c>
       <c r="J22" t="n">
-        <v>3.39</v>
+        <v>-0.46</v>
       </c>
       <c r="K22" t="n">
-        <v>4.14</v>
+        <v>2.3</v>
       </c>
       <c r="L22" t="n">
-        <v>4.9</v>
+        <v>5.07</v>
       </c>
       <c r="M22" t="n">
-        <v>6.41</v>
+        <v>6.4</v>
       </c>
       <c r="N22" t="n">
-        <v>7.93</v>
+        <v>7.74</v>
       </c>
       <c r="O22" t="n">
-        <v>7.92</v>
+        <v>11.93</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2367,10 +2361,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2385,57 +2377,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-0.0523</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="L23" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="M23" t="n">
         <v>3.71</v>
       </c>
-      <c r="C23" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="D23" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="E23" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="F23" t="n">
-        <v>-0.93</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>-0.2141</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I23" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="J23" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="L23" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="M23" t="n">
-        <v>6.4</v>
-      </c>
       <c r="N23" t="n">
-        <v>7.74</v>
+        <v>3.99</v>
       </c>
       <c r="O23" t="n">
-        <v>11.93</v>
+        <v>4.32</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2476,60 +2468,62 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="C24" t="n">
-        <v>3.32</v>
+        <v>3.17</v>
       </c>
       <c r="D24" t="n">
-        <v>3.06</v>
+        <v>2.92</v>
       </c>
       <c r="E24" t="n">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.18</v>
+        <v>-0.2</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0523</v>
+        <v>-0.0604</v>
       </c>
       <c r="H24" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="I24" t="n">
-        <v>2.57</v>
+        <v>2.79</v>
       </c>
       <c r="J24" t="n">
-        <v>2.83</v>
+        <v>3.01</v>
       </c>
       <c r="K24" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="L24" t="n">
-        <v>3.43</v>
+        <v>3.21</v>
       </c>
       <c r="M24" t="n">
-        <v>3.71</v>
+        <v>3.37</v>
       </c>
       <c r="N24" t="n">
-        <v>3.99</v>
+        <v>3.53</v>
       </c>
       <c r="O24" t="n">
-        <v>4.32</v>
+        <v>3.58</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S24" s="7" t="inlineStr">
@@ -2560,50 +2554,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B25" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>-0.0617</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="L25" t="n">
         <v>3.05</v>
       </c>
-      <c r="C25" t="n">
+      <c r="M25" t="n">
         <v>3.17</v>
       </c>
-      <c r="D25" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="E25" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>-0.0604</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="J25" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="L25" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="M25" t="n">
-        <v>3.37</v>
-      </c>
       <c r="N25" t="n">
-        <v>3.53</v>
+        <v>3.3</v>
       </c>
       <c r="O25" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2623,8 +2617,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T25" s="8" t="n">
-        <v/>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2639,84 +2635,82 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.24</v>
+        <v>2.93</v>
       </c>
       <c r="C26" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="D26" t="n">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="E26" t="n">
-        <v>2.86</v>
+        <v>3.19</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.19</v>
+        <v>0.33</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0617</v>
+        <v>0.1144</v>
       </c>
       <c r="H26" t="n">
-        <v>0.48</v>
+        <v>0.41</v>
       </c>
       <c r="I26" t="n">
-        <v>2.67</v>
+        <v>2.3</v>
       </c>
       <c r="J26" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="K26" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="L26" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="M26" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="N26" t="n">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="O26" t="n">
-        <v>3.42</v>
+        <v>3.73</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
@@ -2725,59 +2719,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="C27" t="n">
-        <v>3.28</v>
+        <v>3.49</v>
       </c>
       <c r="D27" t="n">
-        <v>2.87</v>
+        <v>2.96</v>
       </c>
       <c r="E27" t="n">
-        <v>3.19</v>
+        <v>3.13</v>
       </c>
       <c r="F27" t="n">
-        <v>0.33</v>
+        <v>-0.06</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.1144</v>
+        <v>-0.0173</v>
       </c>
       <c r="H27" t="n">
-        <v>0.41</v>
+        <v>0.53</v>
       </c>
       <c r="I27" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="J27" t="n">
-        <v>2.3</v>
+        <v>2.83</v>
       </c>
       <c r="K27" t="n">
-        <v>2.62</v>
+        <v>2.98</v>
       </c>
       <c r="L27" t="n">
-        <v>2.94</v>
+        <v>3.13</v>
       </c>
       <c r="M27" t="n">
-        <v>3.1</v>
+        <v>3.39</v>
       </c>
       <c r="N27" t="n">
-        <v>3.26</v>
+        <v>3.66</v>
       </c>
       <c r="O27" t="n">
-        <v>3.73</v>
+        <v>3.69</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2785,12 +2775,14 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
@@ -2798,10 +2790,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2811,55 +2801,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="C28" t="n">
-        <v>3.49</v>
+        <v>3.27</v>
       </c>
       <c r="D28" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="E28" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0173</v>
+        <v>-0.0115</v>
       </c>
       <c r="H28" t="n">
-        <v>0.53</v>
+        <v>0.35</v>
       </c>
       <c r="I28" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="J28" t="n">
-        <v>2.83</v>
+        <v>2.55</v>
       </c>
       <c r="K28" t="n">
-        <v>2.98</v>
+        <v>2.86</v>
       </c>
       <c r="L28" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="M28" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>3.66</v>
+        <v>3.62</v>
       </c>
       <c r="O28" t="n">
-        <v>3.69</v>
+        <v>4.03</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2867,20 +2861,16 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2895,66 +2885,68 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3.18</v>
+        <v>3.11</v>
       </c>
       <c r="C29" t="n">
-        <v>3.27</v>
+        <v>3.15</v>
       </c>
       <c r="D29" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="E29" t="n">
         <v>3.1</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0115</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="I29" t="n">
-        <v>2.43</v>
+        <v>2.58</v>
       </c>
       <c r="J29" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="K29" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="L29" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="N29" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="O29" t="n">
         <v>3.62</v>
       </c>
-      <c r="O29" t="n">
-        <v>4.03</v>
-      </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
@@ -2977,63 +2969,65 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.11</v>
+        <v>3.06</v>
       </c>
       <c r="C30" t="n">
-        <v>3.15</v>
+        <v>3.06</v>
       </c>
       <c r="D30" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="E30" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0</v>
+        <v>-0.0953</v>
       </c>
       <c r="H30" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="I30" t="n">
         <v>2.58</v>
       </c>
       <c r="J30" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="K30" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="L30" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="M30" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="N30" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="O30" t="n">
         <v>3.44</v>
       </c>
-      <c r="O30" t="n">
-        <v>3.62</v>
-      </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
@@ -3042,7 +3036,7 @@
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3054,76 +3048,70 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W30" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3.06</v>
+        <v>2.84</v>
       </c>
       <c r="C31" t="n">
-        <v>3.06</v>
+        <v>2.89</v>
       </c>
       <c r="D31" t="n">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
       <c r="E31" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3</v>
+        <v>-0.15</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0953</v>
+        <v>-0.0543</v>
       </c>
       <c r="H31" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="I31" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="J31" t="n">
-        <v>2.85</v>
+        <v>2.46</v>
       </c>
       <c r="K31" t="n">
-        <v>2.95</v>
+        <v>2.66</v>
       </c>
       <c r="L31" t="n">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="M31" t="n">
-        <v>3.24</v>
+        <v>2.94</v>
       </c>
       <c r="N31" t="n">
-        <v>3.43</v>
+        <v>3.02</v>
       </c>
       <c r="O31" t="n">
-        <v>3.44</v>
+        <v>3.33</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S31" s="7" t="inlineStr">
@@ -3150,50 +3138,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.84</v>
+        <v>2.69</v>
       </c>
       <c r="C32" t="n">
-        <v>2.89</v>
+        <v>2.72</v>
       </c>
       <c r="D32" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="E32" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.15</v>
+        <v>0.03</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0543</v>
+        <v>0.0098</v>
       </c>
       <c r="H32" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="I32" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="J32" t="n">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="K32" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="L32" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="M32" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="N32" t="n">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="O32" t="n">
-        <v>3.33</v>
+        <v>3.15</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3201,14 +3189,12 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R32" s="6" t="n">
+        <v/>
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3225,72 +3211,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>2.69</v>
       </c>
       <c r="C33" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="D33" t="n">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="E33" t="n">
-        <v>2.67</v>
+        <v>2.52</v>
       </c>
       <c r="F33" t="n">
-        <v>0.03</v>
+        <v>-0.15</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0098</v>
+        <v>-0.0565</v>
       </c>
       <c r="H33" t="n">
-        <v>0.16</v>
+        <v>0.27</v>
       </c>
       <c r="I33" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="J33" t="n">
-        <v>2.33</v>
+        <v>2.53</v>
       </c>
       <c r="K33" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="L33" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="M33" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="N33" t="n">
         <v>2.85</v>
       </c>
       <c r="O33" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3312,83 +3308,81 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.69</v>
+        <v>2.51</v>
       </c>
       <c r="C34" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="D34" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="E34" t="n">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.15</v>
+        <v>0.26</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0565</v>
+        <v>0.1019</v>
       </c>
       <c r="H34" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="J34" t="n">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="K34" t="n">
-        <v>2.59</v>
+        <v>2.39</v>
       </c>
       <c r="L34" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="M34" t="n">
         <v>2.66</v>
       </c>
-      <c r="M34" t="n">
-        <v>2.75</v>
-      </c>
       <c r="N34" t="n">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="O34" t="n">
-        <v>2.88</v>
+        <v>3.03</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W34" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -3400,50 +3394,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B35" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>-0.0083</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J35" t="n">
         <v>2.51</v>
       </c>
-      <c r="C35" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="D35" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="E35" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>0.1019</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I35" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2.2</v>
-      </c>
       <c r="K35" t="n">
-        <v>2.39</v>
+        <v>2.61</v>
       </c>
       <c r="L35" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="M35" t="n">
-        <v>2.66</v>
+        <v>2.95</v>
       </c>
       <c r="N35" t="n">
-        <v>2.74</v>
+        <v>3.18</v>
       </c>
       <c r="O35" t="n">
-        <v>3.03</v>
+        <v>3.16</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3456,18 +3450,14 @@
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3486,50 +3476,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="C36" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="D36" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="E36" t="n">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.02</v>
+        <v>0.2</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0083</v>
+        <v>0.0736</v>
       </c>
       <c r="H36" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="I36" t="n">
-        <v>2.14</v>
+        <v>2.47</v>
       </c>
       <c r="J36" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="K36" t="n">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="L36" t="n">
-        <v>2.72</v>
+        <v>2.77</v>
       </c>
       <c r="M36" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N36" t="n">
         <v>2.95</v>
       </c>
-      <c r="N36" t="n">
-        <v>3.18</v>
-      </c>
       <c r="O36" t="n">
-        <v>3.16</v>
+        <v>3.09</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3542,14 +3532,18 @@
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3559,59 +3553,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="C37" t="n">
-        <v>2.98</v>
+        <v>3.14</v>
       </c>
       <c r="D37" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="E37" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2</v>
+        <v>-0.05</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0736</v>
+        <v>-0.0179</v>
       </c>
       <c r="H37" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="I37" t="n">
-        <v>2.47</v>
+        <v>2.52</v>
       </c>
       <c r="J37" t="n">
-        <v>2.54</v>
+        <v>2.78</v>
       </c>
       <c r="K37" t="n">
-        <v>2.65</v>
+        <v>2.84</v>
       </c>
       <c r="L37" t="n">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="M37" t="n">
-        <v>2.86</v>
+        <v>3.08</v>
       </c>
       <c r="N37" t="n">
-        <v>2.95</v>
+        <v>3.24</v>
       </c>
       <c r="O37" t="n">
-        <v>3.09</v>
+        <v>3.21</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3622,9 +3612,9 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
@@ -3632,10 +3622,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U37" s="8" t="n">
+        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3645,55 +3633,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="C38" t="n">
-        <v>3.14</v>
+        <v>3.39</v>
       </c>
       <c r="D38" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="E38" t="n">
-        <v>2.91</v>
+        <v>3.29</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.05</v>
+        <v>0.38</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.1318</v>
       </c>
       <c r="H38" t="n">
-        <v>0.25</v>
+        <v>0.53</v>
       </c>
       <c r="I38" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="J38" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K38" t="n">
         <v>2.78</v>
       </c>
-      <c r="K38" t="n">
-        <v>2.84</v>
-      </c>
       <c r="L38" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="M38" t="n">
-        <v>3.08</v>
+        <v>3.03</v>
       </c>
       <c r="N38" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="O38" t="n">
-        <v>3.21</v>
+        <v>3.39</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3704,9 +3696,9 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
@@ -3714,11 +3706,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v/>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W38" s="9" t="inlineStr">
         <is>
@@ -3734,50 +3730,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.9</v>
+        <v>3.34</v>
       </c>
       <c r="C39" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="D39" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="E39" t="n">
-        <v>3.29</v>
+        <v>3.23</v>
       </c>
       <c r="F39" t="n">
-        <v>0.38</v>
+        <v>-0.06</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.1318</v>
+        <v>-0.0185</v>
       </c>
       <c r="H39" t="n">
-        <v>0.53</v>
+        <v>0.3</v>
       </c>
       <c r="I39" t="n">
-        <v>2.64</v>
+        <v>2.33</v>
       </c>
       <c r="J39" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="K39" t="n">
-        <v>2.78</v>
+        <v>3.02</v>
       </c>
       <c r="L39" t="n">
-        <v>2.96</v>
+        <v>3.21</v>
       </c>
       <c r="M39" t="n">
-        <v>3.03</v>
+        <v>3.56</v>
       </c>
       <c r="N39" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="O39" t="n">
-        <v>3.39</v>
+        <v>3.92</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3790,23 +3786,17 @@
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v/>
       </c>
       <c r="W39" s="9" t="inlineStr">
         <is>
@@ -3822,50 +3812,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3.34</v>
+        <v>3.18</v>
       </c>
       <c r="C40" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="D40" t="n">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="E40" t="n">
-        <v>3.23</v>
+        <v>3.12</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.06</v>
+        <v>-0.11</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0185</v>
+        <v>-0.0338</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
       <c r="I40" t="n">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="J40" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="K40" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="L40" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="M40" t="n">
-        <v>3.56</v>
+        <v>3.38</v>
       </c>
       <c r="N40" t="n">
-        <v>3.9</v>
+        <v>3.52</v>
       </c>
       <c r="O40" t="n">
-        <v>3.92</v>
+        <v>3.69</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3873,12 +3863,14 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3897,57 +3889,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="C41" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="D41" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="E41" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.11</v>
+        <v>0.08</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0338</v>
+        <v>0.025</v>
       </c>
       <c r="H41" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="I41" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="J41" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="K41" t="n">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="L41" t="n">
-        <v>3.24</v>
+        <v>3.13</v>
       </c>
       <c r="M41" t="n">
-        <v>3.38</v>
+        <v>3.23</v>
       </c>
       <c r="N41" t="n">
-        <v>3.52</v>
+        <v>3.33</v>
       </c>
       <c r="O41" t="n">
-        <v>3.69</v>
+        <v>3.47</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3955,19 +3947,19 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
@@ -3981,57 +3973,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3.09</v>
+        <v>3.28</v>
       </c>
       <c r="C42" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="D42" t="n">
-        <v>3.02</v>
+        <v>3.14</v>
       </c>
       <c r="E42" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="F42" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.025</v>
+        <v>0.0103</v>
       </c>
       <c r="H42" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="I42" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="J42" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="K42" t="n">
-        <v>3.01</v>
+        <v>3.06</v>
       </c>
       <c r="L42" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="M42" t="n">
-        <v>3.23</v>
+        <v>3.34</v>
       </c>
       <c r="N42" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="O42" t="n">
-        <v>3.47</v>
+        <v>3.58</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4044,12 +4036,12 @@
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U42" s="8" t="n">
@@ -4063,59 +4055,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>3.28</v>
       </c>
       <c r="C43" t="n">
-        <v>3.44</v>
+        <v>3.33</v>
       </c>
       <c r="D43" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="E43" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="F43" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0103</v>
+        <v>0.0043</v>
       </c>
       <c r="H43" t="n">
-        <v>0.31</v>
+        <v>0.18</v>
       </c>
       <c r="I43" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="J43" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="K43" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="L43" t="n">
-        <v>3.18</v>
+        <v>3.26</v>
       </c>
       <c r="M43" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="N43" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="O43" t="n">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4126,15 +4114,13 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4147,72 +4133,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="C44" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>-0.094</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="J44" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="K44" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="L44" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="M44" t="n">
         <v>3.33</v>
       </c>
-      <c r="D44" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="E44" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>0.0043</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="I44" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="J44" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K44" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="L44" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="M44" t="n">
-        <v>3.38</v>
-      </c>
       <c r="N44" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="O44" t="n">
         <v>3.51</v>
       </c>
-      <c r="O44" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4220,9 +4218,9 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W44" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
@@ -4234,75 +4232,67 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3.21</v>
+        <v>2.93</v>
       </c>
       <c r="C45" t="n">
-        <v>3.36</v>
+        <v>2.97</v>
       </c>
       <c r="D45" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="E45" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.3</v>
+        <v>-0.03</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.094</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="H45" t="n">
-        <v>0.48</v>
+        <v>0.14</v>
       </c>
       <c r="I45" t="n">
-        <v>2.97</v>
+        <v>2.39</v>
       </c>
       <c r="J45" t="n">
-        <v>3.07</v>
+        <v>2.37</v>
       </c>
       <c r="K45" t="n">
-        <v>3.16</v>
+        <v>2.7</v>
       </c>
       <c r="L45" t="n">
-        <v>3.24</v>
+        <v>3.03</v>
       </c>
       <c r="M45" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="N45" t="n">
         <v>3.33</v>
       </c>
-      <c r="N45" t="n">
-        <v>3.42</v>
-      </c>
       <c r="O45" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3.84</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4315,59 +4305,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="C46" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="D46" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="E46" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-0.0137</v>
       </c>
       <c r="H46" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="I46" t="n">
-        <v>2.39</v>
+        <v>2.68</v>
       </c>
       <c r="J46" t="n">
-        <v>2.37</v>
+        <v>2.77</v>
       </c>
       <c r="K46" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="L46" t="n">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="M46" t="n">
-        <v>3.18</v>
+        <v>2.98</v>
       </c>
       <c r="N46" t="n">
-        <v>3.33</v>
+        <v>3.06</v>
       </c>
       <c r="O46" t="n">
-        <v>3.84</v>
+        <v>3.11</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4375,16 +4361,20 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T46" s="8" t="n">
-        <v/>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4397,76 +4387,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="C47" t="n">
-        <v>2.99</v>
+        <v>2.84</v>
       </c>
       <c r="D47" t="n">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="E47" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.04</v>
+        <v>-0.12</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0432</v>
       </c>
       <c r="H47" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="I47" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="J47" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="K47" t="n">
-        <v>2.84</v>
+        <v>2.79</v>
       </c>
       <c r="L47" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="M47" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="N47" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="O47" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
+        <v>3.15</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4479,69 +4475,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="C48" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="D48" t="n">
         <v>2.62</v>
       </c>
       <c r="E48" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.12</v>
+        <v>-0.09</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0432</v>
+        <v>-0.0309</v>
       </c>
       <c r="H48" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="I48" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="J48" t="n">
-        <v>2.69</v>
+        <v>2.54</v>
       </c>
       <c r="K48" t="n">
-        <v>2.79</v>
+        <v>2.64</v>
       </c>
       <c r="L48" t="n">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="M48" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="N48" t="n">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="O48" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3.05</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v/>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
@@ -4572,50 +4560,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="C49" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="D49" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="E49" t="n">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0309</v>
+        <v>0.0267</v>
       </c>
       <c r="H49" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="I49" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="J49" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="K49" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="L49" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="M49" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="N49" t="n">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="O49" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4623,19 +4611,19 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
       <c r="U49" s="8" t="n">
         <v/>
       </c>
@@ -4647,55 +4635,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="C50" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="D50" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="E50" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="F50" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0267</v>
+        <v>0.0146</v>
       </c>
       <c r="H50" t="n">
-        <v>0.13</v>
+        <v>0.24</v>
       </c>
       <c r="I50" t="n">
-        <v>2.42</v>
+        <v>2.57</v>
       </c>
       <c r="J50" t="n">
-        <v>2.44</v>
+        <v>2.59</v>
       </c>
       <c r="K50" t="n">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="L50" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="M50" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="N50" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="O50" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4703,21 +4695,25 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4729,57 +4725,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="C51" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="D51" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="E51" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="F51" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0146</v>
+        <v>0.0415</v>
       </c>
       <c r="H51" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="I51" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="J51" t="n">
-        <v>2.59</v>
+        <v>2.54</v>
       </c>
       <c r="K51" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="L51" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="M51" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="N51" t="n">
-        <v>2.84</v>
+        <v>3.02</v>
       </c>
       <c r="O51" t="n">
-        <v>2.96</v>
+        <v>3.11</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4787,25 +4783,21 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R51" s="6" t="n">
+        <v/>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4817,57 +4809,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="C52" t="n">
-        <v>2.94</v>
+        <v>3.03</v>
       </c>
       <c r="D52" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="E52" t="n">
-        <v>2.89</v>
+        <v>2.97</v>
       </c>
       <c r="F52" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0415</v>
+        <v>0.0301</v>
       </c>
       <c r="H52" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="I52" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="J52" t="n">
-        <v>2.54</v>
+        <v>2.67</v>
       </c>
       <c r="K52" t="n">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="L52" t="n">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="M52" t="n">
-        <v>2.89</v>
+        <v>3.01</v>
       </c>
       <c r="N52" t="n">
-        <v>3.02</v>
+        <v>3.17</v>
       </c>
       <c r="O52" t="n">
-        <v>3.11</v>
+        <v>3.19</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4908,70 +4900,72 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B53" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="C53" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>-0.0484</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I53" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K53" t="n">
         <v>2.88</v>
       </c>
-      <c r="C53" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="D53" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="E53" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>0.0301</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="I53" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="J53" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="K53" t="n">
-        <v>2.76</v>
-      </c>
       <c r="L53" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="M53" t="n">
-        <v>3.01</v>
+        <v>3.07</v>
       </c>
       <c r="N53" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="O53" t="n">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
+      <c r="Q53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
       <c r="U53" s="8" t="n">
         <v/>
       </c>
@@ -4983,81 +4977,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="C54" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="D54" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="E54" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.14</v>
+        <v>0.08</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0484</v>
+        <v>0.0286</v>
       </c>
       <c r="H54" t="n">
-        <v>0.26</v>
+        <v>0.13</v>
       </c>
       <c r="I54" t="n">
-        <v>2.64</v>
+        <v>2.49</v>
       </c>
       <c r="J54" t="n">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="K54" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="L54" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="M54" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N54" t="n">
         <v>3.07</v>
       </c>
-      <c r="N54" t="n">
-        <v>3.19</v>
-      </c>
       <c r="O54" t="n">
-        <v>3.22</v>
+        <v>3.27</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
       <c r="U54" s="8" t="n">
         <v/>
       </c>
@@ -5069,55 +5057,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="C55" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="E55" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.0975</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I55" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K55" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="L55" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="M55" t="n">
         <v>2.98</v>
       </c>
-      <c r="D55" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E55" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>0.0286</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I55" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="J55" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K55" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L55" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="M55" t="n">
-        <v>2.96</v>
-      </c>
       <c r="N55" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="O55" t="n">
-        <v>3.27</v>
+        <v>3.11</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5125,8 +5117,10 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
@@ -5135,73 +5129,77 @@
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V55" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W55" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W55" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="C56" t="n">
-        <v>3.32</v>
+        <v>3.16</v>
       </c>
       <c r="D56" t="n">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="E56" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="F56" t="n">
-        <v>0.28</v>
+        <v>-0.16</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0975</v>
+        <v>-0.0504</v>
       </c>
       <c r="H56" t="n">
-        <v>0.5</v>
+        <v>0.24</v>
       </c>
       <c r="I56" t="n">
-        <v>2.71</v>
+        <v>2.32</v>
       </c>
       <c r="J56" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="K56" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="L56" t="n">
-        <v>2.91</v>
+        <v>3.13</v>
       </c>
       <c r="M56" t="n">
-        <v>2.98</v>
+        <v>3.45</v>
       </c>
       <c r="N56" t="n">
-        <v>3.04</v>
+        <v>3.76</v>
       </c>
       <c r="O56" t="n">
-        <v>3.11</v>
+        <v>3.82</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5211,29 +5209,23 @@
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V56" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V56" s="8" t="n">
+        <v/>
+      </c>
       <c r="W56" s="9" t="inlineStr">
         <is>
           <t>多方</t>
@@ -5241,57 +5233,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="C57" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D57" t="n">
+        <v>3</v>
+      </c>
+      <c r="E57" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I57" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="J57" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L57" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="M57" t="n">
         <v>3.16</v>
       </c>
-      <c r="D57" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E57" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="F57" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>-0.0504</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="I57" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="J57" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="K57" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="L57" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="M57" t="n">
-        <v>3.45</v>
-      </c>
       <c r="N57" t="n">
-        <v>3.76</v>
+        <v>3.28</v>
       </c>
       <c r="O57" t="n">
-        <v>3.82</v>
+        <v>3.4</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5299,22 +5291,24 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
@@ -5323,91 +5317,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="C58" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D58" t="n">
-        <v>3</v>
-      </c>
-      <c r="E58" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="I58" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="J58" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="K58" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="L58" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="M58" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="N58" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="O58" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -5253,13 +5253,13 @@
         <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="F57" t="n">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.061</v>
+        <v>0.0422</v>
       </c>
       <c r="H57" t="n">
         <v>0.3</v>
@@ -5301,12 +5301,12 @@
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="V57" s="8" t="n">

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -5256,10 +5256,10 @@
         <v>3.16</v>
       </c>
       <c r="F57" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0422</v>
+        <v>0.0409</v>
       </c>
       <c r="H57" t="n">
         <v>0.3</v>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -659,25 +659,25 @@
         <v>0.31</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="J2" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="K2" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="L2" t="n">
         <v>2.99</v>
       </c>
       <c r="M2" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="O2" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -700,8 +700,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -713,7 +715,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -5253,13 +5255,13 @@
         <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>3.16</v>
+        <v>3.22</v>
       </c>
       <c r="F57" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0409</v>
+        <v>0.061</v>
       </c>
       <c r="H57" t="n">
         <v>0.3</v>
@@ -5301,14 +5303,14 @@
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
@@ -5318,6 +5320,88 @@
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="C58" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="E58" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.0165</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K58" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="L58" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="M58" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="O58" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>0.31</v>
       </c>
       <c r="I2" t="n">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="J2" t="n">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="K2" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="L2" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="M2" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="N2" t="n">
-        <v>3.16</v>
+        <v>3.13</v>
       </c>
       <c r="O2" t="n">
-        <v>3.43</v>
+        <v>3.34</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5331,22 +5331,22 @@
         <v>3.17</v>
       </c>
       <c r="C58" t="n">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
       <c r="D58" t="n">
         <v>3.09</v>
       </c>
       <c r="E58" t="n">
-        <v>3.17</v>
+        <v>3.33</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.05</v>
+        <v>0.11</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0165</v>
+        <v>0.0329</v>
       </c>
       <c r="H58" t="n">
-        <v>0.11</v>
+        <v>0.24</v>
       </c>
       <c r="I58" t="n">
         <v>2.7</v>
@@ -5378,13 +5378,15 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5397,11 +5399,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>0.31</v>
       </c>
       <c r="I2" t="n">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="J2" t="n">
-        <v>2.69</v>
+        <v>2.76</v>
       </c>
       <c r="K2" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="L2" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="M2" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="N2" t="n">
-        <v>3.13</v>
+        <v>3.09</v>
       </c>
       <c r="O2" t="n">
-        <v>3.34</v>
+        <v>3.23</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5337,13 +5337,13 @@
         <v>3.09</v>
       </c>
       <c r="E58" t="n">
-        <v>3.33</v>
+        <v>3.28</v>
       </c>
       <c r="F58" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0329</v>
+        <v>0.0183</v>
       </c>
       <c r="H58" t="n">
         <v>0.24</v>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -5337,13 +5337,13 @@
         <v>3.09</v>
       </c>
       <c r="E58" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="F58" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0183</v>
+        <v>0.0146</v>
       </c>
       <c r="H58" t="n">
         <v>0.24</v>
@@ -5380,13 +5380,11 @@
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>0.31</v>
       </c>
       <c r="I2" t="n">
-        <v>2.73</v>
+        <v>2.79</v>
       </c>
       <c r="J2" t="n">
-        <v>2.76</v>
+        <v>2.83</v>
       </c>
       <c r="K2" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="L2" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="M2" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="N2" t="n">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
       <c r="O2" t="n">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -705,8 +705,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -5337,13 +5339,13 @@
         <v>3.09</v>
       </c>
       <c r="E58" t="n">
-        <v>3.27</v>
+        <v>3.21</v>
       </c>
       <c r="F58" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0146</v>
+        <v>-0.0025</v>
       </c>
       <c r="H58" t="n">
         <v>0.24</v>
@@ -5397,7 +5399,11 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="C2" t="n">
-        <v>3.17</v>
+        <v>2.97</v>
       </c>
       <c r="D2" t="n">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="E2" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="F2" t="n">
         <v>-0.05</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.018</v>
+        <v>-0.0184</v>
       </c>
       <c r="H2" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.79</v>
+        <v>2.55</v>
       </c>
       <c r="J2" t="n">
-        <v>2.83</v>
+        <v>2.51</v>
       </c>
       <c r="K2" t="n">
-        <v>2.89</v>
+        <v>2.73</v>
       </c>
       <c r="L2" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="M2" t="n">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="N2" t="n">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="O2" t="n">
-        <v>3.1</v>
+        <v>3.48</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -695,20 +695,14 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -717,57 +711,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.91</v>
+        <v>3.15</v>
       </c>
       <c r="C3" t="n">
-        <v>2.97</v>
+        <v>3.59</v>
       </c>
       <c r="D3" t="n">
-        <v>2.77</v>
+        <v>3.13</v>
       </c>
       <c r="E3" t="n">
-        <v>2.84</v>
+        <v>3.32</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.05</v>
+        <v>0.49</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0184</v>
+        <v>0.1725</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="I3" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="J3" t="n">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
       <c r="K3" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="L3" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="M3" t="n">
-        <v>3.04</v>
+        <v>2.93</v>
       </c>
       <c r="N3" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="O3" t="n">
-        <v>3.48</v>
+        <v>3.16</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -775,83 +769,83 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
-      </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="C4" t="n">
-        <v>3.59</v>
+        <v>3.55</v>
       </c>
       <c r="D4" t="n">
-        <v>3.13</v>
+        <v>3.09</v>
       </c>
       <c r="E4" t="n">
-        <v>3.32</v>
+        <v>3.11</v>
       </c>
       <c r="F4" t="n">
-        <v>0.49</v>
+        <v>-0.22</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.1725</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="I4" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="J4" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="K4" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="L4" t="n">
-        <v>2.85</v>
+        <v>3.34</v>
       </c>
       <c r="M4" t="n">
-        <v>2.93</v>
+        <v>3.55</v>
       </c>
       <c r="N4" t="n">
-        <v>3.01</v>
+        <v>3.76</v>
       </c>
       <c r="O4" t="n">
-        <v>3.16</v>
+        <v>4.04</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -859,12 +853,14 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
@@ -872,70 +868,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="C5" t="n">
-        <v>3.55</v>
+        <v>3.14</v>
       </c>
       <c r="D5" t="n">
-        <v>3.09</v>
+        <v>2.89</v>
       </c>
       <c r="E5" t="n">
-        <v>3.11</v>
+        <v>3.01</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.22</v>
+        <v>-0.1</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.0316</v>
       </c>
       <c r="H5" t="n">
-        <v>0.46</v>
+        <v>0.25</v>
       </c>
       <c r="I5" t="n">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="J5" t="n">
-        <v>2.85</v>
+        <v>2.54</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="L5" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="M5" t="n">
         <v>3.34</v>
       </c>
-      <c r="M5" t="n">
-        <v>3.55</v>
-      </c>
       <c r="N5" t="n">
-        <v>3.76</v>
+        <v>3.46</v>
       </c>
       <c r="O5" t="n">
-        <v>4.04</v>
+        <v>4.01</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -953,10 +949,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -978,50 +972,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="C6" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="D6" t="n">
         <v>3.14</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.0984</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K6" t="n">
         <v>2.89</v>
       </c>
-      <c r="E6" t="n">
+      <c r="L6" t="n">
         <v>3.01</v>
       </c>
-      <c r="F6" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>-0.0316</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="L6" t="n">
-        <v>3.21</v>
-      </c>
       <c r="M6" t="n">
-        <v>3.34</v>
+        <v>3.13</v>
       </c>
       <c r="N6" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="O6" t="n">
-        <v>4.01</v>
+        <v>3.38</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1029,83 +1023,83 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v/>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.16</v>
+        <v>3.41</v>
       </c>
       <c r="C7" t="n">
-        <v>3.57</v>
+        <v>4.16</v>
       </c>
       <c r="D7" t="n">
-        <v>3.14</v>
+        <v>3.19</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3</v>
+        <v>4.12</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3</v>
+        <v>0.82</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0984</v>
+        <v>0.2482</v>
       </c>
       <c r="H7" t="n">
-        <v>0.44</v>
+        <v>0.96</v>
       </c>
       <c r="I7" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="J7" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="K7" t="n">
-        <v>2.89</v>
+        <v>3.09</v>
       </c>
       <c r="L7" t="n">
-        <v>3.01</v>
+        <v>3.33</v>
       </c>
       <c r="M7" t="n">
-        <v>3.13</v>
+        <v>3.52</v>
       </c>
       <c r="N7" t="n">
-        <v>3.25</v>
+        <v>3.71</v>
       </c>
       <c r="O7" t="n">
-        <v>3.38</v>
+        <v>4.01</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1128,12 +1122,12 @@
       </c>
       <c r="U7" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W7" s="9" t="inlineStr">
@@ -1146,50 +1140,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.41</v>
+        <v>4.16</v>
       </c>
       <c r="C8" t="n">
-        <v>4.16</v>
+        <v>4.42</v>
       </c>
       <c r="D8" t="n">
-        <v>3.19</v>
+        <v>4.09</v>
       </c>
       <c r="E8" t="n">
-        <v>4.12</v>
+        <v>4.32</v>
       </c>
       <c r="F8" t="n">
-        <v>0.82</v>
+        <v>0.19</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.2482</v>
+        <v>0.0463</v>
       </c>
       <c r="H8" t="n">
-        <v>0.96</v>
+        <v>0.33</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>2.23</v>
       </c>
       <c r="J8" t="n">
-        <v>2.84</v>
+        <v>3.38</v>
       </c>
       <c r="K8" t="n">
-        <v>3.09</v>
+        <v>3.64</v>
       </c>
       <c r="L8" t="n">
-        <v>3.33</v>
+        <v>3.9</v>
       </c>
       <c r="M8" t="n">
-        <v>3.52</v>
+        <v>4.61</v>
       </c>
       <c r="N8" t="n">
-        <v>3.71</v>
+        <v>5.31</v>
       </c>
       <c r="O8" t="n">
-        <v>4.01</v>
+        <v>5.12</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1207,18 +1201,14 @@
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
@@ -1230,50 +1220,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.16</v>
+        <v>4.48</v>
       </c>
       <c r="C9" t="n">
-        <v>4.42</v>
+        <v>4.69</v>
       </c>
       <c r="D9" t="n">
-        <v>4.09</v>
+        <v>4.26</v>
       </c>
       <c r="E9" t="n">
-        <v>4.32</v>
+        <v>4.57</v>
       </c>
       <c r="F9" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0463</v>
+        <v>0.0582</v>
       </c>
       <c r="H9" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="I9" t="n">
-        <v>2.23</v>
+        <v>3.75</v>
       </c>
       <c r="J9" t="n">
-        <v>3.38</v>
+        <v>4.01</v>
       </c>
       <c r="K9" t="n">
-        <v>3.64</v>
+        <v>4.15</v>
       </c>
       <c r="L9" t="n">
-        <v>3.9</v>
+        <v>4.28</v>
       </c>
       <c r="M9" t="n">
-        <v>4.61</v>
+        <v>4.48</v>
       </c>
       <c r="N9" t="n">
-        <v>5.31</v>
+        <v>4.68</v>
       </c>
       <c r="O9" t="n">
-        <v>5.12</v>
+        <v>4.75</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1294,8 +1284,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U9" s="8" t="n">
-        <v/>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
@@ -1310,50 +1302,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.48</v>
+        <v>4.53</v>
       </c>
       <c r="C10" t="n">
-        <v>4.69</v>
+        <v>4.68</v>
       </c>
       <c r="D10" t="n">
-        <v>4.26</v>
+        <v>4.24</v>
       </c>
       <c r="E10" t="n">
-        <v>4.57</v>
+        <v>4.58</v>
       </c>
       <c r="F10" t="n">
-        <v>0.25</v>
+        <v>0.01</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0582</v>
+        <v>0.0031</v>
       </c>
       <c r="H10" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="I10" t="n">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="J10" t="n">
-        <v>4.01</v>
+        <v>4.19</v>
       </c>
       <c r="K10" t="n">
-        <v>4.15</v>
+        <v>4.35</v>
       </c>
       <c r="L10" t="n">
-        <v>4.28</v>
+        <v>4.52</v>
       </c>
       <c r="M10" t="n">
-        <v>4.48</v>
+        <v>4.78</v>
       </c>
       <c r="N10" t="n">
-        <v>4.68</v>
+        <v>5.04</v>
       </c>
       <c r="O10" t="n">
-        <v>4.75</v>
+        <v>5.11</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1361,23 +1353,21 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1387,55 +1377,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.53</v>
+        <v>4.47</v>
       </c>
       <c r="C11" t="n">
-        <v>4.68</v>
+        <v>4.87</v>
       </c>
       <c r="D11" t="n">
-        <v>4.24</v>
+        <v>4.27</v>
       </c>
       <c r="E11" t="n">
-        <v>4.58</v>
+        <v>4.85</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01</v>
+        <v>0.27</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.059</v>
       </c>
       <c r="H11" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="I11" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="J11" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="K11" t="n">
-        <v>4.35</v>
+        <v>4.36</v>
       </c>
       <c r="L11" t="n">
         <v>4.52</v>
       </c>
       <c r="M11" t="n">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="N11" t="n">
-        <v>5.04</v>
+        <v>5.08</v>
       </c>
       <c r="O11" t="n">
-        <v>5.11</v>
+        <v>5.12</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1450,11 +1444,13 @@
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1467,59 +1463,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.47</v>
+        <v>4.87</v>
       </c>
       <c r="C12" t="n">
-        <v>4.87</v>
+        <v>5.5</v>
       </c>
       <c r="D12" t="n">
-        <v>4.27</v>
+        <v>4.76</v>
       </c>
       <c r="E12" t="n">
-        <v>4.85</v>
+        <v>5.29</v>
       </c>
       <c r="F12" t="n">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.059</v>
+        <v>0.0905</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6</v>
+        <v>0.74</v>
       </c>
       <c r="I12" t="n">
-        <v>3.8</v>
+        <v>3.66</v>
       </c>
       <c r="J12" t="n">
-        <v>4.2</v>
+        <v>4.39</v>
       </c>
       <c r="K12" t="n">
-        <v>4.36</v>
+        <v>4.55</v>
       </c>
       <c r="L12" t="n">
-        <v>4.52</v>
+        <v>4.71</v>
       </c>
       <c r="M12" t="n">
-        <v>4.8</v>
+        <v>5.15</v>
       </c>
       <c r="N12" t="n">
-        <v>5.08</v>
+        <v>5.59</v>
       </c>
       <c r="O12" t="n">
-        <v>5.12</v>
+        <v>5.47</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1527,26 +1519,26 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v/>
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
@@ -1558,81 +1550,83 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.87</v>
+        <v>5.1</v>
       </c>
       <c r="C13" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="D13" t="n">
-        <v>4.76</v>
+        <v>4.07</v>
       </c>
       <c r="E13" t="n">
-        <v>5.29</v>
+        <v>4.11</v>
       </c>
       <c r="F13" t="n">
-        <v>0.44</v>
+        <v>-1.18</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0905</v>
+        <v>-0.2223</v>
       </c>
       <c r="H13" t="n">
-        <v>0.74</v>
+        <v>1.14</v>
       </c>
       <c r="I13" t="n">
-        <v>3.66</v>
+        <v>4.02</v>
       </c>
       <c r="J13" t="n">
-        <v>4.39</v>
+        <v>4.63</v>
       </c>
       <c r="K13" t="n">
-        <v>4.55</v>
+        <v>4.92</v>
       </c>
       <c r="L13" t="n">
-        <v>4.71</v>
+        <v>5.21</v>
       </c>
       <c r="M13" t="n">
-        <v>5.15</v>
+        <v>5.66</v>
       </c>
       <c r="N13" t="n">
-        <v>5.59</v>
+        <v>6.11</v>
       </c>
       <c r="O13" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
+        <v>6.23</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W13" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="V13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W13" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr"/>
@@ -1640,69 +1634,63 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.1</v>
+        <v>4.17</v>
       </c>
       <c r="C14" t="n">
-        <v>5.2</v>
+        <v>4.22</v>
       </c>
       <c r="D14" t="n">
-        <v>4.07</v>
+        <v>3.84</v>
       </c>
       <c r="E14" t="n">
-        <v>4.11</v>
+        <v>3.98</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.18</v>
+        <v>-0.13</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.2223</v>
+        <v>-0.0314</v>
       </c>
       <c r="H14" t="n">
-        <v>1.14</v>
+        <v>0.38</v>
       </c>
       <c r="I14" t="n">
-        <v>4.02</v>
+        <v>2.93</v>
       </c>
       <c r="J14" t="n">
-        <v>4.63</v>
+        <v>2.71</v>
       </c>
       <c r="K14" t="n">
-        <v>4.92</v>
+        <v>3.54</v>
       </c>
       <c r="L14" t="n">
-        <v>5.21</v>
+        <v>4.37</v>
       </c>
       <c r="M14" t="n">
-        <v>5.66</v>
+        <v>4.68</v>
       </c>
       <c r="N14" t="n">
-        <v>6.11</v>
+        <v>4.99</v>
       </c>
       <c r="O14" t="n">
-        <v>6.23</v>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>6.34</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1724,50 +1712,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B15" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.0959</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="L15" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="M15" t="n">
         <v>4.17</v>
       </c>
-      <c r="C15" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="D15" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="E15" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>-0.0314</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="L15" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="M15" t="n">
-        <v>4.68</v>
-      </c>
       <c r="N15" t="n">
-        <v>4.99</v>
+        <v>4.34</v>
       </c>
       <c r="O15" t="n">
-        <v>6.34</v>
+        <v>4.6</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1778,105 +1766,113 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="W15" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.08</v>
+        <v>4.45</v>
       </c>
       <c r="C16" t="n">
-        <v>4.59</v>
+        <v>4.72</v>
       </c>
       <c r="D16" t="n">
-        <v>3.8</v>
+        <v>3.56</v>
       </c>
       <c r="E16" t="n">
-        <v>4.37</v>
+        <v>3.62</v>
       </c>
       <c r="F16" t="n">
-        <v>0.38</v>
+        <v>-0.75</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0959</v>
+        <v>-0.1713</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8</v>
+        <v>1.16</v>
       </c>
       <c r="I16" t="n">
-        <v>3.46</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>3.58</v>
+        <v>3.66</v>
       </c>
       <c r="K16" t="n">
-        <v>3.79</v>
+        <v>3.97</v>
       </c>
       <c r="L16" t="n">
-        <v>4.01</v>
+        <v>4.28</v>
       </c>
       <c r="M16" t="n">
-        <v>4.17</v>
+        <v>4.76</v>
       </c>
       <c r="N16" t="n">
-        <v>4.34</v>
+        <v>5.25</v>
       </c>
       <c r="O16" t="n">
-        <v>4.6</v>
+        <v>5.39</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W16" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -1888,64 +1884,62 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.45</v>
+        <v>3.51</v>
       </c>
       <c r="C17" t="n">
-        <v>4.72</v>
+        <v>3.63</v>
       </c>
       <c r="D17" t="n">
-        <v>3.56</v>
+        <v>3.13</v>
       </c>
       <c r="E17" t="n">
-        <v>3.62</v>
+        <v>3.17</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.75</v>
+        <v>-0.45</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.1713</v>
+        <v>-0.1241</v>
       </c>
       <c r="H17" t="n">
-        <v>1.16</v>
+        <v>0.5</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J17" t="n">
-        <v>3.66</v>
+        <v>2.2</v>
       </c>
       <c r="K17" t="n">
-        <v>3.97</v>
+        <v>3.04</v>
       </c>
       <c r="L17" t="n">
-        <v>4.28</v>
+        <v>3.88</v>
       </c>
       <c r="M17" t="n">
-        <v>4.76</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>5.25</v>
+        <v>4.51</v>
       </c>
       <c r="O17" t="n">
-        <v>5.39</v>
+        <v>5.88</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -1965,59 +1959,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.51</v>
+        <v>3.29</v>
       </c>
       <c r="C18" t="n">
-        <v>3.63</v>
+        <v>3.5</v>
       </c>
       <c r="D18" t="n">
-        <v>3.13</v>
+        <v>3.01</v>
       </c>
       <c r="E18" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.45</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.1241</v>
+        <v>-0.0208</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="J18" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="K18" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="L18" t="n">
-        <v>3.88</v>
+        <v>3.28</v>
       </c>
       <c r="M18" t="n">
-        <v>4.2</v>
+        <v>3.42</v>
       </c>
       <c r="N18" t="n">
-        <v>4.51</v>
+        <v>3.57</v>
       </c>
       <c r="O18" t="n">
-        <v>5.88</v>
+        <v>4.14</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2025,18 +2015,18 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R18" s="6" t="n">
+        <v/>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2054,50 +2044,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="C19" t="n">
-        <v>3.5</v>
+        <v>5.65</v>
       </c>
       <c r="D19" t="n">
-        <v>3.01</v>
+        <v>3.38</v>
       </c>
       <c r="E19" t="n">
-        <v>3.1</v>
+        <v>5.28</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.07000000000000001</v>
+        <v>2.17</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.7</v>
       </c>
       <c r="H19" t="n">
-        <v>0.49</v>
+        <v>2.27</v>
       </c>
       <c r="I19" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="J19" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="K19" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="L19" t="n">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="M19" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>3.57</v>
+        <v>3.52</v>
       </c>
       <c r="O19" t="n">
-        <v>4.14</v>
+        <v>3.99</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2108,9 +2098,9 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
@@ -2118,15 +2108,19 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W19" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W19" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
@@ -2134,50 +2128,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.5</v>
+        <v>5.79</v>
       </c>
       <c r="C20" t="n">
-        <v>5.65</v>
+        <v>7.83</v>
       </c>
       <c r="D20" t="n">
-        <v>3.38</v>
+        <v>3.73</v>
       </c>
       <c r="E20" t="n">
-        <v>5.28</v>
+        <v>4.35</v>
       </c>
       <c r="F20" t="n">
-        <v>2.17</v>
+        <v>-0.92</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.7</v>
+        <v>-0.1746</v>
       </c>
       <c r="H20" t="n">
-        <v>2.27</v>
+        <v>4.1</v>
       </c>
       <c r="I20" t="n">
-        <v>2.51</v>
+        <v>1.11</v>
       </c>
       <c r="J20" t="n">
-        <v>2.54</v>
+        <v>3.39</v>
       </c>
       <c r="K20" t="n">
-        <v>2.86</v>
+        <v>4.14</v>
       </c>
       <c r="L20" t="n">
-        <v>3.18</v>
+        <v>4.9</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>6.41</v>
       </c>
       <c r="N20" t="n">
-        <v>3.52</v>
+        <v>7.93</v>
       </c>
       <c r="O20" t="n">
-        <v>3.99</v>
+        <v>7.92</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2185,12 +2179,14 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
@@ -2198,70 +2194,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.79</v>
+        <v>3.71</v>
       </c>
       <c r="C21" t="n">
-        <v>7.83</v>
+        <v>3.74</v>
       </c>
       <c r="D21" t="n">
-        <v>3.73</v>
+        <v>3.15</v>
       </c>
       <c r="E21" t="n">
-        <v>4.35</v>
+        <v>3.42</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.92</v>
+        <v>-0.93</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.1746</v>
+        <v>-0.2141</v>
       </c>
       <c r="H21" t="n">
-        <v>4.1</v>
+        <v>0.58</v>
       </c>
       <c r="I21" t="n">
-        <v>1.11</v>
+        <v>-0.37</v>
       </c>
       <c r="J21" t="n">
-        <v>3.39</v>
+        <v>-0.46</v>
       </c>
       <c r="K21" t="n">
-        <v>4.14</v>
+        <v>2.3</v>
       </c>
       <c r="L21" t="n">
-        <v>4.9</v>
+        <v>5.07</v>
       </c>
       <c r="M21" t="n">
-        <v>6.41</v>
+        <v>6.4</v>
       </c>
       <c r="N21" t="n">
-        <v>7.93</v>
+        <v>7.74</v>
       </c>
       <c r="O21" t="n">
-        <v>7.92</v>
+        <v>11.93</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2279,10 +2275,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T21" s="8" t="n">
+        <v/>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2297,57 +2291,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-0.0523</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="L22" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="M22" t="n">
         <v>3.71</v>
       </c>
-      <c r="C22" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="D22" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="E22" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-0.93</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>-0.2141</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I22" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="J22" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="L22" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="M22" t="n">
-        <v>6.4</v>
-      </c>
       <c r="N22" t="n">
-        <v>7.74</v>
+        <v>3.99</v>
       </c>
       <c r="O22" t="n">
-        <v>11.93</v>
+        <v>4.32</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2388,60 +2382,62 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="C23" t="n">
-        <v>3.32</v>
+        <v>3.17</v>
       </c>
       <c r="D23" t="n">
-        <v>3.06</v>
+        <v>2.92</v>
       </c>
       <c r="E23" t="n">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.18</v>
+        <v>-0.2</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0523</v>
+        <v>-0.0604</v>
       </c>
       <c r="H23" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="I23" t="n">
-        <v>2.57</v>
+        <v>2.79</v>
       </c>
       <c r="J23" t="n">
-        <v>2.83</v>
+        <v>3.01</v>
       </c>
       <c r="K23" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="L23" t="n">
-        <v>3.43</v>
+        <v>3.21</v>
       </c>
       <c r="M23" t="n">
-        <v>3.71</v>
+        <v>3.37</v>
       </c>
       <c r="N23" t="n">
-        <v>3.99</v>
+        <v>3.53</v>
       </c>
       <c r="O23" t="n">
-        <v>4.32</v>
+        <v>3.58</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
@@ -2472,50 +2468,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B24" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>-0.0617</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="L24" t="n">
         <v>3.05</v>
       </c>
-      <c r="C24" t="n">
+      <c r="M24" t="n">
         <v>3.17</v>
       </c>
-      <c r="D24" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="E24" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>-0.0604</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="K24" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="L24" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="M24" t="n">
-        <v>3.37</v>
-      </c>
       <c r="N24" t="n">
-        <v>3.53</v>
+        <v>3.3</v>
       </c>
       <c r="O24" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2535,8 +2531,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T24" s="8" t="n">
-        <v/>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2551,84 +2549,82 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.24</v>
+        <v>2.93</v>
       </c>
       <c r="C25" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="D25" t="n">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="E25" t="n">
-        <v>2.86</v>
+        <v>3.19</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.19</v>
+        <v>0.33</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0617</v>
+        <v>0.1144</v>
       </c>
       <c r="H25" t="n">
-        <v>0.48</v>
+        <v>0.41</v>
       </c>
       <c r="I25" t="n">
-        <v>2.67</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="K25" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="L25" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="M25" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="O25" t="n">
-        <v>3.42</v>
+        <v>3.73</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
@@ -2637,59 +2633,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="C26" t="n">
-        <v>3.28</v>
+        <v>3.49</v>
       </c>
       <c r="D26" t="n">
-        <v>2.87</v>
+        <v>2.96</v>
       </c>
       <c r="E26" t="n">
-        <v>3.19</v>
+        <v>3.13</v>
       </c>
       <c r="F26" t="n">
-        <v>0.33</v>
+        <v>-0.06</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.1144</v>
+        <v>-0.0173</v>
       </c>
       <c r="H26" t="n">
-        <v>0.41</v>
+        <v>0.53</v>
       </c>
       <c r="I26" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="J26" t="n">
-        <v>2.3</v>
+        <v>2.83</v>
       </c>
       <c r="K26" t="n">
-        <v>2.62</v>
+        <v>2.98</v>
       </c>
       <c r="L26" t="n">
-        <v>2.94</v>
+        <v>3.13</v>
       </c>
       <c r="M26" t="n">
-        <v>3.1</v>
+        <v>3.39</v>
       </c>
       <c r="N26" t="n">
-        <v>3.26</v>
+        <v>3.66</v>
       </c>
       <c r="O26" t="n">
-        <v>3.73</v>
+        <v>3.69</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2697,12 +2689,14 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
@@ -2710,10 +2704,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2723,55 +2715,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="C27" t="n">
-        <v>3.49</v>
+        <v>3.27</v>
       </c>
       <c r="D27" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="E27" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0173</v>
+        <v>-0.0115</v>
       </c>
       <c r="H27" t="n">
-        <v>0.53</v>
+        <v>0.35</v>
       </c>
       <c r="I27" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="J27" t="n">
-        <v>2.83</v>
+        <v>2.55</v>
       </c>
       <c r="K27" t="n">
-        <v>2.98</v>
+        <v>2.86</v>
       </c>
       <c r="L27" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="M27" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>3.66</v>
+        <v>3.62</v>
       </c>
       <c r="O27" t="n">
-        <v>3.69</v>
+        <v>4.03</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2779,20 +2775,16 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2807,66 +2799,68 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.18</v>
+        <v>3.11</v>
       </c>
       <c r="C28" t="n">
-        <v>3.27</v>
+        <v>3.15</v>
       </c>
       <c r="D28" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="E28" t="n">
         <v>3.1</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0115</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="I28" t="n">
-        <v>2.43</v>
+        <v>2.58</v>
       </c>
       <c r="J28" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="K28" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="L28" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="N28" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="O28" t="n">
         <v>3.62</v>
       </c>
-      <c r="O28" t="n">
-        <v>4.03</v>
-      </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
@@ -2889,63 +2883,65 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3.11</v>
+        <v>3.06</v>
       </c>
       <c r="C29" t="n">
-        <v>3.15</v>
+        <v>3.06</v>
       </c>
       <c r="D29" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="E29" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0</v>
+        <v>-0.0953</v>
       </c>
       <c r="H29" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="I29" t="n">
         <v>2.58</v>
       </c>
       <c r="J29" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="K29" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="L29" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="M29" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="N29" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="O29" t="n">
         <v>3.44</v>
       </c>
-      <c r="O29" t="n">
-        <v>3.62</v>
-      </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
@@ -2954,7 +2950,7 @@
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2966,76 +2962,70 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W29" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.06</v>
+        <v>2.84</v>
       </c>
       <c r="C30" t="n">
-        <v>3.06</v>
+        <v>2.89</v>
       </c>
       <c r="D30" t="n">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
       <c r="E30" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.3</v>
+        <v>-0.15</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0953</v>
+        <v>-0.0543</v>
       </c>
       <c r="H30" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="I30" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="J30" t="n">
-        <v>2.85</v>
+        <v>2.46</v>
       </c>
       <c r="K30" t="n">
-        <v>2.95</v>
+        <v>2.66</v>
       </c>
       <c r="L30" t="n">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="M30" t="n">
-        <v>3.24</v>
+        <v>2.94</v>
       </c>
       <c r="N30" t="n">
-        <v>3.43</v>
+        <v>3.02</v>
       </c>
       <c r="O30" t="n">
-        <v>3.44</v>
+        <v>3.33</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S30" s="7" t="inlineStr">
@@ -3062,50 +3052,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.84</v>
+        <v>2.69</v>
       </c>
       <c r="C31" t="n">
-        <v>2.89</v>
+        <v>2.72</v>
       </c>
       <c r="D31" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="E31" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.15</v>
+        <v>0.03</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0543</v>
+        <v>0.0098</v>
       </c>
       <c r="H31" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="I31" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="J31" t="n">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="K31" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="L31" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="M31" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="N31" t="n">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="O31" t="n">
-        <v>3.33</v>
+        <v>3.15</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3113,14 +3103,12 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R31" s="6" t="n">
+        <v/>
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3137,72 +3125,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>2.69</v>
       </c>
       <c r="C32" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="D32" t="n">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="E32" t="n">
-        <v>2.67</v>
+        <v>2.52</v>
       </c>
       <c r="F32" t="n">
-        <v>0.03</v>
+        <v>-0.15</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0098</v>
+        <v>-0.0565</v>
       </c>
       <c r="H32" t="n">
-        <v>0.16</v>
+        <v>0.27</v>
       </c>
       <c r="I32" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="J32" t="n">
-        <v>2.33</v>
+        <v>2.53</v>
       </c>
       <c r="K32" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="L32" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="M32" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="N32" t="n">
         <v>2.85</v>
       </c>
       <c r="O32" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3224,83 +3222,81 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.69</v>
+        <v>2.51</v>
       </c>
       <c r="C33" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="D33" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="E33" t="n">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.15</v>
+        <v>0.26</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0565</v>
+        <v>0.1019</v>
       </c>
       <c r="H33" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="I33" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="J33" t="n">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="K33" t="n">
-        <v>2.59</v>
+        <v>2.39</v>
       </c>
       <c r="L33" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="M33" t="n">
         <v>2.66</v>
       </c>
-      <c r="M33" t="n">
-        <v>2.75</v>
-      </c>
       <c r="N33" t="n">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="O33" t="n">
-        <v>2.88</v>
+        <v>3.03</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W33" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -3312,50 +3308,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B34" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>-0.0083</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J34" t="n">
         <v>2.51</v>
       </c>
-      <c r="C34" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="D34" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="E34" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="G34" s="5" t="n">
-        <v>0.1019</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I34" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2.2</v>
-      </c>
       <c r="K34" t="n">
-        <v>2.39</v>
+        <v>2.61</v>
       </c>
       <c r="L34" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="M34" t="n">
-        <v>2.66</v>
+        <v>2.95</v>
       </c>
       <c r="N34" t="n">
-        <v>2.74</v>
+        <v>3.18</v>
       </c>
       <c r="O34" t="n">
-        <v>3.03</v>
+        <v>3.16</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3368,18 +3364,14 @@
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3398,50 +3390,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="C35" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="D35" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="E35" t="n">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.02</v>
+        <v>0.2</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0083</v>
+        <v>0.0736</v>
       </c>
       <c r="H35" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="I35" t="n">
-        <v>2.14</v>
+        <v>2.47</v>
       </c>
       <c r="J35" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="K35" t="n">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="L35" t="n">
-        <v>2.72</v>
+        <v>2.77</v>
       </c>
       <c r="M35" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N35" t="n">
         <v>2.95</v>
       </c>
-      <c r="N35" t="n">
-        <v>3.18</v>
-      </c>
       <c r="O35" t="n">
-        <v>3.16</v>
+        <v>3.09</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3454,14 +3446,18 @@
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3471,59 +3467,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="C36" t="n">
-        <v>2.98</v>
+        <v>3.14</v>
       </c>
       <c r="D36" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="E36" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="F36" t="n">
-        <v>0.2</v>
+        <v>-0.05</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0736</v>
+        <v>-0.0179</v>
       </c>
       <c r="H36" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="I36" t="n">
-        <v>2.47</v>
+        <v>2.52</v>
       </c>
       <c r="J36" t="n">
-        <v>2.54</v>
+        <v>2.78</v>
       </c>
       <c r="K36" t="n">
-        <v>2.65</v>
+        <v>2.84</v>
       </c>
       <c r="L36" t="n">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="M36" t="n">
-        <v>2.86</v>
+        <v>3.08</v>
       </c>
       <c r="N36" t="n">
-        <v>2.95</v>
+        <v>3.24</v>
       </c>
       <c r="O36" t="n">
-        <v>3.09</v>
+        <v>3.21</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3534,9 +3526,9 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
@@ -3544,10 +3536,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U36" s="8" t="n">
+        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3557,55 +3547,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="C37" t="n">
-        <v>3.14</v>
+        <v>3.39</v>
       </c>
       <c r="D37" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="E37" t="n">
-        <v>2.91</v>
+        <v>3.29</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.05</v>
+        <v>0.38</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.1318</v>
       </c>
       <c r="H37" t="n">
-        <v>0.25</v>
+        <v>0.53</v>
       </c>
       <c r="I37" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="J37" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K37" t="n">
         <v>2.78</v>
       </c>
-      <c r="K37" t="n">
-        <v>2.84</v>
-      </c>
       <c r="L37" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="M37" t="n">
-        <v>3.08</v>
+        <v>3.03</v>
       </c>
       <c r="N37" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="O37" t="n">
-        <v>3.21</v>
+        <v>3.39</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3616,9 +3610,9 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
@@ -3626,11 +3620,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v/>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
@@ -3646,50 +3644,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.9</v>
+        <v>3.34</v>
       </c>
       <c r="C38" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="D38" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.29</v>
+        <v>3.23</v>
       </c>
       <c r="F38" t="n">
-        <v>0.38</v>
+        <v>-0.06</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.1318</v>
+        <v>-0.0185</v>
       </c>
       <c r="H38" t="n">
-        <v>0.53</v>
+        <v>0.3</v>
       </c>
       <c r="I38" t="n">
-        <v>2.64</v>
+        <v>2.33</v>
       </c>
       <c r="J38" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="K38" t="n">
-        <v>2.78</v>
+        <v>3.02</v>
       </c>
       <c r="L38" t="n">
-        <v>2.96</v>
+        <v>3.21</v>
       </c>
       <c r="M38" t="n">
-        <v>3.03</v>
+        <v>3.56</v>
       </c>
       <c r="N38" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="O38" t="n">
-        <v>3.39</v>
+        <v>3.92</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3702,23 +3700,17 @@
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v/>
       </c>
       <c r="W38" s="9" t="inlineStr">
         <is>
@@ -3734,50 +3726,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3.34</v>
+        <v>3.18</v>
       </c>
       <c r="C39" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="D39" t="n">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="E39" t="n">
-        <v>3.23</v>
+        <v>3.12</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.06</v>
+        <v>-0.11</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0185</v>
+        <v>-0.0338</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
       <c r="I39" t="n">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="J39" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="K39" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="L39" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="M39" t="n">
-        <v>3.56</v>
+        <v>3.38</v>
       </c>
       <c r="N39" t="n">
-        <v>3.9</v>
+        <v>3.52</v>
       </c>
       <c r="O39" t="n">
-        <v>3.92</v>
+        <v>3.69</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3785,12 +3777,14 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3809,57 +3803,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="C40" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="D40" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="E40" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.11</v>
+        <v>0.08</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0338</v>
+        <v>0.025</v>
       </c>
       <c r="H40" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="I40" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="J40" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="K40" t="n">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="L40" t="n">
-        <v>3.24</v>
+        <v>3.13</v>
       </c>
       <c r="M40" t="n">
-        <v>3.38</v>
+        <v>3.23</v>
       </c>
       <c r="N40" t="n">
-        <v>3.52</v>
+        <v>3.33</v>
       </c>
       <c r="O40" t="n">
-        <v>3.69</v>
+        <v>3.47</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3867,19 +3861,19 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
@@ -3893,57 +3887,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3.09</v>
+        <v>3.28</v>
       </c>
       <c r="C41" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="D41" t="n">
-        <v>3.02</v>
+        <v>3.14</v>
       </c>
       <c r="E41" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="F41" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.025</v>
+        <v>0.0103</v>
       </c>
       <c r="H41" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="I41" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="J41" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="K41" t="n">
-        <v>3.01</v>
+        <v>3.06</v>
       </c>
       <c r="L41" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="M41" t="n">
-        <v>3.23</v>
+        <v>3.34</v>
       </c>
       <c r="N41" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="O41" t="n">
-        <v>3.47</v>
+        <v>3.58</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3956,12 +3950,12 @@
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U41" s="8" t="n">
@@ -3975,59 +3969,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>3.28</v>
       </c>
       <c r="C42" t="n">
-        <v>3.44</v>
+        <v>3.33</v>
       </c>
       <c r="D42" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="E42" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="F42" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0103</v>
+        <v>0.0043</v>
       </c>
       <c r="H42" t="n">
-        <v>0.31</v>
+        <v>0.18</v>
       </c>
       <c r="I42" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="J42" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="K42" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="L42" t="n">
-        <v>3.18</v>
+        <v>3.26</v>
       </c>
       <c r="M42" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="N42" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="O42" t="n">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4038,15 +4028,13 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4059,72 +4047,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="C43" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>-0.094</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="J43" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="L43" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="M43" t="n">
         <v>3.33</v>
       </c>
-      <c r="D43" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="E43" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>0.0043</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="I43" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="J43" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K43" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="L43" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="M43" t="n">
-        <v>3.38</v>
-      </c>
       <c r="N43" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="O43" t="n">
         <v>3.51</v>
       </c>
-      <c r="O43" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4132,9 +4132,9 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W43" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
@@ -4146,75 +4146,67 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3.21</v>
+        <v>2.93</v>
       </c>
       <c r="C44" t="n">
-        <v>3.36</v>
+        <v>2.97</v>
       </c>
       <c r="D44" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="E44" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.3</v>
+        <v>-0.03</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.094</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="H44" t="n">
-        <v>0.48</v>
+        <v>0.14</v>
       </c>
       <c r="I44" t="n">
-        <v>2.97</v>
+        <v>2.39</v>
       </c>
       <c r="J44" t="n">
-        <v>3.07</v>
+        <v>2.37</v>
       </c>
       <c r="K44" t="n">
-        <v>3.16</v>
+        <v>2.7</v>
       </c>
       <c r="L44" t="n">
-        <v>3.24</v>
+        <v>3.03</v>
       </c>
       <c r="M44" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="N44" t="n">
         <v>3.33</v>
       </c>
-      <c r="N44" t="n">
-        <v>3.42</v>
-      </c>
       <c r="O44" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3.84</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4227,59 +4219,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="C45" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="D45" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="E45" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-0.0137</v>
       </c>
       <c r="H45" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="I45" t="n">
-        <v>2.39</v>
+        <v>2.68</v>
       </c>
       <c r="J45" t="n">
-        <v>2.37</v>
+        <v>2.77</v>
       </c>
       <c r="K45" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="L45" t="n">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="M45" t="n">
-        <v>3.18</v>
+        <v>2.98</v>
       </c>
       <c r="N45" t="n">
-        <v>3.33</v>
+        <v>3.06</v>
       </c>
       <c r="O45" t="n">
-        <v>3.84</v>
+        <v>3.11</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4287,16 +4275,20 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T45" s="8" t="n">
-        <v/>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4309,76 +4301,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="C46" t="n">
-        <v>2.99</v>
+        <v>2.84</v>
       </c>
       <c r="D46" t="n">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="E46" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.04</v>
+        <v>-0.12</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0432</v>
       </c>
       <c r="H46" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="I46" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="J46" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="K46" t="n">
-        <v>2.84</v>
+        <v>2.79</v>
       </c>
       <c r="L46" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="M46" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="N46" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="O46" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
+        <v>3.15</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4391,69 +4389,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="C47" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="D47" t="n">
         <v>2.62</v>
       </c>
       <c r="E47" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.12</v>
+        <v>-0.09</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0432</v>
+        <v>-0.0309</v>
       </c>
       <c r="H47" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="I47" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="J47" t="n">
-        <v>2.69</v>
+        <v>2.54</v>
       </c>
       <c r="K47" t="n">
-        <v>2.79</v>
+        <v>2.64</v>
       </c>
       <c r="L47" t="n">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="M47" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="N47" t="n">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="O47" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3.05</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
@@ -4484,50 +4474,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="C48" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="D48" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="E48" t="n">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0309</v>
+        <v>0.0267</v>
       </c>
       <c r="H48" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="I48" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="J48" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="K48" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="L48" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="M48" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="N48" t="n">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="O48" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4535,19 +4525,19 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
       <c r="U48" s="8" t="n">
         <v/>
       </c>
@@ -4559,55 +4549,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="C49" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="D49" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="E49" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="F49" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0267</v>
+        <v>0.0146</v>
       </c>
       <c r="H49" t="n">
-        <v>0.13</v>
+        <v>0.24</v>
       </c>
       <c r="I49" t="n">
-        <v>2.42</v>
+        <v>2.57</v>
       </c>
       <c r="J49" t="n">
-        <v>2.44</v>
+        <v>2.59</v>
       </c>
       <c r="K49" t="n">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="L49" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="M49" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="N49" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="O49" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4615,21 +4609,25 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4641,57 +4639,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="C50" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="D50" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="E50" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="F50" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0146</v>
+        <v>0.0415</v>
       </c>
       <c r="H50" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="I50" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="J50" t="n">
-        <v>2.59</v>
+        <v>2.54</v>
       </c>
       <c r="K50" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="L50" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="M50" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="N50" t="n">
-        <v>2.84</v>
+        <v>3.02</v>
       </c>
       <c r="O50" t="n">
-        <v>2.96</v>
+        <v>3.11</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4699,25 +4697,21 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R50" s="6" t="n">
+        <v/>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4729,57 +4723,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="C51" t="n">
-        <v>2.94</v>
+        <v>3.03</v>
       </c>
       <c r="D51" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="E51" t="n">
-        <v>2.89</v>
+        <v>2.97</v>
       </c>
       <c r="F51" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0415</v>
+        <v>0.0301</v>
       </c>
       <c r="H51" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="I51" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="J51" t="n">
-        <v>2.54</v>
+        <v>2.67</v>
       </c>
       <c r="K51" t="n">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="L51" t="n">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="M51" t="n">
-        <v>2.89</v>
+        <v>3.01</v>
       </c>
       <c r="N51" t="n">
-        <v>3.02</v>
+        <v>3.17</v>
       </c>
       <c r="O51" t="n">
-        <v>3.11</v>
+        <v>3.19</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4820,70 +4814,72 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B52" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="C52" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>-0.0484</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I52" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K52" t="n">
         <v>2.88</v>
       </c>
-      <c r="C52" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="D52" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="E52" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>0.0301</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="I52" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="J52" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="K52" t="n">
-        <v>2.76</v>
-      </c>
       <c r="L52" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="M52" t="n">
-        <v>3.01</v>
+        <v>3.07</v>
       </c>
       <c r="N52" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="O52" t="n">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
+      <c r="Q52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
       <c r="U52" s="8" t="n">
         <v/>
       </c>
@@ -4895,81 +4891,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="C53" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="D53" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="E53" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.14</v>
+        <v>0.08</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0484</v>
+        <v>0.0286</v>
       </c>
       <c r="H53" t="n">
-        <v>0.26</v>
+        <v>0.13</v>
       </c>
       <c r="I53" t="n">
-        <v>2.64</v>
+        <v>2.49</v>
       </c>
       <c r="J53" t="n">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="K53" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="L53" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="M53" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N53" t="n">
         <v>3.07</v>
       </c>
-      <c r="N53" t="n">
-        <v>3.19</v>
-      </c>
       <c r="O53" t="n">
-        <v>3.22</v>
+        <v>3.27</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
       <c r="U53" s="8" t="n">
         <v/>
       </c>
@@ -4981,55 +4971,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="C54" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="E54" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.0975</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I54" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K54" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="L54" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="M54" t="n">
         <v>2.98</v>
       </c>
-      <c r="D54" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E54" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>0.0286</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I54" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="J54" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K54" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L54" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="M54" t="n">
-        <v>2.96</v>
-      </c>
       <c r="N54" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="O54" t="n">
-        <v>3.27</v>
+        <v>3.11</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5037,8 +5031,10 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
@@ -5047,73 +5043,77 @@
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V54" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W54" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W54" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="C55" t="n">
-        <v>3.32</v>
+        <v>3.16</v>
       </c>
       <c r="D55" t="n">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="E55" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="F55" t="n">
-        <v>0.28</v>
+        <v>-0.16</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0975</v>
+        <v>-0.0504</v>
       </c>
       <c r="H55" t="n">
-        <v>0.5</v>
+        <v>0.24</v>
       </c>
       <c r="I55" t="n">
-        <v>2.71</v>
+        <v>2.32</v>
       </c>
       <c r="J55" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="K55" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="L55" t="n">
-        <v>2.91</v>
+        <v>3.13</v>
       </c>
       <c r="M55" t="n">
-        <v>2.98</v>
+        <v>3.45</v>
       </c>
       <c r="N55" t="n">
-        <v>3.04</v>
+        <v>3.76</v>
       </c>
       <c r="O55" t="n">
-        <v>3.11</v>
+        <v>3.82</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5123,29 +5123,23 @@
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V55" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V55" s="8" t="n">
+        <v/>
+      </c>
       <c r="W55" s="9" t="inlineStr">
         <is>
           <t>多方</t>
@@ -5153,57 +5147,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="C56" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E56" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I56" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="J56" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K56" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L56" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="M56" t="n">
         <v>3.16</v>
       </c>
-      <c r="D56" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E56" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="F56" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>-0.0504</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="I56" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="J56" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="K56" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="L56" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="M56" t="n">
-        <v>3.45</v>
-      </c>
       <c r="N56" t="n">
-        <v>3.76</v>
+        <v>3.28</v>
       </c>
       <c r="O56" t="n">
-        <v>3.82</v>
+        <v>3.4</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5211,22 +5205,24 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
@@ -5235,59 +5231,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3.02</v>
+        <v>3.17</v>
       </c>
       <c r="C57" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="E57" t="n">
-        <v>3.22</v>
+        <v>3.12</v>
       </c>
       <c r="F57" t="n">
-        <v>0.18</v>
+        <v>-0.1</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.061</v>
+        <v>-0.032</v>
       </c>
       <c r="H57" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="I57" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="J57" t="n">
-        <v>2.79</v>
+        <v>2.96</v>
       </c>
       <c r="K57" t="n">
-        <v>2.91</v>
+        <v>3.07</v>
       </c>
       <c r="L57" t="n">
-        <v>3.03</v>
+        <v>3.18</v>
       </c>
       <c r="M57" t="n">
-        <v>3.16</v>
+        <v>3.37</v>
       </c>
       <c r="N57" t="n">
-        <v>3.28</v>
+        <v>3.56</v>
       </c>
       <c r="O57" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5295,24 +5287,22 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
@@ -5321,85 +5311,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="C58" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="D58" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="E58" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0025</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="I58" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J58" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K58" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="L58" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="M58" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="N58" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="O58" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>弱警訊</t>
         </is>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -5255,7 +5255,7 @@
         <v>-0.1</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.032</v>
+        <v>-0.0323</v>
       </c>
       <c r="H57" t="n">
         <v>0.27</v>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -5246,19 +5246,19 @@
         <v>3.33</v>
       </c>
       <c r="D57" t="n">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="E57" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.1</v>
+        <v>-0.17</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0323</v>
+        <v>-0.0516</v>
       </c>
       <c r="H57" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="I57" t="n">
         <v>2.7</v>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -5249,13 +5249,13 @@
         <v>3.03</v>
       </c>
       <c r="E57" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.17</v>
+        <v>-0.16</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0516</v>
+        <v>-0.0494</v>
       </c>
       <c r="H57" t="n">
         <v>0.3</v>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5246,19 +5249,19 @@
         <v>3.33</v>
       </c>
       <c r="D57" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="E57" t="n">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.16</v>
+        <v>-0.1</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0494</v>
+        <v>-0.0323</v>
       </c>
       <c r="H57" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="I57" t="n">
         <v>2.7</v>
@@ -5314,6 +5317,90 @@
       <c r="X57" t="inlineStr">
         <is>
           <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="C58" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="L58" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="M58" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O58" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -5333,7 +5333,7 @@
         <v>3.05</v>
       </c>
       <c r="D58" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="E58" t="n">
         <v/>
@@ -5345,7 +5345,7 @@
         <v/>
       </c>
       <c r="H58" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="I58" t="n">
         <v>2.79</v>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5327,25 +5324,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3.04</v>
+        <v>3.09</v>
       </c>
       <c r="C58" t="n">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="D58" t="n">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>2.97</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>-0.14</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>-0.0462</v>
       </c>
       <c r="H58" t="n">
-        <v>0.03</v>
+        <v>0.22</v>
       </c>
       <c r="I58" t="n">
         <v>2.79</v>
@@ -5368,20 +5365,20 @@
       <c r="O58" t="n">
         <v>3.61</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5400,7 +5397,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="J2" t="n">
-        <v>2.51</v>
+        <v>2.59</v>
       </c>
       <c r="K2" t="n">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="L2" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="M2" t="n">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="N2" t="n">
-        <v>3.14</v>
+        <v>3.09</v>
       </c>
       <c r="O2" t="n">
-        <v>3.48</v>
+        <v>3.36</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5330,19 +5330,19 @@
         <v>3.18</v>
       </c>
       <c r="D58" t="n">
-        <v>2.97</v>
+        <v>2.77</v>
       </c>
       <c r="E58" t="n">
-        <v>2.97</v>
+        <v>2.78</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.14</v>
+        <v>-0.34</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0462</v>
+        <v>-0.1094</v>
       </c>
       <c r="H58" t="n">
-        <v>0.22</v>
+        <v>0.41</v>
       </c>
       <c r="I58" t="n">
         <v>2.79</v>
@@ -5365,15 +5365,19 @@
       <c r="O58" t="n">
         <v>3.61</v>
       </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
@@ -5390,16 +5394,12 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -5330,19 +5330,19 @@
         <v>3.18</v>
       </c>
       <c r="D58" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="E58" t="n">
         <v>2.77</v>
       </c>
-      <c r="E58" t="n">
-        <v>2.78</v>
-      </c>
       <c r="F58" t="n">
-        <v>-0.34</v>
+        <v>-0.35</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.1094</v>
+        <v>-0.112</v>
       </c>
       <c r="H58" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="I58" t="n">
         <v>2.79</v>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -659,31 +659,33 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.61</v>
+        <v>2.77</v>
       </c>
       <c r="J2" t="n">
-        <v>2.59</v>
+        <v>2.79</v>
       </c>
       <c r="K2" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="L2" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="M2" t="n">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="N2" t="n">
-        <v>3.09</v>
+        <v>2.97</v>
       </c>
       <c r="O2" t="n">
-        <v>3.36</v>
+        <v>3.04</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
@@ -695,8 +697,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -711,7 +715,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -5339,7 +5343,7 @@
         <v>-0.35</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.112</v>
+        <v>-0.1123</v>
       </c>
       <c r="H58" t="n">
         <v>0.43</v>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,138 +634,134 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.91</v>
+        <v>3.15</v>
       </c>
       <c r="C2" t="n">
-        <v>2.97</v>
+        <v>3.59</v>
       </c>
       <c r="D2" t="n">
-        <v>2.77</v>
+        <v>3.13</v>
       </c>
       <c r="E2" t="n">
-        <v>2.84</v>
+        <v>3.32</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.05</v>
+        <v>0.49</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0184</v>
+        <v>0.1725</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="I2" t="n">
-        <v>2.77</v>
+        <v>2.58</v>
       </c>
       <c r="J2" t="n">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="K2" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="L2" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="M2" t="n">
         <v>2.93</v>
       </c>
       <c r="N2" t="n">
-        <v>2.97</v>
+        <v>3.01</v>
       </c>
       <c r="O2" t="n">
-        <v>3.04</v>
+        <v>3.16</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
-      </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="C3" t="n">
-        <v>3.59</v>
+        <v>3.55</v>
       </c>
       <c r="D3" t="n">
-        <v>3.13</v>
+        <v>3.09</v>
       </c>
       <c r="E3" t="n">
-        <v>3.32</v>
+        <v>3.11</v>
       </c>
       <c r="F3" t="n">
-        <v>0.49</v>
+        <v>-0.22</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.1725</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="I3" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="J3" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="K3" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="L3" t="n">
-        <v>2.85</v>
+        <v>3.34</v>
       </c>
       <c r="M3" t="n">
-        <v>2.93</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>3.01</v>
+        <v>3.76</v>
       </c>
       <c r="O3" t="n">
-        <v>3.16</v>
+        <v>4.04</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -773,12 +769,14 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
@@ -786,70 +784,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="C4" t="n">
-        <v>3.55</v>
+        <v>3.14</v>
       </c>
       <c r="D4" t="n">
-        <v>3.09</v>
+        <v>2.89</v>
       </c>
       <c r="E4" t="n">
-        <v>3.11</v>
+        <v>3.01</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.22</v>
+        <v>-0.1</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.0316</v>
       </c>
       <c r="H4" t="n">
-        <v>0.46</v>
+        <v>0.25</v>
       </c>
       <c r="I4" t="n">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="J4" t="n">
-        <v>2.85</v>
+        <v>2.54</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="L4" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="M4" t="n">
         <v>3.34</v>
       </c>
-      <c r="M4" t="n">
-        <v>3.55</v>
-      </c>
       <c r="N4" t="n">
-        <v>3.76</v>
+        <v>3.46</v>
       </c>
       <c r="O4" t="n">
-        <v>4.04</v>
+        <v>4.01</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -862,15 +860,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -892,50 +888,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="C5" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="D5" t="n">
         <v>3.14</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.0984</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K5" t="n">
         <v>2.89</v>
       </c>
-      <c r="E5" t="n">
+      <c r="L5" t="n">
         <v>3.01</v>
       </c>
-      <c r="F5" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>-0.0316</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="L5" t="n">
-        <v>3.21</v>
-      </c>
       <c r="M5" t="n">
-        <v>3.34</v>
+        <v>3.13</v>
       </c>
       <c r="N5" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="O5" t="n">
-        <v>4.01</v>
+        <v>3.38</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -943,83 +939,83 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
+      <c r="V5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.16</v>
+        <v>3.41</v>
       </c>
       <c r="C6" t="n">
-        <v>3.57</v>
+        <v>4.16</v>
       </c>
       <c r="D6" t="n">
-        <v>3.14</v>
+        <v>3.19</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3</v>
+        <v>4.12</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3</v>
+        <v>0.82</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0984</v>
+        <v>0.2482</v>
       </c>
       <c r="H6" t="n">
-        <v>0.44</v>
+        <v>0.96</v>
       </c>
       <c r="I6" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="J6" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="K6" t="n">
-        <v>2.89</v>
+        <v>3.09</v>
       </c>
       <c r="L6" t="n">
-        <v>3.01</v>
+        <v>3.33</v>
       </c>
       <c r="M6" t="n">
-        <v>3.13</v>
+        <v>3.52</v>
       </c>
       <c r="N6" t="n">
-        <v>3.25</v>
+        <v>3.71</v>
       </c>
       <c r="O6" t="n">
-        <v>3.38</v>
+        <v>4.01</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1030,7 +1026,7 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1042,12 +1038,12 @@
       </c>
       <c r="U6" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W6" s="9" t="inlineStr">
@@ -1060,50 +1056,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.41</v>
+        <v>4.16</v>
       </c>
       <c r="C7" t="n">
-        <v>4.16</v>
+        <v>4.42</v>
       </c>
       <c r="D7" t="n">
-        <v>3.19</v>
+        <v>4.09</v>
       </c>
       <c r="E7" t="n">
-        <v>4.12</v>
+        <v>4.32</v>
       </c>
       <c r="F7" t="n">
-        <v>0.82</v>
+        <v>0.19</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.2482</v>
+        <v>0.0463</v>
       </c>
       <c r="H7" t="n">
-        <v>0.96</v>
+        <v>0.33</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7</v>
+        <v>2.23</v>
       </c>
       <c r="J7" t="n">
-        <v>2.84</v>
+        <v>3.38</v>
       </c>
       <c r="K7" t="n">
-        <v>3.09</v>
+        <v>3.64</v>
       </c>
       <c r="L7" t="n">
-        <v>3.33</v>
+        <v>3.9</v>
       </c>
       <c r="M7" t="n">
-        <v>3.52</v>
+        <v>4.61</v>
       </c>
       <c r="N7" t="n">
-        <v>3.71</v>
+        <v>5.31</v>
       </c>
       <c r="O7" t="n">
-        <v>4.01</v>
+        <v>5.12</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1114,25 +1110,21 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="10" t="inlineStr">
+      <c r="S7" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
@@ -1144,50 +1136,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.16</v>
+        <v>4.48</v>
       </c>
       <c r="C8" t="n">
-        <v>4.42</v>
+        <v>4.69</v>
       </c>
       <c r="D8" t="n">
-        <v>4.09</v>
+        <v>4.26</v>
       </c>
       <c r="E8" t="n">
-        <v>4.32</v>
+        <v>4.57</v>
       </c>
       <c r="F8" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0463</v>
+        <v>0.0582</v>
       </c>
       <c r="H8" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="I8" t="n">
-        <v>2.23</v>
+        <v>3.75</v>
       </c>
       <c r="J8" t="n">
-        <v>3.38</v>
+        <v>4.01</v>
       </c>
       <c r="K8" t="n">
-        <v>3.64</v>
+        <v>4.15</v>
       </c>
       <c r="L8" t="n">
-        <v>3.9</v>
+        <v>4.28</v>
       </c>
       <c r="M8" t="n">
-        <v>4.61</v>
+        <v>4.48</v>
       </c>
       <c r="N8" t="n">
-        <v>5.31</v>
+        <v>4.68</v>
       </c>
       <c r="O8" t="n">
-        <v>5.12</v>
+        <v>4.75</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1198,7 +1190,7 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="S8" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1208,8 +1200,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U8" s="8" t="n">
-        <v/>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1224,50 +1218,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.48</v>
+        <v>4.53</v>
       </c>
       <c r="C9" t="n">
-        <v>4.69</v>
+        <v>4.68</v>
       </c>
       <c r="D9" t="n">
-        <v>4.26</v>
+        <v>4.24</v>
       </c>
       <c r="E9" t="n">
-        <v>4.57</v>
+        <v>4.58</v>
       </c>
       <c r="F9" t="n">
-        <v>0.25</v>
+        <v>0.01</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0582</v>
+        <v>0.0031</v>
       </c>
       <c r="H9" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="I9" t="n">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="J9" t="n">
-        <v>4.01</v>
+        <v>4.19</v>
       </c>
       <c r="K9" t="n">
-        <v>4.15</v>
+        <v>4.35</v>
       </c>
       <c r="L9" t="n">
-        <v>4.28</v>
+        <v>4.52</v>
       </c>
       <c r="M9" t="n">
-        <v>4.48</v>
+        <v>4.78</v>
       </c>
       <c r="N9" t="n">
-        <v>4.68</v>
+        <v>5.04</v>
       </c>
       <c r="O9" t="n">
-        <v>4.75</v>
+        <v>5.11</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1275,24 +1269,22 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
@@ -1301,55 +1293,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.53</v>
+        <v>4.47</v>
       </c>
       <c r="C10" t="n">
-        <v>4.68</v>
+        <v>4.87</v>
       </c>
       <c r="D10" t="n">
-        <v>4.24</v>
+        <v>4.27</v>
       </c>
       <c r="E10" t="n">
-        <v>4.58</v>
+        <v>4.85</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01</v>
+        <v>0.27</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.059</v>
       </c>
       <c r="H10" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="I10" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="J10" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="K10" t="n">
-        <v>4.35</v>
+        <v>4.36</v>
       </c>
       <c r="L10" t="n">
         <v>4.52</v>
       </c>
       <c r="M10" t="n">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="N10" t="n">
-        <v>5.04</v>
+        <v>5.08</v>
       </c>
       <c r="O10" t="n">
-        <v>5.11</v>
+        <v>5.12</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1362,13 +1358,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1381,59 +1379,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.47</v>
+        <v>4.87</v>
       </c>
       <c r="C11" t="n">
-        <v>4.87</v>
+        <v>5.5</v>
       </c>
       <c r="D11" t="n">
-        <v>4.27</v>
+        <v>4.76</v>
       </c>
       <c r="E11" t="n">
-        <v>4.85</v>
+        <v>5.29</v>
       </c>
       <c r="F11" t="n">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.059</v>
+        <v>0.0905</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6</v>
+        <v>0.74</v>
       </c>
       <c r="I11" t="n">
-        <v>3.8</v>
+        <v>3.66</v>
       </c>
       <c r="J11" t="n">
-        <v>4.2</v>
+        <v>4.39</v>
       </c>
       <c r="K11" t="n">
-        <v>4.36</v>
+        <v>4.55</v>
       </c>
       <c r="L11" t="n">
-        <v>4.52</v>
+        <v>4.71</v>
       </c>
       <c r="M11" t="n">
-        <v>4.8</v>
+        <v>5.15</v>
       </c>
       <c r="N11" t="n">
-        <v>5.08</v>
+        <v>5.59</v>
       </c>
       <c r="O11" t="n">
-        <v>5.12</v>
+        <v>5.47</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1441,26 +1435,26 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v/>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
@@ -1472,81 +1466,83 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.87</v>
+        <v>5.1</v>
       </c>
       <c r="C12" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="D12" t="n">
-        <v>4.76</v>
+        <v>4.07</v>
       </c>
       <c r="E12" t="n">
-        <v>5.29</v>
+        <v>4.11</v>
       </c>
       <c r="F12" t="n">
-        <v>0.44</v>
+        <v>-1.18</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0905</v>
+        <v>-0.2223</v>
       </c>
       <c r="H12" t="n">
-        <v>0.74</v>
+        <v>1.14</v>
       </c>
       <c r="I12" t="n">
-        <v>3.66</v>
+        <v>4.02</v>
       </c>
       <c r="J12" t="n">
-        <v>4.39</v>
+        <v>4.63</v>
       </c>
       <c r="K12" t="n">
-        <v>4.55</v>
+        <v>4.92</v>
       </c>
       <c r="L12" t="n">
-        <v>4.71</v>
+        <v>5.21</v>
       </c>
       <c r="M12" t="n">
-        <v>5.15</v>
+        <v>5.66</v>
       </c>
       <c r="N12" t="n">
-        <v>5.59</v>
+        <v>6.11</v>
       </c>
       <c r="O12" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+        <v>6.23</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
-      <c r="V12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W12" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="V12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W12" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X12" t="inlineStr"/>
@@ -1554,69 +1550,63 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.1</v>
+        <v>4.17</v>
       </c>
       <c r="C13" t="n">
-        <v>5.2</v>
+        <v>4.22</v>
       </c>
       <c r="D13" t="n">
-        <v>4.07</v>
+        <v>3.84</v>
       </c>
       <c r="E13" t="n">
-        <v>4.11</v>
+        <v>3.98</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.18</v>
+        <v>-0.13</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.2223</v>
+        <v>-0.0314</v>
       </c>
       <c r="H13" t="n">
-        <v>1.14</v>
+        <v>0.38</v>
       </c>
       <c r="I13" t="n">
-        <v>4.02</v>
+        <v>2.93</v>
       </c>
       <c r="J13" t="n">
-        <v>4.63</v>
+        <v>2.71</v>
       </c>
       <c r="K13" t="n">
-        <v>4.92</v>
+        <v>3.54</v>
       </c>
       <c r="L13" t="n">
-        <v>5.21</v>
+        <v>4.37</v>
       </c>
       <c r="M13" t="n">
-        <v>5.66</v>
+        <v>4.68</v>
       </c>
       <c r="N13" t="n">
-        <v>6.11</v>
+        <v>4.99</v>
       </c>
       <c r="O13" t="n">
-        <v>6.23</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>6.34</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1638,50 +1628,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B14" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.0959</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="L14" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="M14" t="n">
         <v>4.17</v>
       </c>
-      <c r="C14" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="D14" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="E14" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>-0.0314</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="L14" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="M14" t="n">
-        <v>4.68</v>
-      </c>
       <c r="N14" t="n">
-        <v>4.99</v>
+        <v>4.34</v>
       </c>
       <c r="O14" t="n">
-        <v>6.34</v>
+        <v>4.6</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1694,103 +1684,111 @@
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="W14" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.08</v>
+        <v>4.45</v>
       </c>
       <c r="C15" t="n">
-        <v>4.59</v>
+        <v>4.72</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8</v>
+        <v>3.56</v>
       </c>
       <c r="E15" t="n">
-        <v>4.37</v>
+        <v>3.62</v>
       </c>
       <c r="F15" t="n">
-        <v>0.38</v>
+        <v>-0.75</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0959</v>
+        <v>-0.1713</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8</v>
+        <v>1.16</v>
       </c>
       <c r="I15" t="n">
-        <v>3.46</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>3.58</v>
+        <v>3.66</v>
       </c>
       <c r="K15" t="n">
-        <v>3.79</v>
+        <v>3.97</v>
       </c>
       <c r="L15" t="n">
-        <v>4.01</v>
+        <v>4.28</v>
       </c>
       <c r="M15" t="n">
-        <v>4.17</v>
+        <v>4.76</v>
       </c>
       <c r="N15" t="n">
-        <v>4.34</v>
+        <v>5.25</v>
       </c>
       <c r="O15" t="n">
-        <v>4.6</v>
+        <v>5.39</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W15" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -1802,65 +1800,63 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.45</v>
+        <v>3.51</v>
       </c>
       <c r="C16" t="n">
-        <v>4.72</v>
+        <v>3.63</v>
       </c>
       <c r="D16" t="n">
-        <v>3.56</v>
+        <v>3.13</v>
       </c>
       <c r="E16" t="n">
-        <v>3.62</v>
+        <v>3.17</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.75</v>
+        <v>-0.45</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.1713</v>
+        <v>-0.1241</v>
       </c>
       <c r="H16" t="n">
-        <v>1.16</v>
+        <v>0.5</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
-        <v>3.66</v>
+        <v>2.2</v>
       </c>
       <c r="K16" t="n">
-        <v>3.97</v>
+        <v>3.04</v>
       </c>
       <c r="L16" t="n">
-        <v>4.28</v>
+        <v>3.88</v>
       </c>
       <c r="M16" t="n">
-        <v>4.76</v>
+        <v>4.2</v>
       </c>
       <c r="N16" t="n">
-        <v>5.25</v>
+        <v>4.51</v>
       </c>
       <c r="O16" t="n">
-        <v>5.39</v>
+        <v>5.88</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1879,59 +1875,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.51</v>
+        <v>3.29</v>
       </c>
       <c r="C17" t="n">
-        <v>3.63</v>
+        <v>3.5</v>
       </c>
       <c r="D17" t="n">
-        <v>3.13</v>
+        <v>3.01</v>
       </c>
       <c r="E17" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.45</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.1241</v>
+        <v>-0.0208</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="I17" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="K17" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="L17" t="n">
-        <v>3.88</v>
+        <v>3.28</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>3.42</v>
       </c>
       <c r="N17" t="n">
-        <v>4.51</v>
+        <v>3.57</v>
       </c>
       <c r="O17" t="n">
-        <v>5.88</v>
+        <v>4.14</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1939,18 +1931,18 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1968,50 +1960,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="C18" t="n">
-        <v>3.5</v>
+        <v>5.65</v>
       </c>
       <c r="D18" t="n">
-        <v>3.01</v>
+        <v>3.38</v>
       </c>
       <c r="E18" t="n">
-        <v>3.1</v>
+        <v>5.28</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.07000000000000001</v>
+        <v>2.17</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.7</v>
       </c>
       <c r="H18" t="n">
-        <v>0.49</v>
+        <v>2.27</v>
       </c>
       <c r="I18" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="J18" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="K18" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="L18" t="n">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="M18" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>3.57</v>
+        <v>3.52</v>
       </c>
       <c r="O18" t="n">
-        <v>4.14</v>
+        <v>3.99</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2024,7 +2016,7 @@
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
@@ -2032,15 +2024,19 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W18" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W18" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
@@ -2048,50 +2044,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.5</v>
+        <v>5.79</v>
       </c>
       <c r="C19" t="n">
-        <v>5.65</v>
+        <v>7.83</v>
       </c>
       <c r="D19" t="n">
-        <v>3.38</v>
+        <v>3.73</v>
       </c>
       <c r="E19" t="n">
-        <v>5.28</v>
+        <v>4.35</v>
       </c>
       <c r="F19" t="n">
-        <v>2.17</v>
+        <v>-0.92</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.7</v>
+        <v>-0.1746</v>
       </c>
       <c r="H19" t="n">
-        <v>2.27</v>
+        <v>4.1</v>
       </c>
       <c r="I19" t="n">
-        <v>2.51</v>
+        <v>1.11</v>
       </c>
       <c r="J19" t="n">
-        <v>2.54</v>
+        <v>3.39</v>
       </c>
       <c r="K19" t="n">
-        <v>2.86</v>
+        <v>4.14</v>
       </c>
       <c r="L19" t="n">
-        <v>3.18</v>
+        <v>4.9</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>6.41</v>
       </c>
       <c r="N19" t="n">
-        <v>3.52</v>
+        <v>7.93</v>
       </c>
       <c r="O19" t="n">
-        <v>3.99</v>
+        <v>7.92</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2099,12 +2095,14 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
@@ -2112,70 +2110,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.79</v>
+        <v>3.71</v>
       </c>
       <c r="C20" t="n">
-        <v>7.83</v>
+        <v>3.74</v>
       </c>
       <c r="D20" t="n">
-        <v>3.73</v>
+        <v>3.15</v>
       </c>
       <c r="E20" t="n">
-        <v>4.35</v>
+        <v>3.42</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.92</v>
+        <v>-0.93</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.1746</v>
+        <v>-0.2141</v>
       </c>
       <c r="H20" t="n">
-        <v>4.1</v>
+        <v>0.58</v>
       </c>
       <c r="I20" t="n">
-        <v>1.11</v>
+        <v>-0.37</v>
       </c>
       <c r="J20" t="n">
-        <v>3.39</v>
+        <v>-0.46</v>
       </c>
       <c r="K20" t="n">
-        <v>4.14</v>
+        <v>2.3</v>
       </c>
       <c r="L20" t="n">
-        <v>4.9</v>
+        <v>5.07</v>
       </c>
       <c r="M20" t="n">
-        <v>6.41</v>
+        <v>6.4</v>
       </c>
       <c r="N20" t="n">
-        <v>7.93</v>
+        <v>7.74</v>
       </c>
       <c r="O20" t="n">
-        <v>7.92</v>
+        <v>11.93</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2188,15 +2186,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S20" s="7" t="inlineStr">
+      <c r="S20" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2211,57 +2207,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>-0.0523</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="L21" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="M21" t="n">
         <v>3.71</v>
       </c>
-      <c r="C21" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="D21" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="E21" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-0.93</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>-0.2141</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I21" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="J21" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="L21" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="M21" t="n">
-        <v>6.4</v>
-      </c>
       <c r="N21" t="n">
-        <v>7.74</v>
+        <v>3.99</v>
       </c>
       <c r="O21" t="n">
-        <v>11.93</v>
+        <v>4.32</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2274,7 +2270,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S21" s="7" t="inlineStr">
+      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2302,63 +2298,65 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="C22" t="n">
-        <v>3.32</v>
+        <v>3.17</v>
       </c>
       <c r="D22" t="n">
-        <v>3.06</v>
+        <v>2.92</v>
       </c>
       <c r="E22" t="n">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.18</v>
+        <v>-0.2</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0523</v>
+        <v>-0.0604</v>
       </c>
       <c r="H22" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="I22" t="n">
-        <v>2.57</v>
+        <v>2.79</v>
       </c>
       <c r="J22" t="n">
-        <v>2.83</v>
+        <v>3.01</v>
       </c>
       <c r="K22" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="L22" t="n">
-        <v>3.43</v>
+        <v>3.21</v>
       </c>
       <c r="M22" t="n">
-        <v>3.71</v>
+        <v>3.37</v>
       </c>
       <c r="N22" t="n">
-        <v>3.99</v>
+        <v>3.53</v>
       </c>
       <c r="O22" t="n">
-        <v>4.32</v>
+        <v>3.58</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2386,50 +2384,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B23" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-0.0617</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="L23" t="n">
         <v>3.05</v>
       </c>
-      <c r="C23" t="n">
+      <c r="M23" t="n">
         <v>3.17</v>
       </c>
-      <c r="D23" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="E23" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="F23" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>-0.0604</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="J23" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="L23" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="M23" t="n">
-        <v>3.37</v>
-      </c>
       <c r="N23" t="n">
-        <v>3.53</v>
+        <v>3.3</v>
       </c>
       <c r="O23" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2444,13 +2442,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S23" s="7" t="inlineStr">
+      <c r="S23" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T23" s="8" t="n">
-        <v/>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2465,84 +2465,82 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.24</v>
+        <v>2.93</v>
       </c>
       <c r="C24" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="D24" t="n">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="E24" t="n">
-        <v>2.86</v>
+        <v>3.19</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.19</v>
+        <v>0.33</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0617</v>
+        <v>0.1144</v>
       </c>
       <c r="H24" t="n">
-        <v>0.48</v>
+        <v>0.41</v>
       </c>
       <c r="I24" t="n">
-        <v>2.67</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="K24" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="L24" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="M24" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="N24" t="n">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="O24" t="n">
-        <v>3.42</v>
+        <v>3.73</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
@@ -2551,59 +2549,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="C25" t="n">
-        <v>3.28</v>
+        <v>3.49</v>
       </c>
       <c r="D25" t="n">
-        <v>2.87</v>
+        <v>2.96</v>
       </c>
       <c r="E25" t="n">
-        <v>3.19</v>
+        <v>3.13</v>
       </c>
       <c r="F25" t="n">
-        <v>0.33</v>
+        <v>-0.06</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.1144</v>
+        <v>-0.0173</v>
       </c>
       <c r="H25" t="n">
-        <v>0.41</v>
+        <v>0.53</v>
       </c>
       <c r="I25" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="J25" t="n">
-        <v>2.3</v>
+        <v>2.83</v>
       </c>
       <c r="K25" t="n">
-        <v>2.62</v>
+        <v>2.98</v>
       </c>
       <c r="L25" t="n">
-        <v>2.94</v>
+        <v>3.13</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>3.39</v>
       </c>
       <c r="N25" t="n">
-        <v>3.26</v>
+        <v>3.66</v>
       </c>
       <c r="O25" t="n">
-        <v>3.73</v>
+        <v>3.69</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2611,12 +2605,14 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
@@ -2624,10 +2620,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2637,55 +2631,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="C26" t="n">
-        <v>3.49</v>
+        <v>3.27</v>
       </c>
       <c r="D26" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="E26" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0173</v>
+        <v>-0.0115</v>
       </c>
       <c r="H26" t="n">
-        <v>0.53</v>
+        <v>0.35</v>
       </c>
       <c r="I26" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="J26" t="n">
-        <v>2.83</v>
+        <v>2.55</v>
       </c>
       <c r="K26" t="n">
-        <v>2.98</v>
+        <v>2.86</v>
       </c>
       <c r="L26" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="M26" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>3.66</v>
+        <v>3.62</v>
       </c>
       <c r="O26" t="n">
-        <v>3.69</v>
+        <v>4.03</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2693,20 +2691,16 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R26" s="6" t="n">
+        <v/>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2721,68 +2715,70 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.18</v>
+        <v>3.11</v>
       </c>
       <c r="C27" t="n">
-        <v>3.27</v>
+        <v>3.15</v>
       </c>
       <c r="D27" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="E27" t="n">
         <v>3.1</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0115</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="I27" t="n">
-        <v>2.43</v>
+        <v>2.58</v>
       </c>
       <c r="J27" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="K27" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="L27" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="N27" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="O27" t="n">
         <v>3.62</v>
       </c>
-      <c r="O27" t="n">
-        <v>4.03</v>
-      </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2803,72 +2799,74 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.11</v>
+        <v>3.06</v>
       </c>
       <c r="C28" t="n">
-        <v>3.15</v>
+        <v>3.06</v>
       </c>
       <c r="D28" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="E28" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0</v>
+        <v>-0.0953</v>
       </c>
       <c r="H28" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="I28" t="n">
         <v>2.58</v>
       </c>
       <c r="J28" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="K28" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="L28" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="M28" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="N28" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="O28" t="n">
         <v>3.44</v>
       </c>
-      <c r="O28" t="n">
-        <v>3.62</v>
-      </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2880,79 +2878,73 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W28" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3.06</v>
+        <v>2.84</v>
       </c>
       <c r="C29" t="n">
-        <v>3.06</v>
+        <v>2.89</v>
       </c>
       <c r="D29" t="n">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
       <c r="E29" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.3</v>
+        <v>-0.15</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0953</v>
+        <v>-0.0543</v>
       </c>
       <c r="H29" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="I29" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
-        <v>2.85</v>
+        <v>2.46</v>
       </c>
       <c r="K29" t="n">
-        <v>2.95</v>
+        <v>2.66</v>
       </c>
       <c r="L29" t="n">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="M29" t="n">
-        <v>3.24</v>
+        <v>2.94</v>
       </c>
       <c r="N29" t="n">
-        <v>3.43</v>
+        <v>3.02</v>
       </c>
       <c r="O29" t="n">
-        <v>3.44</v>
+        <v>3.33</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2976,50 +2968,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.84</v>
+        <v>2.69</v>
       </c>
       <c r="C30" t="n">
-        <v>2.89</v>
+        <v>2.72</v>
       </c>
       <c r="D30" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="E30" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.15</v>
+        <v>0.03</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0543</v>
+        <v>0.0098</v>
       </c>
       <c r="H30" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="I30" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="J30" t="n">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="K30" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="L30" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="M30" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="N30" t="n">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="O30" t="n">
-        <v>3.33</v>
+        <v>3.15</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3027,14 +3019,12 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3051,72 +3041,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>2.69</v>
       </c>
       <c r="C31" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="D31" t="n">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="E31" t="n">
-        <v>2.67</v>
+        <v>2.52</v>
       </c>
       <c r="F31" t="n">
-        <v>0.03</v>
+        <v>-0.15</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0098</v>
+        <v>-0.0565</v>
       </c>
       <c r="H31" t="n">
-        <v>0.16</v>
+        <v>0.27</v>
       </c>
       <c r="I31" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="J31" t="n">
-        <v>2.33</v>
+        <v>2.53</v>
       </c>
       <c r="K31" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="L31" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="M31" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="N31" t="n">
         <v>2.85</v>
       </c>
       <c r="O31" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3138,83 +3138,81 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.69</v>
+        <v>2.51</v>
       </c>
       <c r="C32" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="D32" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="E32" t="n">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.15</v>
+        <v>0.26</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0565</v>
+        <v>0.1019</v>
       </c>
       <c r="H32" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="I32" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="J32" t="n">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="K32" t="n">
-        <v>2.59</v>
+        <v>2.39</v>
       </c>
       <c r="L32" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="M32" t="n">
         <v>2.66</v>
       </c>
-      <c r="M32" t="n">
-        <v>2.75</v>
-      </c>
       <c r="N32" t="n">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="O32" t="n">
-        <v>2.88</v>
+        <v>3.03</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W32" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -3226,50 +3224,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B33" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>-0.0083</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J33" t="n">
         <v>2.51</v>
       </c>
-      <c r="C33" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="D33" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="E33" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>0.1019</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I33" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="J33" t="n">
-        <v>2.2</v>
-      </c>
       <c r="K33" t="n">
-        <v>2.39</v>
+        <v>2.61</v>
       </c>
       <c r="L33" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="M33" t="n">
-        <v>2.66</v>
+        <v>2.95</v>
       </c>
       <c r="N33" t="n">
-        <v>2.74</v>
+        <v>3.18</v>
       </c>
       <c r="O33" t="n">
-        <v>3.03</v>
+        <v>3.16</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3280,20 +3278,16 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3312,50 +3306,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="C34" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="D34" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="E34" t="n">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.02</v>
+        <v>0.2</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0083</v>
+        <v>0.0736</v>
       </c>
       <c r="H34" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="I34" t="n">
-        <v>2.14</v>
+        <v>2.47</v>
       </c>
       <c r="J34" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="K34" t="n">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="L34" t="n">
-        <v>2.72</v>
+        <v>2.77</v>
       </c>
       <c r="M34" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N34" t="n">
         <v>2.95</v>
       </c>
-      <c r="N34" t="n">
-        <v>3.18</v>
-      </c>
       <c r="O34" t="n">
-        <v>3.16</v>
+        <v>3.09</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3366,16 +3360,20 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3385,59 +3383,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="C35" t="n">
-        <v>2.98</v>
+        <v>3.14</v>
       </c>
       <c r="D35" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="E35" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2</v>
+        <v>-0.05</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0736</v>
+        <v>-0.0179</v>
       </c>
       <c r="H35" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="I35" t="n">
-        <v>2.47</v>
+        <v>2.52</v>
       </c>
       <c r="J35" t="n">
-        <v>2.54</v>
+        <v>2.78</v>
       </c>
       <c r="K35" t="n">
-        <v>2.65</v>
+        <v>2.84</v>
       </c>
       <c r="L35" t="n">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="M35" t="n">
-        <v>2.86</v>
+        <v>3.08</v>
       </c>
       <c r="N35" t="n">
-        <v>2.95</v>
+        <v>3.24</v>
       </c>
       <c r="O35" t="n">
-        <v>3.09</v>
+        <v>3.21</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3450,7 +3444,7 @@
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
@@ -3458,10 +3452,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U35" s="8" t="n">
+        <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3471,55 +3463,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="C36" t="n">
-        <v>3.14</v>
+        <v>3.39</v>
       </c>
       <c r="D36" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="E36" t="n">
-        <v>2.91</v>
+        <v>3.29</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.05</v>
+        <v>0.38</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.1318</v>
       </c>
       <c r="H36" t="n">
-        <v>0.25</v>
+        <v>0.53</v>
       </c>
       <c r="I36" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="J36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K36" t="n">
         <v>2.78</v>
       </c>
-      <c r="K36" t="n">
-        <v>2.84</v>
-      </c>
       <c r="L36" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="M36" t="n">
-        <v>3.08</v>
+        <v>3.03</v>
       </c>
       <c r="N36" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="O36" t="n">
-        <v>3.21</v>
+        <v>3.39</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3532,7 +3528,7 @@
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
@@ -3540,11 +3536,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v/>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V36" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W36" s="9" t="inlineStr">
         <is>
@@ -3560,50 +3560,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.9</v>
+        <v>3.34</v>
       </c>
       <c r="C37" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="D37" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="E37" t="n">
-        <v>3.29</v>
+        <v>3.23</v>
       </c>
       <c r="F37" t="n">
-        <v>0.38</v>
+        <v>-0.06</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.1318</v>
+        <v>-0.0185</v>
       </c>
       <c r="H37" t="n">
-        <v>0.53</v>
+        <v>0.3</v>
       </c>
       <c r="I37" t="n">
-        <v>2.64</v>
+        <v>2.33</v>
       </c>
       <c r="J37" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="K37" t="n">
-        <v>2.78</v>
+        <v>3.02</v>
       </c>
       <c r="L37" t="n">
-        <v>2.96</v>
+        <v>3.21</v>
       </c>
       <c r="M37" t="n">
-        <v>3.03</v>
+        <v>3.56</v>
       </c>
       <c r="N37" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="O37" t="n">
-        <v>3.39</v>
+        <v>3.92</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3614,25 +3614,19 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V37" s="8" t="n">
+        <v/>
       </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
@@ -3648,50 +3642,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3.34</v>
+        <v>3.18</v>
       </c>
       <c r="C38" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="D38" t="n">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="E38" t="n">
-        <v>3.23</v>
+        <v>3.12</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.06</v>
+        <v>-0.11</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0185</v>
+        <v>-0.0338</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
       <c r="I38" t="n">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="J38" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="K38" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="L38" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="M38" t="n">
-        <v>3.56</v>
+        <v>3.38</v>
       </c>
       <c r="N38" t="n">
-        <v>3.9</v>
+        <v>3.52</v>
       </c>
       <c r="O38" t="n">
-        <v>3.92</v>
+        <v>3.69</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3699,12 +3693,14 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3723,57 +3719,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="C39" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="D39" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="E39" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.11</v>
+        <v>0.08</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0338</v>
+        <v>0.025</v>
       </c>
       <c r="H39" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="I39" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="J39" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="K39" t="n">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="L39" t="n">
-        <v>3.24</v>
+        <v>3.13</v>
       </c>
       <c r="M39" t="n">
-        <v>3.38</v>
+        <v>3.23</v>
       </c>
       <c r="N39" t="n">
-        <v>3.52</v>
+        <v>3.33</v>
       </c>
       <c r="O39" t="n">
-        <v>3.69</v>
+        <v>3.47</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3781,19 +3777,19 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
@@ -3807,57 +3803,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3.09</v>
+        <v>3.28</v>
       </c>
       <c r="C40" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="D40" t="n">
-        <v>3.02</v>
+        <v>3.14</v>
       </c>
       <c r="E40" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="F40" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.025</v>
+        <v>0.0103</v>
       </c>
       <c r="H40" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="I40" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="J40" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="K40" t="n">
-        <v>3.01</v>
+        <v>3.06</v>
       </c>
       <c r="L40" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="M40" t="n">
-        <v>3.23</v>
+        <v>3.34</v>
       </c>
       <c r="N40" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="O40" t="n">
-        <v>3.47</v>
+        <v>3.58</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3868,14 +3864,14 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U40" s="8" t="n">
@@ -3889,59 +3885,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>3.28</v>
       </c>
       <c r="C41" t="n">
-        <v>3.44</v>
+        <v>3.33</v>
       </c>
       <c r="D41" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="E41" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="F41" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0103</v>
+        <v>0.0043</v>
       </c>
       <c r="H41" t="n">
-        <v>0.31</v>
+        <v>0.18</v>
       </c>
       <c r="I41" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="J41" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="K41" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="L41" t="n">
-        <v>3.18</v>
+        <v>3.26</v>
       </c>
       <c r="M41" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="N41" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="O41" t="n">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3954,13 +3946,11 @@
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3973,72 +3963,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="C42" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>-0.094</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="L42" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="M42" t="n">
         <v>3.33</v>
       </c>
-      <c r="D42" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="E42" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>0.0043</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="I42" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="J42" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K42" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="L42" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="M42" t="n">
-        <v>3.38</v>
-      </c>
       <c r="N42" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="O42" t="n">
         <v>3.51</v>
       </c>
-      <c r="O42" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4046,9 +4048,9 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W42" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
@@ -4060,75 +4062,67 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3.21</v>
+        <v>2.93</v>
       </c>
       <c r="C43" t="n">
-        <v>3.36</v>
+        <v>2.97</v>
       </c>
       <c r="D43" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="E43" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.3</v>
+        <v>-0.03</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.094</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>0.48</v>
+        <v>0.14</v>
       </c>
       <c r="I43" t="n">
-        <v>2.97</v>
+        <v>2.39</v>
       </c>
       <c r="J43" t="n">
-        <v>3.07</v>
+        <v>2.37</v>
       </c>
       <c r="K43" t="n">
-        <v>3.16</v>
+        <v>2.7</v>
       </c>
       <c r="L43" t="n">
-        <v>3.24</v>
+        <v>3.03</v>
       </c>
       <c r="M43" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="N43" t="n">
         <v>3.33</v>
       </c>
-      <c r="N43" t="n">
-        <v>3.42</v>
-      </c>
       <c r="O43" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3.84</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4141,59 +4135,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="C44" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="D44" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="E44" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-0.0137</v>
       </c>
       <c r="H44" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="I44" t="n">
-        <v>2.39</v>
+        <v>2.68</v>
       </c>
       <c r="J44" t="n">
-        <v>2.37</v>
+        <v>2.77</v>
       </c>
       <c r="K44" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="L44" t="n">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="M44" t="n">
-        <v>3.18</v>
+        <v>2.98</v>
       </c>
       <c r="N44" t="n">
-        <v>3.33</v>
+        <v>3.06</v>
       </c>
       <c r="O44" t="n">
-        <v>3.84</v>
+        <v>3.11</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4201,16 +4191,20 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T44" s="8" t="n">
-        <v/>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4223,76 +4217,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="C45" t="n">
-        <v>2.99</v>
+        <v>2.84</v>
       </c>
       <c r="D45" t="n">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="E45" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.04</v>
+        <v>-0.12</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0432</v>
       </c>
       <c r="H45" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="I45" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="J45" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="K45" t="n">
-        <v>2.84</v>
+        <v>2.79</v>
       </c>
       <c r="L45" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="M45" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="N45" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="O45" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
+        <v>3.15</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4305,76 +4305,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="C46" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="D46" t="n">
         <v>2.62</v>
       </c>
       <c r="E46" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.12</v>
+        <v>-0.09</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0432</v>
+        <v>-0.0309</v>
       </c>
       <c r="H46" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="I46" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="J46" t="n">
-        <v>2.69</v>
+        <v>2.54</v>
       </c>
       <c r="K46" t="n">
-        <v>2.79</v>
+        <v>2.64</v>
       </c>
       <c r="L46" t="n">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="M46" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="N46" t="n">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="O46" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3.05</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S46" s="7" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4398,50 +4390,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="C47" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="D47" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="E47" t="n">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0309</v>
+        <v>0.0267</v>
       </c>
       <c r="H47" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="I47" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="J47" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="K47" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="L47" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="M47" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="N47" t="n">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="O47" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4449,19 +4441,19 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
       <c r="U47" s="8" t="n">
         <v/>
       </c>
@@ -4473,55 +4465,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="C48" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="D48" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="E48" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="F48" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0267</v>
+        <v>0.0146</v>
       </c>
       <c r="H48" t="n">
-        <v>0.13</v>
+        <v>0.24</v>
       </c>
       <c r="I48" t="n">
-        <v>2.42</v>
+        <v>2.57</v>
       </c>
       <c r="J48" t="n">
-        <v>2.44</v>
+        <v>2.59</v>
       </c>
       <c r="K48" t="n">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="L48" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="M48" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="N48" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="O48" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4529,21 +4525,25 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4555,57 +4555,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="C49" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="D49" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="E49" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="F49" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0146</v>
+        <v>0.0415</v>
       </c>
       <c r="H49" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="I49" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="J49" t="n">
-        <v>2.59</v>
+        <v>2.54</v>
       </c>
       <c r="K49" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="L49" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="M49" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="N49" t="n">
-        <v>2.84</v>
+        <v>3.02</v>
       </c>
       <c r="O49" t="n">
-        <v>2.96</v>
+        <v>3.11</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4613,25 +4613,21 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4643,57 +4639,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="C50" t="n">
-        <v>2.94</v>
+        <v>3.03</v>
       </c>
       <c r="D50" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="E50" t="n">
-        <v>2.89</v>
+        <v>2.97</v>
       </c>
       <c r="F50" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0415</v>
+        <v>0.0301</v>
       </c>
       <c r="H50" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="I50" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="J50" t="n">
-        <v>2.54</v>
+        <v>2.67</v>
       </c>
       <c r="K50" t="n">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="L50" t="n">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="M50" t="n">
-        <v>2.89</v>
+        <v>3.01</v>
       </c>
       <c r="N50" t="n">
-        <v>3.02</v>
+        <v>3.17</v>
       </c>
       <c r="O50" t="n">
-        <v>3.11</v>
+        <v>3.19</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4704,7 +4700,7 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="10" t="inlineStr">
+      <c r="S50" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4734,69 +4730,71 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B51" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="C51" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>-0.0484</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I51" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K51" t="n">
         <v>2.88</v>
       </c>
-      <c r="C51" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="D51" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="E51" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>0.0301</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="I51" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="J51" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="K51" t="n">
-        <v>2.76</v>
-      </c>
       <c r="L51" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="M51" t="n">
-        <v>3.01</v>
+        <v>3.07</v>
       </c>
       <c r="N51" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="O51" t="n">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4809,81 +4807,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="C52" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="D52" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="E52" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.14</v>
+        <v>0.08</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0484</v>
+        <v>0.0286</v>
       </c>
       <c r="H52" t="n">
-        <v>0.26</v>
+        <v>0.13</v>
       </c>
       <c r="I52" t="n">
-        <v>2.64</v>
+        <v>2.49</v>
       </c>
       <c r="J52" t="n">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="K52" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="L52" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="M52" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N52" t="n">
         <v>3.07</v>
       </c>
-      <c r="N52" t="n">
-        <v>3.19</v>
-      </c>
       <c r="O52" t="n">
-        <v>3.22</v>
+        <v>3.27</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
       <c r="U52" s="8" t="n">
         <v/>
       </c>
@@ -4895,55 +4887,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="C53" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="E53" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.0975</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I53" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K53" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="L53" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="M53" t="n">
         <v>2.98</v>
       </c>
-      <c r="D53" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E53" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>0.0286</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I53" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="J53" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K53" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L53" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="M53" t="n">
-        <v>2.96</v>
-      </c>
       <c r="N53" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="O53" t="n">
-        <v>3.27</v>
+        <v>3.11</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4951,83 +4947,89 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T53" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V53" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W53" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W53" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="C54" t="n">
-        <v>3.32</v>
+        <v>3.16</v>
       </c>
       <c r="D54" t="n">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="E54" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="F54" t="n">
-        <v>0.28</v>
+        <v>-0.16</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0975</v>
+        <v>-0.0504</v>
       </c>
       <c r="H54" t="n">
-        <v>0.5</v>
+        <v>0.24</v>
       </c>
       <c r="I54" t="n">
-        <v>2.71</v>
+        <v>2.32</v>
       </c>
       <c r="J54" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="K54" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="L54" t="n">
-        <v>2.91</v>
+        <v>3.13</v>
       </c>
       <c r="M54" t="n">
-        <v>2.98</v>
+        <v>3.45</v>
       </c>
       <c r="N54" t="n">
-        <v>3.04</v>
+        <v>3.76</v>
       </c>
       <c r="O54" t="n">
-        <v>3.11</v>
+        <v>3.82</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5037,28 +5039,22 @@
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V54" s="8" t="n">
+        <v/>
       </c>
       <c r="W54" s="9" t="inlineStr">
         <is>
@@ -5067,57 +5063,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="C55" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D55" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I55" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K55" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L55" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="M55" t="n">
         <v>3.16</v>
       </c>
-      <c r="D55" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E55" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="F55" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>-0.0504</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="I55" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="J55" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="K55" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="L55" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="M55" t="n">
-        <v>3.45</v>
-      </c>
       <c r="N55" t="n">
-        <v>3.76</v>
+        <v>3.28</v>
       </c>
       <c r="O55" t="n">
-        <v>3.82</v>
+        <v>3.4</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5125,22 +5121,24 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
@@ -5149,59 +5147,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3.02</v>
+        <v>3.17</v>
       </c>
       <c r="C56" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="E56" t="n">
-        <v>3.22</v>
+        <v>3.12</v>
       </c>
       <c r="F56" t="n">
-        <v>0.18</v>
+        <v>-0.1</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.061</v>
+        <v>-0.0323</v>
       </c>
       <c r="H56" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="I56" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="J56" t="n">
-        <v>2.79</v>
+        <v>2.96</v>
       </c>
       <c r="K56" t="n">
-        <v>2.91</v>
+        <v>3.07</v>
       </c>
       <c r="L56" t="n">
-        <v>3.03</v>
+        <v>3.18</v>
       </c>
       <c r="M56" t="n">
-        <v>3.16</v>
+        <v>3.37</v>
       </c>
       <c r="N56" t="n">
-        <v>3.28</v>
+        <v>3.56</v>
       </c>
       <c r="O56" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5209,23 +5203,21 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
@@ -5235,68 +5227,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3.17</v>
+        <v>3.09</v>
       </c>
       <c r="C57" t="n">
-        <v>3.33</v>
+        <v>3.18</v>
       </c>
       <c r="D57" t="n">
-        <v>3.06</v>
+        <v>2.73</v>
       </c>
       <c r="E57" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0323</v>
+        <v>-0.0221</v>
       </c>
       <c r="H57" t="n">
-        <v>0.27</v>
+        <v>0.46</v>
       </c>
       <c r="I57" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="J57" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="K57" t="n">
-        <v>3.07</v>
+        <v>2.98</v>
       </c>
       <c r="L57" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="M57" t="n">
-        <v>3.37</v>
+        <v>3.25</v>
       </c>
       <c r="N57" t="n">
-        <v>3.56</v>
+        <v>3.35</v>
       </c>
       <c r="O57" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
+        <v>3.61</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="7" t="inlineStr">
+      <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5317,93 +5317,9 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="C58" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="D58" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="E58" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.1123</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="I58" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="J58" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K58" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="L58" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="M58" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N58" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O58" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -5246,19 +5246,19 @@
         <v>3.18</v>
       </c>
       <c r="D57" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="E57" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.13</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0221</v>
+        <v>-0.0417</v>
       </c>
       <c r="H57" t="n">
-        <v>0.46</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I57" t="n">
         <v>2.79</v>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5249,13 +5252,13 @@
         <v>2.62</v>
       </c>
       <c r="E57" t="n">
-        <v>2.99</v>
+        <v>2.64</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.13</v>
+        <v>-0.48</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0417</v>
+        <v>-0.1528</v>
       </c>
       <c r="H57" t="n">
         <v>0.5600000000000001</v>
@@ -5283,41 +5286,123 @@
       </c>
       <c r="P57" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W57" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="C58" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="L58" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="M58" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="O58" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W57" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>強警訊</t>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -662,25 +659,25 @@
         <v>0.45</v>
       </c>
       <c r="I2" t="n">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="J2" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="K2" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="L2" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="M2" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="N2" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="O2" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5327,25 +5324,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3.04</v>
+        <v>2.54</v>
       </c>
       <c r="C58" t="n">
         <v>3.07</v>
       </c>
       <c r="D58" t="n">
-        <v>3.03</v>
+        <v>2.5</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>3.06</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>0.42</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>0.158</v>
       </c>
       <c r="H58" t="n">
-        <v>0.04</v>
+        <v>0.58</v>
       </c>
       <c r="I58" t="n">
         <v>2.06</v>
@@ -5368,29 +5365,29 @@
       <c r="O58" t="n">
         <v>3.75</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
       </c>
       <c r="V58" s="8" t="n">
         <v/>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -5327,22 +5327,22 @@
         <v>2.54</v>
       </c>
       <c r="C58" t="n">
-        <v>3.07</v>
+        <v>3.03</v>
       </c>
       <c r="D58" t="n">
         <v>2.5</v>
       </c>
       <c r="E58" t="n">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="F58" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.158</v>
+        <v>0.147</v>
       </c>
       <c r="H58" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="I58" t="n">
         <v>2.06</v>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>0.45</v>
       </c>
       <c r="I2" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="J2" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="K2" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="L2" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="M2" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="N2" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="O2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5327,22 +5327,22 @@
         <v>2.54</v>
       </c>
       <c r="C58" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="D58" t="n">
         <v>2.5</v>
       </c>
       <c r="E58" t="n">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="F58" t="n">
-        <v>0.39</v>
+        <v>0.26</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.147</v>
+        <v>0.097</v>
       </c>
       <c r="H58" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="I58" t="n">
         <v>2.06</v>
@@ -5381,13 +5381,11 @@
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
       </c>
       <c r="V58" s="8" t="n">
         <v/>

--- a/three_gate/analysis/NG_weekly.xlsx
+++ b/three_gate/analysis/NG_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="C2" t="n">
-        <v>3.59</v>
+        <v>3.55</v>
       </c>
       <c r="D2" t="n">
-        <v>3.13</v>
+        <v>3.09</v>
       </c>
       <c r="E2" t="n">
-        <v>3.32</v>
+        <v>3.11</v>
       </c>
       <c r="F2" t="n">
-        <v>0.49</v>
+        <v>-0.22</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.1725</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="I2" t="n">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="J2" t="n">
-        <v>2.66</v>
+        <v>2.85</v>
       </c>
       <c r="K2" t="n">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="L2" t="n">
-        <v>2.85</v>
+        <v>3.34</v>
       </c>
       <c r="M2" t="n">
-        <v>2.91</v>
+        <v>3.55</v>
       </c>
       <c r="N2" t="n">
-        <v>2.98</v>
+        <v>3.76</v>
       </c>
       <c r="O2" t="n">
-        <v>3.1</v>
+        <v>4.04</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,12 +685,14 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
@@ -698,70 +700,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="C3" t="n">
-        <v>3.55</v>
+        <v>3.14</v>
       </c>
       <c r="D3" t="n">
-        <v>3.09</v>
+        <v>2.89</v>
       </c>
       <c r="E3" t="n">
-        <v>3.11</v>
+        <v>3.01</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.22</v>
+        <v>-0.1</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.0316</v>
       </c>
       <c r="H3" t="n">
-        <v>0.46</v>
+        <v>0.25</v>
       </c>
       <c r="I3" t="n">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="J3" t="n">
-        <v>2.85</v>
+        <v>2.54</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="L3" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="M3" t="n">
         <v>3.34</v>
       </c>
-      <c r="M3" t="n">
-        <v>3.55</v>
-      </c>
       <c r="N3" t="n">
-        <v>3.76</v>
+        <v>3.46</v>
       </c>
       <c r="O3" t="n">
-        <v>4.04</v>
+        <v>4.01</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -774,15 +776,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -804,50 +804,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="C4" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="D4" t="n">
         <v>3.14</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.0984</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K4" t="n">
         <v>2.89</v>
       </c>
-      <c r="E4" t="n">
+      <c r="L4" t="n">
         <v>3.01</v>
       </c>
-      <c r="F4" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>-0.0316</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3.21</v>
-      </c>
       <c r="M4" t="n">
-        <v>3.34</v>
+        <v>3.13</v>
       </c>
       <c r="N4" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="O4" t="n">
-        <v>4.01</v>
+        <v>3.38</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -855,83 +855,83 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.16</v>
+        <v>3.41</v>
       </c>
       <c r="C5" t="n">
-        <v>3.57</v>
+        <v>4.16</v>
       </c>
       <c r="D5" t="n">
-        <v>3.14</v>
+        <v>3.19</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3</v>
+        <v>4.12</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3</v>
+        <v>0.82</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0984</v>
+        <v>0.2482</v>
       </c>
       <c r="H5" t="n">
-        <v>0.44</v>
+        <v>0.96</v>
       </c>
       <c r="I5" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="J5" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="K5" t="n">
-        <v>2.89</v>
+        <v>3.09</v>
       </c>
       <c r="L5" t="n">
-        <v>3.01</v>
+        <v>3.33</v>
       </c>
       <c r="M5" t="n">
-        <v>3.13</v>
+        <v>3.52</v>
       </c>
       <c r="N5" t="n">
-        <v>3.25</v>
+        <v>3.71</v>
       </c>
       <c r="O5" t="n">
-        <v>3.38</v>
+        <v>4.01</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -942,7 +942,7 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -954,12 +954,12 @@
       </c>
       <c r="U5" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W5" s="9" t="inlineStr">
@@ -972,50 +972,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.41</v>
+        <v>4.16</v>
       </c>
       <c r="C6" t="n">
-        <v>4.16</v>
+        <v>4.42</v>
       </c>
       <c r="D6" t="n">
-        <v>3.19</v>
+        <v>4.09</v>
       </c>
       <c r="E6" t="n">
-        <v>4.12</v>
+        <v>4.32</v>
       </c>
       <c r="F6" t="n">
-        <v>0.82</v>
+        <v>0.19</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.2482</v>
+        <v>0.0463</v>
       </c>
       <c r="H6" t="n">
-        <v>0.96</v>
+        <v>0.33</v>
       </c>
       <c r="I6" t="n">
-        <v>2.7</v>
+        <v>2.23</v>
       </c>
       <c r="J6" t="n">
-        <v>2.84</v>
+        <v>3.38</v>
       </c>
       <c r="K6" t="n">
-        <v>3.09</v>
+        <v>3.64</v>
       </c>
       <c r="L6" t="n">
-        <v>3.33</v>
+        <v>3.9</v>
       </c>
       <c r="M6" t="n">
-        <v>3.52</v>
+        <v>4.61</v>
       </c>
       <c r="N6" t="n">
-        <v>3.71</v>
+        <v>5.31</v>
       </c>
       <c r="O6" t="n">
-        <v>4.01</v>
+        <v>5.12</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1026,25 +1026,21 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="7" t="inlineStr">
+      <c r="S6" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
@@ -1056,50 +1052,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.16</v>
+        <v>4.48</v>
       </c>
       <c r="C7" t="n">
-        <v>4.42</v>
+        <v>4.69</v>
       </c>
       <c r="D7" t="n">
-        <v>4.09</v>
+        <v>4.26</v>
       </c>
       <c r="E7" t="n">
-        <v>4.32</v>
+        <v>4.57</v>
       </c>
       <c r="F7" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0463</v>
+        <v>0.0582</v>
       </c>
       <c r="H7" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="I7" t="n">
-        <v>2.23</v>
+        <v>3.75</v>
       </c>
       <c r="J7" t="n">
-        <v>3.38</v>
+        <v>4.01</v>
       </c>
       <c r="K7" t="n">
-        <v>3.64</v>
+        <v>4.15</v>
       </c>
       <c r="L7" t="n">
-        <v>3.9</v>
+        <v>4.28</v>
       </c>
       <c r="M7" t="n">
-        <v>4.61</v>
+        <v>4.48</v>
       </c>
       <c r="N7" t="n">
-        <v>5.31</v>
+        <v>4.68</v>
       </c>
       <c r="O7" t="n">
-        <v>5.12</v>
+        <v>4.75</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1110,7 +1106,7 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1120,8 +1116,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U7" s="8" t="n">
-        <v/>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
@@ -1136,50 +1134,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.48</v>
+        <v>4.53</v>
       </c>
       <c r="C8" t="n">
-        <v>4.69</v>
+        <v>4.68</v>
       </c>
       <c r="D8" t="n">
-        <v>4.26</v>
+        <v>4.24</v>
       </c>
       <c r="E8" t="n">
-        <v>4.57</v>
+        <v>4.58</v>
       </c>
       <c r="F8" t="n">
-        <v>0.25</v>
+        <v>0.01</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0582</v>
+        <v>0.0031</v>
       </c>
       <c r="H8" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="I8" t="n">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="J8" t="n">
-        <v>4.01</v>
+        <v>4.19</v>
       </c>
       <c r="K8" t="n">
-        <v>4.15</v>
+        <v>4.35</v>
       </c>
       <c r="L8" t="n">
-        <v>4.28</v>
+        <v>4.52</v>
       </c>
       <c r="M8" t="n">
-        <v>4.48</v>
+        <v>4.78</v>
       </c>
       <c r="N8" t="n">
-        <v>4.68</v>
+        <v>5.04</v>
       </c>
       <c r="O8" t="n">
-        <v>4.75</v>
+        <v>5.11</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1187,24 +1185,22 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
+      <c r="R8" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
@@ -1213,55 +1209,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.53</v>
+        <v>4.47</v>
       </c>
       <c r="C9" t="n">
-        <v>4.68</v>
+        <v>4.87</v>
       </c>
       <c r="D9" t="n">
-        <v>4.24</v>
+        <v>4.27</v>
       </c>
       <c r="E9" t="n">
-        <v>4.58</v>
+        <v>4.85</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01</v>
+        <v>0.27</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.059</v>
       </c>
       <c r="H9" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="I9" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="J9" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="K9" t="n">
-        <v>4.35</v>
+        <v>4.36</v>
       </c>
       <c r="L9" t="n">
         <v>4.52</v>
       </c>
       <c r="M9" t="n">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="N9" t="n">
-        <v>5.04</v>
+        <v>5.08</v>
       </c>
       <c r="O9" t="n">
-        <v>5.11</v>
+        <v>5.12</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1274,13 +1274,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1293,59 +1295,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.47</v>
+        <v>4.87</v>
       </c>
       <c r="C10" t="n">
-        <v>4.87</v>
+        <v>5.5</v>
       </c>
       <c r="D10" t="n">
-        <v>4.27</v>
+        <v>4.76</v>
       </c>
       <c r="E10" t="n">
-        <v>4.85</v>
+        <v>5.29</v>
       </c>
       <c r="F10" t="n">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.059</v>
+        <v>0.0905</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6</v>
+        <v>0.74</v>
       </c>
       <c r="I10" t="n">
-        <v>3.8</v>
+        <v>3.66</v>
       </c>
       <c r="J10" t="n">
-        <v>4.2</v>
+        <v>4.39</v>
       </c>
       <c r="K10" t="n">
-        <v>4.36</v>
+        <v>4.55</v>
       </c>
       <c r="L10" t="n">
-        <v>4.52</v>
+        <v>4.71</v>
       </c>
       <c r="M10" t="n">
-        <v>4.8</v>
+        <v>5.15</v>
       </c>
       <c r="N10" t="n">
-        <v>5.08</v>
+        <v>5.59</v>
       </c>
       <c r="O10" t="n">
-        <v>5.12</v>
+        <v>5.47</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1353,26 +1351,26 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V10" s="8" t="n">
-        <v/>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
@@ -1384,81 +1382,83 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.87</v>
+        <v>5.1</v>
       </c>
       <c r="C11" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="D11" t="n">
-        <v>4.76</v>
+        <v>4.07</v>
       </c>
       <c r="E11" t="n">
-        <v>5.29</v>
+        <v>4.11</v>
       </c>
       <c r="F11" t="n">
-        <v>0.44</v>
+        <v>-1.18</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0905</v>
+        <v>-0.2223</v>
       </c>
       <c r="H11" t="n">
-        <v>0.74</v>
+        <v>1.14</v>
       </c>
       <c r="I11" t="n">
-        <v>3.66</v>
+        <v>4.02</v>
       </c>
       <c r="J11" t="n">
-        <v>4.39</v>
+        <v>4.63</v>
       </c>
       <c r="K11" t="n">
-        <v>4.55</v>
+        <v>4.92</v>
       </c>
       <c r="L11" t="n">
-        <v>4.71</v>
+        <v>5.21</v>
       </c>
       <c r="M11" t="n">
-        <v>5.15</v>
+        <v>5.66</v>
       </c>
       <c r="N11" t="n">
-        <v>5.59</v>
+        <v>6.11</v>
       </c>
       <c r="O11" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+        <v>6.23</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W11" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="V11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W11" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X11" t="inlineStr"/>
@@ -1466,69 +1466,63 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.1</v>
+        <v>4.17</v>
       </c>
       <c r="C12" t="n">
-        <v>5.2</v>
+        <v>4.22</v>
       </c>
       <c r="D12" t="n">
-        <v>4.07</v>
+        <v>3.84</v>
       </c>
       <c r="E12" t="n">
-        <v>4.11</v>
+        <v>3.98</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.18</v>
+        <v>-0.13</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.2223</v>
+        <v>-0.0314</v>
       </c>
       <c r="H12" t="n">
-        <v>1.14</v>
+        <v>0.38</v>
       </c>
       <c r="I12" t="n">
-        <v>4.02</v>
+        <v>2.93</v>
       </c>
       <c r="J12" t="n">
-        <v>4.63</v>
+        <v>2.71</v>
       </c>
       <c r="K12" t="n">
-        <v>4.92</v>
+        <v>3.54</v>
       </c>
       <c r="L12" t="n">
-        <v>5.21</v>
+        <v>4.37</v>
       </c>
       <c r="M12" t="n">
-        <v>5.66</v>
+        <v>4.68</v>
       </c>
       <c r="N12" t="n">
-        <v>6.11</v>
+        <v>4.99</v>
       </c>
       <c r="O12" t="n">
-        <v>6.23</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>6.34</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1550,50 +1544,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B13" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.0959</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="M13" t="n">
         <v>4.17</v>
       </c>
-      <c r="C13" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="D13" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="E13" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>-0.0314</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="L13" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="M13" t="n">
-        <v>4.68</v>
-      </c>
       <c r="N13" t="n">
-        <v>4.99</v>
+        <v>4.34</v>
       </c>
       <c r="O13" t="n">
-        <v>6.34</v>
+        <v>4.6</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1606,103 +1600,111 @@
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="W13" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.08</v>
+        <v>4.45</v>
       </c>
       <c r="C14" t="n">
-        <v>4.59</v>
+        <v>4.72</v>
       </c>
       <c r="D14" t="n">
-        <v>3.8</v>
+        <v>3.56</v>
       </c>
       <c r="E14" t="n">
-        <v>4.37</v>
+        <v>3.62</v>
       </c>
       <c r="F14" t="n">
-        <v>0.38</v>
+        <v>-0.75</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0959</v>
+        <v>-0.1713</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8</v>
+        <v>1.16</v>
       </c>
       <c r="I14" t="n">
-        <v>3.46</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>3.58</v>
+        <v>3.66</v>
       </c>
       <c r="K14" t="n">
-        <v>3.79</v>
+        <v>3.97</v>
       </c>
       <c r="L14" t="n">
-        <v>4.01</v>
+        <v>4.28</v>
       </c>
       <c r="M14" t="n">
-        <v>4.17</v>
+        <v>4.76</v>
       </c>
       <c r="N14" t="n">
-        <v>4.34</v>
+        <v>5.25</v>
       </c>
       <c r="O14" t="n">
-        <v>4.6</v>
+        <v>5.39</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W14" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -1714,65 +1716,63 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.45</v>
+        <v>3.51</v>
       </c>
       <c r="C15" t="n">
-        <v>4.72</v>
+        <v>3.63</v>
       </c>
       <c r="D15" t="n">
-        <v>3.56</v>
+        <v>3.13</v>
       </c>
       <c r="E15" t="n">
-        <v>3.62</v>
+        <v>3.17</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.75</v>
+        <v>-0.45</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.1713</v>
+        <v>-0.1241</v>
       </c>
       <c r="H15" t="n">
-        <v>1.16</v>
+        <v>0.5</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J15" t="n">
-        <v>3.66</v>
+        <v>2.2</v>
       </c>
       <c r="K15" t="n">
-        <v>3.97</v>
+        <v>3.04</v>
       </c>
       <c r="L15" t="n">
-        <v>4.28</v>
+        <v>3.88</v>
       </c>
       <c r="M15" t="n">
-        <v>4.76</v>
+        <v>4.2</v>
       </c>
       <c r="N15" t="n">
-        <v>5.25</v>
+        <v>4.51</v>
       </c>
       <c r="O15" t="n">
-        <v>5.39</v>
+        <v>5.88</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1791,59 +1791,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.51</v>
+        <v>3.29</v>
       </c>
       <c r="C16" t="n">
-        <v>3.63</v>
+        <v>3.5</v>
       </c>
       <c r="D16" t="n">
-        <v>3.13</v>
+        <v>3.01</v>
       </c>
       <c r="E16" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.45</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.1241</v>
+        <v>-0.0208</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="K16" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="L16" t="n">
-        <v>3.88</v>
+        <v>3.28</v>
       </c>
       <c r="M16" t="n">
-        <v>4.2</v>
+        <v>3.42</v>
       </c>
       <c r="N16" t="n">
-        <v>4.51</v>
+        <v>3.57</v>
       </c>
       <c r="O16" t="n">
-        <v>5.88</v>
+        <v>4.14</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1851,18 +1847,18 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1880,50 +1876,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="C17" t="n">
-        <v>3.5</v>
+        <v>5.65</v>
       </c>
       <c r="D17" t="n">
-        <v>3.01</v>
+        <v>3.38</v>
       </c>
       <c r="E17" t="n">
-        <v>3.1</v>
+        <v>5.28</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.07000000000000001</v>
+        <v>2.17</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.7</v>
       </c>
       <c r="H17" t="n">
-        <v>0.49</v>
+        <v>2.27</v>
       </c>
       <c r="I17" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="J17" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="K17" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="L17" t="n">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="M17" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>3.57</v>
+        <v>3.52</v>
       </c>
       <c r="O17" t="n">
-        <v>4.14</v>
+        <v>3.99</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1936,7 +1932,7 @@
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
@@ -1944,15 +1940,19 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W17" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W17" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr"/>
@@ -1960,50 +1960,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.5</v>
+        <v>5.79</v>
       </c>
       <c r="C18" t="n">
-        <v>5.65</v>
+        <v>7.83</v>
       </c>
       <c r="D18" t="n">
-        <v>3.38</v>
+        <v>3.73</v>
       </c>
       <c r="E18" t="n">
-        <v>5.28</v>
+        <v>4.35</v>
       </c>
       <c r="F18" t="n">
-        <v>2.17</v>
+        <v>-0.92</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.7</v>
+        <v>-0.1746</v>
       </c>
       <c r="H18" t="n">
-        <v>2.27</v>
+        <v>4.1</v>
       </c>
       <c r="I18" t="n">
-        <v>2.51</v>
+        <v>1.11</v>
       </c>
       <c r="J18" t="n">
-        <v>2.54</v>
+        <v>3.39</v>
       </c>
       <c r="K18" t="n">
-        <v>2.86</v>
+        <v>4.14</v>
       </c>
       <c r="L18" t="n">
-        <v>3.18</v>
+        <v>4.9</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>6.41</v>
       </c>
       <c r="N18" t="n">
-        <v>3.52</v>
+        <v>7.93</v>
       </c>
       <c r="O18" t="n">
-        <v>3.99</v>
+        <v>7.92</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2011,12 +2011,14 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
@@ -2024,70 +2026,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v/>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.79</v>
+        <v>3.71</v>
       </c>
       <c r="C19" t="n">
-        <v>7.83</v>
+        <v>3.74</v>
       </c>
       <c r="D19" t="n">
-        <v>3.73</v>
+        <v>3.15</v>
       </c>
       <c r="E19" t="n">
-        <v>4.35</v>
+        <v>3.42</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.92</v>
+        <v>-0.93</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.1746</v>
+        <v>-0.2141</v>
       </c>
       <c r="H19" t="n">
-        <v>4.1</v>
+        <v>0.58</v>
       </c>
       <c r="I19" t="n">
-        <v>1.11</v>
+        <v>-0.37</v>
       </c>
       <c r="J19" t="n">
-        <v>3.39</v>
+        <v>-0.46</v>
       </c>
       <c r="K19" t="n">
-        <v>4.14</v>
+        <v>2.3</v>
       </c>
       <c r="L19" t="n">
-        <v>4.9</v>
+        <v>5.07</v>
       </c>
       <c r="M19" t="n">
-        <v>6.41</v>
+        <v>6.4</v>
       </c>
       <c r="N19" t="n">
-        <v>7.93</v>
+        <v>7.74</v>
       </c>
       <c r="O19" t="n">
-        <v>7.92</v>
+        <v>11.93</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2100,15 +2102,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S19" s="10" t="inlineStr">
+      <c r="S19" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2123,57 +2123,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>-0.0523</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="M20" t="n">
         <v>3.71</v>
       </c>
-      <c r="C20" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="D20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="E20" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-0.93</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>-0.2141</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I20" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="J20" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="L20" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="M20" t="n">
-        <v>6.4</v>
-      </c>
       <c r="N20" t="n">
-        <v>7.74</v>
+        <v>3.99</v>
       </c>
       <c r="O20" t="n">
-        <v>11.93</v>
+        <v>4.32</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2186,7 +2186,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2214,63 +2214,65 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="C21" t="n">
-        <v>3.32</v>
+        <v>3.17</v>
       </c>
       <c r="D21" t="n">
-        <v>3.06</v>
+        <v>2.92</v>
       </c>
       <c r="E21" t="n">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.18</v>
+        <v>-0.2</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0523</v>
+        <v>-0.0604</v>
       </c>
       <c r="H21" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="I21" t="n">
-        <v>2.57</v>
+        <v>2.79</v>
       </c>
       <c r="J21" t="n">
-        <v>2.83</v>
+        <v>3.01</v>
       </c>
       <c r="K21" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="L21" t="n">
-        <v>3.43</v>
+        <v>3.21</v>
       </c>
       <c r="M21" t="n">
-        <v>3.71</v>
+        <v>3.37</v>
       </c>
       <c r="N21" t="n">
-        <v>3.99</v>
+        <v>3.53</v>
       </c>
       <c r="O21" t="n">
-        <v>4.32</v>
+        <v>3.58</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2298,50 +2300,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B22" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-0.0617</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="L22" t="n">
         <v>3.05</v>
       </c>
-      <c r="C22" t="n">
+      <c r="M22" t="n">
         <v>3.17</v>
       </c>
-      <c r="D22" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="E22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>-0.0604</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="L22" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="M22" t="n">
-        <v>3.37</v>
-      </c>
       <c r="N22" t="n">
-        <v>3.53</v>
+        <v>3.3</v>
       </c>
       <c r="O22" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2356,13 +2358,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S22" s="10" t="inlineStr">
+      <c r="S22" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T22" s="8" t="n">
-        <v/>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2377,84 +2381,82 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.24</v>
+        <v>2.93</v>
       </c>
       <c r="C23" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="D23" t="n">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="E23" t="n">
-        <v>2.86</v>
+        <v>3.19</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.19</v>
+        <v>0.33</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0617</v>
+        <v>0.1144</v>
       </c>
       <c r="H23" t="n">
-        <v>0.48</v>
+        <v>0.41</v>
       </c>
       <c r="I23" t="n">
-        <v>2.67</v>
+        <v>2.3</v>
       </c>
       <c r="J23" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="K23" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="L23" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="M23" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="O23" t="n">
-        <v>3.42</v>
+        <v>3.73</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
@@ -2463,59 +2465,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="C24" t="n">
-        <v>3.28</v>
+        <v>3.49</v>
       </c>
       <c r="D24" t="n">
-        <v>2.87</v>
+        <v>2.96</v>
       </c>
       <c r="E24" t="n">
-        <v>3.19</v>
+        <v>3.13</v>
       </c>
       <c r="F24" t="n">
-        <v>0.33</v>
+        <v>-0.06</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.1144</v>
+        <v>-0.0173</v>
       </c>
       <c r="H24" t="n">
-        <v>0.41</v>
+        <v>0.53</v>
       </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="J24" t="n">
-        <v>2.3</v>
+        <v>2.83</v>
       </c>
       <c r="K24" t="n">
-        <v>2.62</v>
+        <v>2.98</v>
       </c>
       <c r="L24" t="n">
-        <v>2.94</v>
+        <v>3.13</v>
       </c>
       <c r="M24" t="n">
-        <v>3.1</v>
+        <v>3.39</v>
       </c>
       <c r="N24" t="n">
-        <v>3.26</v>
+        <v>3.66</v>
       </c>
       <c r="O24" t="n">
-        <v>3.73</v>
+        <v>3.69</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2523,12 +2521,14 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
@@ -2536,10 +2536,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2549,55 +2547,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="C25" t="n">
-        <v>3.49</v>
+        <v>3.27</v>
       </c>
       <c r="D25" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="E25" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0173</v>
+        <v>-0.0115</v>
       </c>
       <c r="H25" t="n">
-        <v>0.53</v>
+        <v>0.35</v>
       </c>
       <c r="I25" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="J25" t="n">
-        <v>2.83</v>
+        <v>2.55</v>
       </c>
       <c r="K25" t="n">
-        <v>2.98</v>
+        <v>2.86</v>
       </c>
       <c r="L25" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="M25" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>3.66</v>
+        <v>3.62</v>
       </c>
       <c r="O25" t="n">
-        <v>3.69</v>
+        <v>4.03</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2605,20 +2607,16 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R25" s="6" t="n">
+        <v/>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2633,68 +2631,70 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.18</v>
+        <v>3.11</v>
       </c>
       <c r="C26" t="n">
-        <v>3.27</v>
+        <v>3.15</v>
       </c>
       <c r="D26" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="E26" t="n">
         <v>3.1</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0115</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="I26" t="n">
-        <v>2.43</v>
+        <v>2.58</v>
       </c>
       <c r="J26" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="K26" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="L26" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="N26" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="O26" t="n">
         <v>3.62</v>
       </c>
-      <c r="O26" t="n">
-        <v>4.03</v>
-      </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2715,72 +2715,74 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.11</v>
+        <v>3.06</v>
       </c>
       <c r="C27" t="n">
-        <v>3.15</v>
+        <v>3.06</v>
       </c>
       <c r="D27" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="E27" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0</v>
+        <v>-0.0953</v>
       </c>
       <c r="H27" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="I27" t="n">
         <v>2.58</v>
       </c>
       <c r="J27" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="K27" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="L27" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="M27" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="N27" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="O27" t="n">
         <v>3.44</v>
       </c>
-      <c r="O27" t="n">
-        <v>3.62</v>
-      </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2792,79 +2794,73 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W27" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.06</v>
+        <v>2.84</v>
       </c>
       <c r="C28" t="n">
-        <v>3.06</v>
+        <v>2.89</v>
       </c>
       <c r="D28" t="n">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
       <c r="E28" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.3</v>
+        <v>-0.15</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0953</v>
+        <v>-0.0543</v>
       </c>
       <c r="H28" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="I28" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="J28" t="n">
-        <v>2.85</v>
+        <v>2.46</v>
       </c>
       <c r="K28" t="n">
-        <v>2.95</v>
+        <v>2.66</v>
       </c>
       <c r="L28" t="n">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="M28" t="n">
-        <v>3.24</v>
+        <v>2.94</v>
       </c>
       <c r="N28" t="n">
-        <v>3.43</v>
+        <v>3.02</v>
       </c>
       <c r="O28" t="n">
-        <v>3.44</v>
+        <v>3.33</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
+      <c r="S28" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2888,50 +2884,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.84</v>
+        <v>2.69</v>
       </c>
       <c r="C29" t="n">
-        <v>2.89</v>
+        <v>2.72</v>
       </c>
       <c r="D29" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="E29" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.15</v>
+        <v>0.03</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0543</v>
+        <v>0.0098</v>
       </c>
       <c r="H29" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="J29" t="n">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="K29" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="L29" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="M29" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="N29" t="n">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="O29" t="n">
-        <v>3.33</v>
+        <v>3.15</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2939,14 +2935,12 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2963,72 +2957,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>2.69</v>
       </c>
       <c r="C30" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="D30" t="n">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="E30" t="n">
-        <v>2.67</v>
+        <v>2.52</v>
       </c>
       <c r="F30" t="n">
-        <v>0.03</v>
+        <v>-0.15</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0098</v>
+        <v>-0.0565</v>
       </c>
       <c r="H30" t="n">
-        <v>0.16</v>
+        <v>0.27</v>
       </c>
       <c r="I30" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="J30" t="n">
-        <v>2.33</v>
+        <v>2.53</v>
       </c>
       <c r="K30" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="L30" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="M30" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="N30" t="n">
         <v>2.85</v>
       </c>
       <c r="O30" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3050,83 +3054,81 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.69</v>
+        <v>2.51</v>
       </c>
       <c r="C31" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="D31" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="E31" t="n">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.15</v>
+        <v>0.26</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0565</v>
+        <v>0.1019</v>
       </c>
       <c r="H31" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="I31" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="J31" t="n">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="K31" t="n">
-        <v>2.59</v>
+        <v>2.39</v>
       </c>
       <c r="L31" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="M31" t="n">
         <v>2.66</v>
       </c>
-      <c r="M31" t="n">
-        <v>2.75</v>
-      </c>
       <c r="N31" t="n">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="O31" t="n">
-        <v>2.88</v>
+        <v>3.03</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W31" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -3138,50 +3140,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B32" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>-0.0083</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J32" t="n">
         <v>2.51</v>
       </c>
-      <c r="C32" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="D32" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="E32" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>0.1019</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I32" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2.2</v>
-      </c>
       <c r="K32" t="n">
-        <v>2.39</v>
+        <v>2.61</v>
       </c>
       <c r="L32" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="M32" t="n">
-        <v>2.66</v>
+        <v>2.95</v>
       </c>
       <c r="N32" t="n">
-        <v>2.74</v>
+        <v>3.18</v>
       </c>
       <c r="O32" t="n">
-        <v>3.03</v>
+        <v>3.16</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3192,20 +3194,16 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3224,50 +3222,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="C33" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="D33" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="E33" t="n">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.02</v>
+        <v>0.2</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0083</v>
+        <v>0.0736</v>
       </c>
       <c r="H33" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="I33" t="n">
-        <v>2.14</v>
+        <v>2.47</v>
       </c>
       <c r="J33" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="K33" t="n">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="L33" t="n">
-        <v>2.72</v>
+        <v>2.77</v>
       </c>
       <c r="M33" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N33" t="n">
         <v>2.95</v>
       </c>
-      <c r="N33" t="n">
-        <v>3.18</v>
-      </c>
       <c r="O33" t="n">
-        <v>3.16</v>
+        <v>3.09</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3278,16 +3276,20 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3297,59 +3299,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="C34" t="n">
-        <v>2.98</v>
+        <v>3.14</v>
       </c>
       <c r="D34" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="E34" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2</v>
+        <v>-0.05</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0736</v>
+        <v>-0.0179</v>
       </c>
       <c r="H34" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="I34" t="n">
-        <v>2.47</v>
+        <v>2.52</v>
       </c>
       <c r="J34" t="n">
-        <v>2.54</v>
+        <v>2.78</v>
       </c>
       <c r="K34" t="n">
-        <v>2.65</v>
+        <v>2.84</v>
       </c>
       <c r="L34" t="n">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="M34" t="n">
-        <v>2.86</v>
+        <v>3.08</v>
       </c>
       <c r="N34" t="n">
-        <v>2.95</v>
+        <v>3.24</v>
       </c>
       <c r="O34" t="n">
-        <v>3.09</v>
+        <v>3.21</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3362,7 +3360,7 @@
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
@@ -3370,10 +3368,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3383,55 +3379,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="C35" t="n">
-        <v>3.14</v>
+        <v>3.39</v>
       </c>
       <c r="D35" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="E35" t="n">
-        <v>2.91</v>
+        <v>3.29</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.05</v>
+        <v>0.38</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.1318</v>
       </c>
       <c r="H35" t="n">
-        <v>0.25</v>
+        <v>0.53</v>
       </c>
       <c r="I35" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="J35" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K35" t="n">
         <v>2.78</v>
       </c>
-      <c r="K35" t="n">
-        <v>2.84</v>
-      </c>
       <c r="L35" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="M35" t="n">
-        <v>3.08</v>
+        <v>3.03</v>
       </c>
       <c r="N35" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="O35" t="n">
-        <v>3.21</v>
+        <v>3.39</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
@@ -3452,11 +3452,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v/>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
@@ -3472,50 +3476,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.9</v>
+        <v>3.34</v>
       </c>
       <c r="C36" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="D36" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="E36" t="n">
-        <v>3.29</v>
+        <v>3.23</v>
       </c>
       <c r="F36" t="n">
-        <v>0.38</v>
+        <v>-0.06</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.1318</v>
+        <v>-0.0185</v>
       </c>
       <c r="H36" t="n">
-        <v>0.53</v>
+        <v>0.3</v>
       </c>
       <c r="I36" t="n">
-        <v>2.64</v>
+        <v>2.33</v>
       </c>
       <c r="J36" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="K36" t="n">
-        <v>2.78</v>
+        <v>3.02</v>
       </c>
       <c r="L36" t="n">
-        <v>2.96</v>
+        <v>3.21</v>
       </c>
       <c r="M36" t="n">
-        <v>3.03</v>
+        <v>3.56</v>
       </c>
       <c r="N36" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="O36" t="n">
-        <v>3.39</v>
+        <v>3.92</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3526,25 +3530,19 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v/>
       </c>
       <c r="W36" s="9" t="inlineStr">
         <is>
@@ -3560,50 +3558,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3.34</v>
+        <v>3.18</v>
       </c>
       <c r="C37" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="D37" t="n">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="E37" t="n">
-        <v>3.23</v>
+        <v>3.12</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.06</v>
+        <v>-0.11</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0185</v>
+        <v>-0.0338</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
       <c r="I37" t="n">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="J37" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="K37" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="L37" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="M37" t="n">
-        <v>3.56</v>
+        <v>3.38</v>
       </c>
       <c r="N37" t="n">
-        <v>3.9</v>
+        <v>3.52</v>
       </c>
       <c r="O37" t="n">
-        <v>3.92</v>
+        <v>3.69</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3611,12 +3609,14 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3635,57 +3635,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="C38" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="D38" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="E38" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.11</v>
+        <v>0.08</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0338</v>
+        <v>0.025</v>
       </c>
       <c r="H38" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="I38" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="J38" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="K38" t="n">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="L38" t="n">
-        <v>3.24</v>
+        <v>3.13</v>
       </c>
       <c r="M38" t="n">
-        <v>3.38</v>
+        <v>3.23</v>
       </c>
       <c r="N38" t="n">
-        <v>3.52</v>
+        <v>3.33</v>
       </c>
       <c r="O38" t="n">
-        <v>3.69</v>
+        <v>3.47</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3693,19 +3693,19 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
@@ -3719,57 +3719,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3.09</v>
+        <v>3.28</v>
       </c>
       <c r="C39" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="D39" t="n">
-        <v>3.02</v>
+        <v>3.14</v>
       </c>
       <c r="E39" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="F39" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.025</v>
+        <v>0.0103</v>
       </c>
       <c r="H39" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="I39" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="J39" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="K39" t="n">
-        <v>3.01</v>
+        <v>3.06</v>
       </c>
       <c r="L39" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="M39" t="n">
-        <v>3.23</v>
+        <v>3.34</v>
       </c>
       <c r="N39" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="O39" t="n">
-        <v>3.47</v>
+        <v>3.58</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3780,14 +3780,14 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U39" s="8" t="n">
@@ -3801,59 +3801,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>3.28</v>
       </c>
       <c r="C40" t="n">
-        <v>3.44</v>
+        <v>3.33</v>
       </c>
       <c r="D40" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="E40" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="F40" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0103</v>
+        <v>0.0043</v>
       </c>
       <c r="H40" t="n">
-        <v>0.31</v>
+        <v>0.18</v>
       </c>
       <c r="I40" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="J40" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="K40" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="L40" t="n">
-        <v>3.18</v>
+        <v>3.26</v>
       </c>
       <c r="M40" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="N40" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="O40" t="n">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3866,13 +3862,11 @@
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3885,72 +3879,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="C41" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>-0.094</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="J41" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="L41" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="M41" t="n">
         <v>3.33</v>
       </c>
-      <c r="D41" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="E41" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>0.0043</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="I41" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="J41" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K41" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="L41" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="M41" t="n">
-        <v>3.38</v>
-      </c>
       <c r="N41" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="O41" t="n">
         <v>3.51</v>
       </c>
-      <c r="O41" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3958,9 +3964,9 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W41" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
@@ -3972,75 +3978,67 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3.21</v>
+        <v>2.93</v>
       </c>
       <c r="C42" t="n">
-        <v>3.36</v>
+        <v>2.97</v>
       </c>
       <c r="D42" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="E42" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.3</v>
+        <v>-0.03</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.094</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>0.48</v>
+        <v>0.14</v>
       </c>
       <c r="I42" t="n">
-        <v>2.97</v>
+        <v>2.39</v>
       </c>
       <c r="J42" t="n">
-        <v>3.07</v>
+        <v>2.37</v>
       </c>
       <c r="K42" t="n">
-        <v>3.16</v>
+        <v>2.7</v>
       </c>
       <c r="L42" t="n">
-        <v>3.24</v>
+        <v>3.03</v>
       </c>
       <c r="M42" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="N42" t="n">
         <v>3.33</v>
       </c>
-      <c r="N42" t="n">
-        <v>3.42</v>
-      </c>
       <c r="O42" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3.84</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4053,59 +4051,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="C43" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="D43" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="E43" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-0.0137</v>
       </c>
       <c r="H43" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="I43" t="n">
-        <v>2.39</v>
+        <v>2.68</v>
       </c>
       <c r="J43" t="n">
-        <v>2.37</v>
+        <v>2.77</v>
       </c>
       <c r="K43" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="L43" t="n">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="M43" t="n">
-        <v>3.18</v>
+        <v>2.98</v>
       </c>
       <c r="N43" t="n">
-        <v>3.33</v>
+        <v>3.06</v>
       </c>
       <c r="O43" t="n">
-        <v>3.84</v>
+        <v>3.11</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4113,16 +4107,20 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4135,76 +4133,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="C44" t="n">
-        <v>2.99</v>
+        <v>2.84</v>
       </c>
       <c r="D44" t="n">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="E44" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.04</v>
+        <v>-0.12</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0432</v>
       </c>
       <c r="H44" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="I44" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="J44" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="K44" t="n">
-        <v>2.84</v>
+        <v>2.79</v>
       </c>
       <c r="L44" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="M44" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="N44" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="O44" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
+        <v>3.15</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4217,76 +4221,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="C45" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="D45" t="n">
         <v>2.62</v>
       </c>
       <c r="E45" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.12</v>
+        <v>-0.09</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0432</v>
+        <v>-0.0309</v>
       </c>
       <c r="H45" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="I45" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="J45" t="n">
-        <v>2.69</v>
+        <v>2.54</v>
       </c>
       <c r="K45" t="n">
-        <v>2.79</v>
+        <v>2.64</v>
       </c>
       <c r="L45" t="n">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="M45" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="N45" t="n">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="O45" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3.05</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
+      <c r="S45" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4310,50 +4306,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="C46" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="D46" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="E46" t="n">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0309</v>
+        <v>0.0267</v>
       </c>
       <c r="H46" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="I46" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="J46" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="K46" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="L46" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="M46" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="N46" t="n">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="O46" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4361,19 +4357,19 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
@@ -4385,55 +4381,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="C47" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="D47" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="E47" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="F47" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0267</v>
+        <v>0.0146</v>
       </c>
       <c r="H47" t="n">
-        <v>0.13</v>
+        <v>0.24</v>
       </c>
       <c r="I47" t="n">
-        <v>2.42</v>
+        <v>2.57</v>
       </c>
       <c r="J47" t="n">
-        <v>2.44</v>
+        <v>2.59</v>
       </c>
       <c r="K47" t="n">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="L47" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="M47" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="N47" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="O47" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4441,21 +4441,25 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4467,57 +4471,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="C48" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="D48" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="E48" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="F48" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0146</v>
+        <v>0.0415</v>
       </c>
       <c r="H48" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="I48" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="J48" t="n">
-        <v>2.59</v>
+        <v>2.54</v>
       </c>
       <c r="K48" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="L48" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="M48" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="N48" t="n">
-        <v>2.84</v>
+        <v>3.02</v>
       </c>
       <c r="O48" t="n">
-        <v>2.96</v>
+        <v>3.11</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4525,25 +4529,21 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4555,57 +4555,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="C49" t="n">
-        <v>2.94</v>
+        <v>3.03</v>
       </c>
       <c r="D49" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="E49" t="n">
-        <v>2.89</v>
+        <v>2.97</v>
       </c>
       <c r="F49" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0415</v>
+        <v>0.0301</v>
       </c>
       <c r="H49" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="I49" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="J49" t="n">
-        <v>2.54</v>
+        <v>2.67</v>
       </c>
       <c r="K49" t="n">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="L49" t="n">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="M49" t="n">
-        <v>2.89</v>
+        <v>3.01</v>
       </c>
       <c r="N49" t="n">
-        <v>3.02</v>
+        <v>3.17</v>
       </c>
       <c r="O49" t="n">
-        <v>3.11</v>
+        <v>3.19</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4616,7 +4616,7 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="7" t="inlineStr">
+      <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4646,69 +4646,71 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B50" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="C50" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>-0.0484</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I50" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K50" t="n">
         <v>2.88</v>
       </c>
-      <c r="C50" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="D50" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="E50" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>0.0301</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="I50" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="J50" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="K50" t="n">
-        <v>2.76</v>
-      </c>
       <c r="L50" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="M50" t="n">
-        <v>3.01</v>
+        <v>3.07</v>
       </c>
       <c r="N50" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="O50" t="n">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4721,81 +4723,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="C51" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="D51" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="E51" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.14</v>
+        <v>0.08</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0484</v>
+        <v>0.0286</v>
       </c>
       <c r="H51" t="n">
-        <v>0.26</v>
+        <v>0.13</v>
       </c>
       <c r="I51" t="n">
-        <v>2.64</v>
+        <v>2.49</v>
       </c>
       <c r="J51" t="n">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="K51" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="L51" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="M51" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N51" t="n">
         <v>3.07</v>
       </c>
-      <c r="N51" t="n">
-        <v>3.19</v>
-      </c>
       <c r="O51" t="n">
-        <v>3.22</v>
+        <v>3.27</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
       <c r="U51" s="8" t="n">
         <v/>
       </c>
@@ -4807,55 +4803,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="C52" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="E52" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.0975</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I52" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K52" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="L52" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="M52" t="n">
         <v>2.98</v>
       </c>
-      <c r="D52" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E52" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>0.0286</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I52" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="J52" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K52" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L52" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="M52" t="n">
-        <v>2.96</v>
-      </c>
       <c r="N52" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="O52" t="n">
-        <v>3.27</v>
+        <v>3.11</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4863,83 +4863,89 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V52" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W52" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W52" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="C53" t="n">
-        <v>3.32</v>
+        <v>3.16</v>
       </c>
       <c r="D53" t="n">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="E53" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="F53" t="n">
-        <v>0.28</v>
+        <v>-0.16</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0975</v>
+        <v>-0.0504</v>
       </c>
       <c r="H53" t="n">
-        <v>0.5</v>
+        <v>0.24</v>
       </c>
       <c r="I53" t="n">
-        <v>2.71</v>
+        <v>2.32</v>
       </c>
       <c r="J53" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="K53" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="L53" t="n">
-        <v>2.91</v>
+        <v>3.13</v>
       </c>
       <c r="M53" t="n">
-        <v>2.98</v>
+        <v>3.45</v>
       </c>
       <c r="N53" t="n">
-        <v>3.04</v>
+        <v>3.76</v>
       </c>
       <c r="O53" t="n">
-        <v>3.11</v>
+        <v>3.82</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4949,28 +4955,22 @@
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V53" s="8" t="n">
+        <v/>
       </c>
       <c r="W53" s="9" t="inlineStr">
         <is>
@@ -4979,57 +4979,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="C54" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D54" t="n">
+        <v>3</v>
+      </c>
+      <c r="E54" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I54" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K54" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L54" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="M54" t="n">
         <v>3.16</v>
       </c>
-      <c r="D54" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E54" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="F54" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>-0.0504</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="I54" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="J54" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="K54" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="L54" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="M54" t="n">
-        <v>3.45</v>
-      </c>
       <c r="N54" t="n">
-        <v>3.76</v>
+        <v>3.28</v>
       </c>
       <c r="O54" t="n">
-        <v>3.82</v>
+        <v>3.4</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5037,22 +5037,24 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
@@ -5061,59 +5063,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3.02</v>
+        <v>3.17</v>
       </c>
       <c r="C55" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="E55" t="n">
-        <v>3.22</v>
+        <v>3.12</v>
       </c>
       <c r="F55" t="n">
-        <v>0.18</v>
+        <v>-0.1</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.061</v>
+        <v>-0.0323</v>
       </c>
       <c r="H55" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="I55" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="J55" t="n">
-        <v>2.79</v>
+        <v>2.96</v>
       </c>
       <c r="K55" t="n">
-        <v>2.91</v>
+        <v>3.07</v>
       </c>
       <c r="L55" t="n">
-        <v>3.03</v>
+        <v>3.18</v>
       </c>
       <c r="M55" t="n">
-        <v>3.16</v>
+        <v>3.37</v>
       </c>
       <c r="N55" t="n">
-        <v>3.28</v>
+        <v>3.56</v>
       </c>
       <c r="O55" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5121,23 +5119,21 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
@@ -5147,68 +5143,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3.17</v>
+        <v>3.09</v>
       </c>
       <c r="C56" t="n">
-        <v>3.33</v>
+        <v>3.18</v>
       </c>
       <c r="D56" t="n">
-        <v>3.06</v>
+        <v>2.62</v>
       </c>
       <c r="E56" t="n">
-        <v>3.12</v>
+        <v>2.64</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.1</v>
+        <v>-0.48</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0323</v>
+        <v>-0.1528</v>
       </c>
       <c r="H56" t="n">
-        <v>0.27</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="J56" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="K56" t="n">
-        <v>3.07</v>
+        <v>2.98</v>
       </c>
       <c r="L56" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="M56" t="n">
-        <v>3.37</v>
+        <v>3.25</v>
       </c>
       <c r="N56" t="n">
-        <v>3.56</v>
+        <v>3.35</v>
       </c>
       <c r="O56" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
+        <v>3.61</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5222,88 +5226,80 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W56" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3.09</v>
+        <v>2.54</v>
       </c>
       <c r="C57" t="n">
-        <v>3.18</v>
+        <v>3.07</v>
       </c>
       <c r="D57" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="E57" t="n">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.48</v>
+        <v>0.24</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.1528</v>
+        <v>0.092</v>
       </c>
       <c r="H57" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="I57" t="n">
-        <v>2.79</v>
+        <v>2.06</v>
       </c>
       <c r="J57" t="n">
-        <v>2.8</v>
+        <v>1.95</v>
       </c>
       <c r="K57" t="n">
-        <v>2.98</v>
+        <v>2.36</v>
       </c>
       <c r="L57" t="n">
-        <v>3.16</v>
+        <v>2.77</v>
       </c>
       <c r="M57" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="N57" t="n">
-        <v>3.35</v>
+        <v>3.07</v>
       </c>
       <c r="O57" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
+        <v>3.75</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
@@ -5315,87 +5311,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="C58" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="D58" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E58" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I58" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="J58" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="K58" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="L58" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="M58" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="N58" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="O58" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>弱警訊</t>
         </is>
